--- a/outputs/Block5_Election_Projection_Report.xlsx
+++ b/outputs/Block5_Election_Projection_Report.xlsx
@@ -68,16 +68,16 @@
     <t>Overall Diagnostic Stability</t>
   </si>
   <si>
-    <t>52.07%</t>
-  </si>
-  <si>
-    <t>45.01%</t>
+    <t>52.36%</t>
+  </si>
+  <si>
+    <t>44.72%</t>
   </si>
   <si>
     <t>2.92%</t>
   </si>
   <si>
-    <t>D 219 - R 216</t>
+    <t>D 223 - R 212</t>
   </si>
   <si>
     <t>Democratic</t>
@@ -89,7 +89,7 @@
     <t>Republican</t>
   </si>
   <si>
-    <t>70.0/100</t>
+    <t>69.1/100</t>
   </si>
   <si>
     <t>Party</t>
@@ -812,7 +812,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -820,7 +820,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1006,10 +1006,10 @@
         <v>118</v>
       </c>
       <c r="P2">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="Q2">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>119</v>
       </c>
       <c r="T2">
-        <v>0.141286249557361</v>
+        <v>0.1495117733786751</v>
       </c>
       <c r="U2">
-        <v>-0.141286249557361</v>
+        <v>-0.1495117733786751</v>
       </c>
       <c r="V2" t="s">
         <v>96</v>
@@ -1050,25 +1050,25 @@
         <v>90</v>
       </c>
       <c r="C3">
-        <v>15.048</v>
+        <v>15.328</v>
       </c>
       <c r="D3">
-        <v>14.824</v>
+        <v>14.864</v>
       </c>
       <c r="E3">
-        <v>15.00521451603779</v>
+        <v>15.0529980979447</v>
       </c>
       <c r="F3">
         <v>14.2</v>
       </c>
       <c r="G3">
-        <v>14.93988810988627</v>
+        <v>15.10405394190727</v>
       </c>
       <c r="J3" t="s">
         <v>94</v>
       </c>
       <c r="K3">
-        <v>15.00521451603779</v>
+        <v>15.0529980979447</v>
       </c>
       <c r="L3">
         <v>6.129350049043507</v>
@@ -1083,10 +1083,10 @@
         <v>118</v>
       </c>
       <c r="P3">
-        <v>14.85295632081913</v>
+        <v>14.78112560442925</v>
       </c>
       <c r="Q3">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R3">
         <v>15</v>
@@ -1095,34 +1095,34 @@
         <v>119</v>
       </c>
       <c r="T3">
-        <v>-0.152258195218657</v>
+        <v>-0.2718724935154491</v>
       </c>
       <c r="U3">
-        <v>0.1470436791808698</v>
+        <v>0.2188743955707473</v>
       </c>
       <c r="V3" t="s">
         <v>96</v>
       </c>
       <c r="W3">
-        <v>14.93988810988627</v>
+        <v>15.10405394190727</v>
       </c>
       <c r="X3">
-        <v>0.06532640615151664</v>
+        <v>0.05105584396257257</v>
       </c>
       <c r="Y3">
-        <v>0.00521451603778722</v>
+        <v>0.05299809794470178</v>
       </c>
       <c r="Z3">
-        <v>0.01065796628171219</v>
+        <v>0.00832973211744366</v>
       </c>
       <c r="AA3">
-        <v>0.0008507453475594778</v>
+        <v>0.008646609758072507</v>
       </c>
       <c r="AB3">
         <v>0.972912706197382</v>
       </c>
       <c r="AC3">
-        <v>99.2800601772977</v>
+        <v>99.1594882890594</v>
       </c>
       <c r="AD3" t="s">
         <v>121</v>
@@ -1136,25 +1136,25 @@
         <v>90</v>
       </c>
       <c r="C4">
-        <v>13.316</v>
+        <v>13.532</v>
       </c>
       <c r="D4">
-        <v>12.472</v>
+        <v>12.556</v>
       </c>
       <c r="E4">
-        <v>12.98388364583827</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="F4">
         <v>11.8</v>
       </c>
       <c r="G4">
-        <v>12.9086498426072</v>
+        <v>13.06094105021875</v>
       </c>
       <c r="J4" t="s">
         <v>94</v>
       </c>
       <c r="K4">
-        <v>12.98388364583827</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="L4">
         <v>3.125306797245826</v>
@@ -1169,10 +1169,10 @@
         <v>118</v>
       </c>
       <c r="P4">
-        <v>12.85213593315269</v>
+        <v>13.11473458118962</v>
       </c>
       <c r="Q4">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R4">
         <v>13</v>
@@ -1181,34 +1181,34 @@
         <v>119</v>
       </c>
       <c r="T4">
-        <v>-0.1317477126855753</v>
+        <v>-0.2412221969964765</v>
       </c>
       <c r="U4">
-        <v>0.1478640668473066</v>
+        <v>-0.1147345811896248</v>
       </c>
       <c r="V4" t="s">
         <v>96</v>
       </c>
       <c r="W4">
-        <v>12.9086498426072</v>
+        <v>13.06094105021875</v>
       </c>
       <c r="X4">
-        <v>0.07523380323107176</v>
+        <v>0.2950157279673533</v>
       </c>
       <c r="Y4">
-        <v>0.01611635416173129</v>
+        <v>0.3559567781861013</v>
       </c>
       <c r="Z4">
-        <v>0.02407245371794266</v>
+        <v>0.09439576563406053</v>
       </c>
       <c r="AA4">
-        <v>0.005156727069462051</v>
+        <v>0.1138949873656525</v>
       </c>
       <c r="AB4">
         <v>0.6511055827595471</v>
       </c>
       <c r="AC4">
-        <v>98.2699453837879</v>
+        <v>90.37337437343564</v>
       </c>
       <c r="AD4" t="s">
         <v>121</v>
@@ -1222,25 +1222,25 @@
         <v>90</v>
       </c>
       <c r="C5">
-        <v>172.1</v>
+        <v>171.868</v>
       </c>
       <c r="D5">
-        <v>175.156</v>
+        <v>174.552</v>
       </c>
       <c r="E5">
-        <v>175.5898630732044</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="F5">
         <v>172.6</v>
       </c>
       <c r="G5">
-        <v>173.5749550722659</v>
+        <v>173.1634121118985</v>
       </c>
       <c r="J5" t="s">
         <v>94</v>
       </c>
       <c r="K5">
-        <v>175.5898630732044</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="L5">
         <v>24.70132137894479</v>
@@ -1255,221 +1255,221 @@
         <v>118</v>
       </c>
       <c r="P5">
-        <v>173.8081494148196</v>
+        <v>172.4018190334305</v>
       </c>
       <c r="Q5">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R5">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="S5" t="s">
         <v>119</v>
       </c>
       <c r="T5">
-        <v>-1.781713658384717</v>
+        <v>-3.171024567518231</v>
       </c>
       <c r="U5">
-        <v>0.1918505851803616</v>
+        <v>-0.4018190334304563</v>
       </c>
       <c r="V5" t="s">
         <v>96</v>
       </c>
       <c r="W5">
-        <v>173.5749550722659</v>
+        <v>173.1634121118985</v>
       </c>
       <c r="X5">
-        <v>2.014908000938448</v>
+        <v>2.409431489050235</v>
       </c>
       <c r="Y5">
-        <v>1.589863073204356</v>
+        <v>3.572843600948687</v>
       </c>
       <c r="Z5">
-        <v>0.08157085890376452</v>
+        <v>0.09754261531547112</v>
       </c>
       <c r="AA5">
-        <v>0.06436348277948976</v>
+        <v>0.1446418005797111</v>
       </c>
       <c r="AB5">
         <v>1.320926276948919</v>
       </c>
       <c r="AC5">
-        <v>92.72349650896915</v>
+        <v>89.22335706647648</v>
       </c>
       <c r="AD5" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6">
-        <v>1.412</v>
+        <v>1.168</v>
       </c>
       <c r="D6">
-        <v>1.808</v>
+        <v>1.328</v>
       </c>
       <c r="E6">
-        <v>1.699906626866217</v>
+        <v>1.138895095514905</v>
       </c>
       <c r="F6">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="G6">
-        <v>1.603126377165344</v>
+        <v>1.243204011857575</v>
       </c>
       <c r="J6" t="s">
         <v>94</v>
       </c>
       <c r="K6">
-        <v>1.699906626866217</v>
+        <v>1.138895095514905</v>
       </c>
       <c r="L6">
-        <v>1.746417103282563</v>
+        <v>0.9319718387197466</v>
       </c>
       <c r="M6">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N6">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="O6" t="s">
         <v>118</v>
       </c>
       <c r="P6">
-        <v>1.717926703142854</v>
+        <v>0.9726626509918868</v>
       </c>
       <c r="Q6">
-        <v>1.010600627112006</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="s">
         <v>119</v>
       </c>
       <c r="T6">
-        <v>0.01802007627663649</v>
+        <v>-0.1662324445230186</v>
       </c>
       <c r="U6">
-        <v>0.2820732968571464</v>
+        <v>0.02733734900811324</v>
       </c>
       <c r="V6" t="s">
         <v>96</v>
       </c>
       <c r="W6">
-        <v>1.603126377165344</v>
+        <v>1.243204011857575</v>
       </c>
       <c r="X6">
-        <v>0.09678024970087273</v>
+        <v>0.10430891634267</v>
       </c>
       <c r="Y6">
-        <v>0.3000933731337829</v>
+        <v>0.1388950955149053</v>
       </c>
       <c r="Z6">
-        <v>0.05541645779748992</v>
+        <v>0.1119228199920285</v>
       </c>
       <c r="AA6">
-        <v>0.1718337346615124</v>
+        <v>0.1490335756343304</v>
       </c>
       <c r="AB6">
-        <v>0.7593117840358968</v>
+        <v>1.035524265244163</v>
       </c>
       <c r="AC6">
-        <v>90.83163983910151</v>
+        <v>88.25749324682307</v>
       </c>
       <c r="AD6" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7">
-        <v>1.164</v>
+        <v>1.344</v>
       </c>
       <c r="D7">
-        <v>1.34</v>
+        <v>1.788</v>
       </c>
       <c r="E7">
-        <v>1.234402433809649</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="F7">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="G7">
-        <v>1.246724413043333</v>
+        <v>1.558293210761144</v>
       </c>
       <c r="J7" t="s">
         <v>94</v>
       </c>
       <c r="K7">
-        <v>1.234402433809649</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="L7">
-        <v>0.9319718387197466</v>
+        <v>1.746417103282563</v>
       </c>
       <c r="M7">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N7">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="s">
         <v>118</v>
       </c>
       <c r="P7">
-        <v>1.06279383028951</v>
+        <v>1.501280428022223</v>
       </c>
       <c r="Q7">
-        <v>0.8609783982760665</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="s">
         <v>119</v>
       </c>
       <c r="T7">
-        <v>-0.1716086035201392</v>
+        <v>0.02825555268635682</v>
       </c>
       <c r="U7">
-        <v>-0.06279383028951013</v>
+        <v>0.4987195719777766</v>
       </c>
       <c r="V7" t="s">
         <v>96</v>
       </c>
       <c r="W7">
-        <v>1.246724413043333</v>
+        <v>1.558293210761144</v>
       </c>
       <c r="X7">
-        <v>0.01232197923368372</v>
+        <v>0.08526833542527745</v>
       </c>
       <c r="Y7">
-        <v>0.2344024338096493</v>
+        <v>0.5269751246641334</v>
       </c>
       <c r="Z7">
-        <v>0.0132214072590546</v>
+        <v>0.04882472535627785</v>
       </c>
       <c r="AA7">
-        <v>0.2515123569953024</v>
+        <v>0.3017464291168656</v>
       </c>
       <c r="AB7">
-        <v>1.035524265244163</v>
+        <v>0.7593117840358968</v>
       </c>
       <c r="AC7">
-        <v>90.78980016577228</v>
+        <v>87.16674245626311</v>
       </c>
       <c r="AD7" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1480,25 +1480,25 @@
         <v>90</v>
       </c>
       <c r="C8">
-        <v>1.128</v>
+        <v>1.076</v>
       </c>
       <c r="D8">
-        <v>1.252</v>
+        <v>1.236</v>
       </c>
       <c r="E8">
-        <v>1.026071324842432</v>
+        <v>0.966548112280941</v>
       </c>
       <c r="F8">
         <v>1.4</v>
       </c>
       <c r="G8">
-        <v>1.187847653455815</v>
+        <v>1.153222778652665</v>
       </c>
       <c r="J8" t="s">
         <v>94</v>
       </c>
       <c r="K8">
-        <v>1.026071324842432</v>
+        <v>0.966548112280941</v>
       </c>
       <c r="L8">
         <v>0.8200692764238203</v>
@@ -1513,10 +1513,10 @@
         <v>118</v>
       </c>
       <c r="P8">
-        <v>1.036948324347409</v>
+        <v>0.9850884312991284</v>
       </c>
       <c r="Q8">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -1525,34 +1525,34 @@
         <v>119</v>
       </c>
       <c r="T8">
-        <v>0.01087699950497645</v>
+        <v>0.01854031901818742</v>
       </c>
       <c r="U8">
-        <v>-0.03694832434740891</v>
+        <v>0.01491156870087162</v>
       </c>
       <c r="V8" t="s">
         <v>96</v>
       </c>
       <c r="W8">
-        <v>1.187847653455815</v>
+        <v>1.153222778652665</v>
       </c>
       <c r="X8">
-        <v>0.1617763286133824</v>
+        <v>0.1866746663717236</v>
       </c>
       <c r="Y8">
-        <v>0.02607132484243246</v>
+        <v>0.03345188771905905</v>
       </c>
       <c r="Z8">
-        <v>0.1972715394470829</v>
+        <v>0.2276328009577183</v>
       </c>
       <c r="AA8">
-        <v>0.03179161272340916</v>
+        <v>0.04079153881357063</v>
       </c>
       <c r="AB8">
         <v>0.7455175240216548</v>
       </c>
       <c r="AC8">
-        <v>86.99204005901876</v>
+        <v>85.02385182059285</v>
       </c>
       <c r="AD8" t="s">
         <v>78</v>
@@ -1566,25 +1566,25 @@
         <v>90</v>
       </c>
       <c r="C9">
-        <v>5.304</v>
+        <v>5.384</v>
       </c>
       <c r="D9">
-        <v>4.316</v>
+        <v>4.436</v>
       </c>
       <c r="E9">
-        <v>4.035405960595082</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="F9">
         <v>4.4</v>
       </c>
       <c r="G9">
-        <v>4.827149341819798</v>
+        <v>4.926455036482963</v>
       </c>
       <c r="J9" t="s">
         <v>94</v>
       </c>
       <c r="K9">
-        <v>4.035405960595082</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="L9">
         <v>2.858585552684069</v>
@@ -1599,10 +1599,10 @@
         <v>118</v>
       </c>
       <c r="P9">
-        <v>3.994458620063688</v>
+        <v>4.212305297947762</v>
       </c>
       <c r="Q9">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R9">
         <v>4</v>
@@ -1611,34 +1611,34 @@
         <v>119</v>
       </c>
       <c r="T9">
-        <v>-0.04094734053139382</v>
+        <v>-0.07747785760363346</v>
       </c>
       <c r="U9">
-        <v>0.005541379936312207</v>
+        <v>-0.2123052979477622</v>
       </c>
       <c r="V9" t="s">
         <v>96</v>
       </c>
       <c r="W9">
-        <v>4.827149341819798</v>
+        <v>4.926455036482963</v>
       </c>
       <c r="X9">
-        <v>0.7917433812247161</v>
+        <v>0.6366718809315675</v>
       </c>
       <c r="Y9">
-        <v>0.03540596059508161</v>
+        <v>0.2897831555513957</v>
       </c>
       <c r="Z9">
-        <v>0.2769703290780675</v>
+        <v>0.2227226959619118</v>
       </c>
       <c r="AA9">
-        <v>0.01238583206363622</v>
+        <v>0.1013729168536879</v>
       </c>
       <c r="AB9">
         <v>0.6972159884595291</v>
       </c>
       <c r="AC9">
-        <v>83.16315746844765</v>
+        <v>83.50611917578671</v>
       </c>
       <c r="AD9" t="s">
         <v>78</v>
@@ -1646,85 +1646,85 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10">
-        <v>3.692</v>
+        <v>0.6</v>
       </c>
       <c r="D10">
-        <v>3.192</v>
+        <v>0.696</v>
       </c>
       <c r="E10">
-        <v>3.475459163737268</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="G10">
-        <v>3.450678816710424</v>
+        <v>0.6451224071145452</v>
       </c>
       <c r="J10" t="s">
         <v>94</v>
       </c>
       <c r="K10">
-        <v>3.475459163737268</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="L10">
-        <v>0.887818750560327</v>
+        <v>1.559831022862906</v>
       </c>
       <c r="M10">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N10">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="s">
         <v>118</v>
       </c>
       <c r="P10">
-        <v>3.440193613933819</v>
+        <v>0.2767323416308665</v>
       </c>
       <c r="Q10">
-        <v>0.9898529811049405</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="s">
         <v>119</v>
       </c>
       <c r="T10">
-        <v>-0.03526554980344976</v>
+        <v>-0.04729480830888999</v>
       </c>
       <c r="U10">
-        <v>-0.4401936139338187</v>
+        <v>-0.2767323416308665</v>
       </c>
       <c r="V10" t="s">
         <v>96</v>
       </c>
       <c r="W10">
-        <v>3.450678816710424</v>
+        <v>0.6451224071145452</v>
       </c>
       <c r="X10">
-        <v>0.0247803470268444</v>
+        <v>0.3210952571747887</v>
       </c>
       <c r="Y10">
-        <v>0.4754591637372685</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="Z10">
-        <v>0.02791149320872625</v>
+        <v>0.2058525907411766</v>
       </c>
       <c r="AA10">
-        <v>0.5355362943587225</v>
+        <v>0.207732212778432</v>
       </c>
       <c r="AB10">
-        <v>0.3551275002241308</v>
+        <v>1.299859185719089</v>
       </c>
       <c r="AC10">
-        <v>81.41748166151876</v>
+        <v>81.34177543201334</v>
       </c>
       <c r="AD10" t="s">
         <v>78</v>
@@ -1732,85 +1732,85 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
         <v>90</v>
       </c>
       <c r="C11">
-        <v>3.184</v>
+        <v>3.784</v>
       </c>
       <c r="D11">
-        <v>4.004</v>
+        <v>3.252</v>
       </c>
       <c r="E11">
-        <v>1.550377686812013</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="F11">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>3.579766740594905</v>
+        <v>3.527234260979891</v>
       </c>
       <c r="J11" t="s">
         <v>94</v>
       </c>
       <c r="K11">
-        <v>1.550377686812013</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="L11">
-        <v>7.059923274159115</v>
+        <v>0.887818750560327</v>
       </c>
       <c r="M11">
         <v>5.24749619700716</v>
       </c>
       <c r="N11">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="s">
         <v>118</v>
       </c>
       <c r="P11">
-        <v>1.566812662552681</v>
+        <v>3.590592119879259</v>
       </c>
       <c r="Q11">
-        <v>1.010600627112006</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S11" t="s">
         <v>119</v>
       </c>
       <c r="T11">
-        <v>0.01643497574066832</v>
+        <v>-0.06604255040874341</v>
       </c>
       <c r="U11">
-        <v>0.433187337447319</v>
+        <v>0.409407880120741</v>
       </c>
       <c r="V11" t="s">
         <v>96</v>
       </c>
       <c r="W11">
-        <v>3.579766740594905</v>
+        <v>3.527234260979891</v>
       </c>
       <c r="X11">
-        <v>2.029389053782892</v>
+        <v>0.1294004093081114</v>
       </c>
       <c r="Y11">
-        <v>0.4496223131879873</v>
+        <v>0.3433653297119976</v>
       </c>
       <c r="Z11">
-        <v>0.2874519984106493</v>
+        <v>0.1457509308363258</v>
       </c>
       <c r="AA11">
-        <v>0.06368657218042365</v>
+        <v>0.3867516083607045</v>
       </c>
       <c r="AB11">
-        <v>0.9289372729156731</v>
+        <v>0.3551275002241308</v>
       </c>
       <c r="AC11">
-        <v>81.12864354622022</v>
+        <v>79.44532252176565</v>
       </c>
       <c r="AD11" t="s">
         <v>78</v>
@@ -1818,85 +1818,85 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C12">
-        <v>0.612</v>
+        <v>7.772</v>
       </c>
       <c r="D12">
-        <v>0.732</v>
+        <v>8.804</v>
       </c>
       <c r="E12">
-        <v>0.3293773794100608</v>
+        <v>9.770258645592461</v>
       </c>
       <c r="F12">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="G12">
-        <v>0.6684030088931816</v>
+        <v>8.270086922309687</v>
       </c>
       <c r="J12" t="s">
         <v>94</v>
       </c>
       <c r="K12">
-        <v>0.3293773794100608</v>
+        <v>9.770258645592461</v>
       </c>
       <c r="L12">
-        <v>1.559831022862906</v>
+        <v>4.467028425282805</v>
       </c>
       <c r="M12">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N12">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="O12" t="s">
         <v>118</v>
       </c>
       <c r="P12">
-        <v>0.2835868085528425</v>
+        <v>9.957671677471454</v>
       </c>
       <c r="Q12">
-        <v>0.8609783982760665</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S12" t="s">
         <v>119</v>
       </c>
       <c r="T12">
-        <v>-0.04579057085721838</v>
+        <v>0.1874130318789931</v>
       </c>
       <c r="U12">
-        <v>-0.2835868085528425</v>
+        <v>0.04232832252854557</v>
       </c>
       <c r="V12" t="s">
         <v>96</v>
       </c>
       <c r="W12">
-        <v>0.6684030088931816</v>
+        <v>8.270086922309687</v>
       </c>
       <c r="X12">
-        <v>0.3390256294831208</v>
+        <v>1.500171723282774</v>
       </c>
       <c r="Y12">
-        <v>0.3293773794100608</v>
+        <v>0.2297413544075386</v>
       </c>
       <c r="Z12">
-        <v>0.2173476642751179</v>
+        <v>0.3358321417414752</v>
       </c>
       <c r="AA12">
-        <v>0.2111622185879616</v>
+        <v>0.05143046619252122</v>
       </c>
       <c r="AB12">
-        <v>1.299859185719089</v>
+        <v>0.911638454139348</v>
       </c>
       <c r="AC12">
-        <v>80.63940515159102</v>
+        <v>78.9550442756191</v>
       </c>
       <c r="AD12" t="s">
         <v>78</v>
@@ -1904,85 +1904,85 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
         <v>90</v>
       </c>
       <c r="C13">
-        <v>172.984</v>
+        <v>2.824</v>
       </c>
       <c r="D13">
-        <v>170.488</v>
+        <v>3.956</v>
       </c>
       <c r="E13">
-        <v>172.6467820636017</v>
+        <v>0.8437214709471421</v>
       </c>
       <c r="F13">
-        <v>169.2</v>
+        <v>5.8</v>
       </c>
       <c r="G13">
-        <v>171.7793246530184</v>
+        <v>3.370351158967601</v>
       </c>
       <c r="J13" t="s">
         <v>94</v>
       </c>
       <c r="K13">
-        <v>172.6467820636017</v>
+        <v>0.8437214709471421</v>
       </c>
       <c r="L13">
-        <v>4.764861070548267</v>
+        <v>7.059923274159115</v>
       </c>
       <c r="M13">
         <v>5.24749619700716</v>
       </c>
       <c r="N13">
-        <v>13.2</v>
+        <v>7.6</v>
       </c>
       <c r="O13" t="s">
         <v>118</v>
       </c>
       <c r="P13">
-        <v>174.4769462223457</v>
+        <v>0.8599057302044893</v>
       </c>
       <c r="Q13">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R13">
-        <v>174</v>
+        <v>1</v>
       </c>
       <c r="S13" t="s">
         <v>119</v>
       </c>
       <c r="T13">
-        <v>1.830164158743969</v>
+        <v>0.01618425925734723</v>
       </c>
       <c r="U13">
-        <v>-0.4769462223457026</v>
+        <v>0.1400942697955107</v>
       </c>
       <c r="V13" t="s">
         <v>96</v>
       </c>
       <c r="W13">
-        <v>171.7793246530184</v>
+        <v>3.370351158967601</v>
       </c>
       <c r="X13">
-        <v>0.8674574105832846</v>
+        <v>2.526629688020459</v>
       </c>
       <c r="Y13">
-        <v>1.353217936398266</v>
+        <v>0.1562785290528579</v>
       </c>
       <c r="Z13">
-        <v>0.1820530331818197</v>
+        <v>0.3578834485735112</v>
       </c>
       <c r="AA13">
-        <v>0.2839994527358924</v>
+        <v>0.02213600955478822</v>
       </c>
       <c r="AB13">
-        <v>0.3609743235263839</v>
+        <v>0.9289372729156731</v>
       </c>
       <c r="AC13">
-        <v>80.43391422492162</v>
+        <v>78.63354118711212</v>
       </c>
       <c r="AD13" t="s">
         <v>78</v>
@@ -1996,25 +1996,25 @@
         <v>90</v>
       </c>
       <c r="C14">
-        <v>3.948</v>
+        <v>3.444</v>
       </c>
       <c r="D14">
-        <v>4.92</v>
+        <v>4.86</v>
       </c>
       <c r="E14">
-        <v>1.16567981478854</v>
+        <v>0.2404700937671027</v>
       </c>
       <c r="F14">
         <v>7.4</v>
       </c>
       <c r="G14">
-        <v>4.417128380314937</v>
+        <v>4.127421591076081</v>
       </c>
       <c r="J14" t="s">
         <v>94</v>
       </c>
       <c r="K14">
-        <v>1.16567981478854</v>
+        <v>0.2404700937671027</v>
       </c>
       <c r="L14">
         <v>9.933150479214353</v>
@@ -2029,46 +2029,46 @@
         <v>118</v>
       </c>
       <c r="P14">
-        <v>1.178036751837105</v>
+        <v>0.2450827893961431</v>
       </c>
       <c r="Q14">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="s">
         <v>119</v>
       </c>
       <c r="T14">
-        <v>0.01235693704856522</v>
+        <v>0.004612695629040375</v>
       </c>
       <c r="U14">
-        <v>-0.1780367518371049</v>
+        <v>-0.2450827893961431</v>
       </c>
       <c r="V14" t="s">
         <v>96</v>
       </c>
       <c r="W14">
-        <v>4.417128380314937</v>
+        <v>4.127421591076081</v>
       </c>
       <c r="X14">
-        <v>3.251448565526397</v>
+        <v>3.886951497308978</v>
       </c>
       <c r="Y14">
-        <v>0.1656798147885397</v>
+        <v>0.2404700937671027</v>
       </c>
       <c r="Z14">
-        <v>0.3273330623884362</v>
+        <v>0.3913110453166527</v>
       </c>
       <c r="AA14">
-        <v>0.01667948302356171</v>
+        <v>0.02420884434100734</v>
       </c>
       <c r="AB14">
         <v>0.9643835416712964</v>
       </c>
       <c r="AC14">
-        <v>80.36396477336831</v>
+        <v>76.8876227493331</v>
       </c>
       <c r="AD14" t="s">
         <v>78</v>
@@ -2076,85 +2076,85 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
         <v>90</v>
       </c>
       <c r="C15">
-        <v>7.968</v>
+        <v>7.492</v>
       </c>
       <c r="D15">
-        <v>8.868</v>
+        <v>5.94</v>
       </c>
       <c r="E15">
-        <v>10.0582691946606</v>
+        <v>5.212253933741241</v>
       </c>
       <c r="F15">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="G15">
-        <v>8.402378129921239</v>
+        <v>6.742939047069155</v>
       </c>
       <c r="J15" t="s">
         <v>94</v>
       </c>
       <c r="K15">
-        <v>10.0582691946606</v>
+        <v>5.212253933741241</v>
       </c>
       <c r="L15">
-        <v>4.467028425282805</v>
+        <v>3.997862832988686</v>
       </c>
       <c r="M15">
         <v>5.24749619700716</v>
       </c>
       <c r="N15">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
       <c r="O15" t="s">
         <v>118</v>
       </c>
       <c r="P15">
-        <v>10.16489315578537</v>
+        <v>5.11811531334273</v>
       </c>
       <c r="Q15">
-        <v>1.010600627112006</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S15" t="s">
         <v>119</v>
       </c>
       <c r="T15">
-        <v>0.1066239611247735</v>
+        <v>-0.09413862039851129</v>
       </c>
       <c r="U15">
-        <v>-0.1648931557853732</v>
+        <v>-0.11811531334273</v>
       </c>
       <c r="V15" t="s">
         <v>96</v>
       </c>
       <c r="W15">
-        <v>8.402378129921239</v>
+        <v>6.742939047069155</v>
       </c>
       <c r="X15">
-        <v>1.655891064739361</v>
+        <v>1.530685113327914</v>
       </c>
       <c r="Y15">
-        <v>0.05826919466059977</v>
+        <v>0.2122539337412412</v>
       </c>
       <c r="Z15">
-        <v>0.3706918575595425</v>
+        <v>0.382875845738714</v>
       </c>
       <c r="AA15">
-        <v>0.01304428562191448</v>
+        <v>0.05309184997289323</v>
       </c>
       <c r="AB15">
-        <v>0.911638454139348</v>
+        <v>0.5966959452221919</v>
       </c>
       <c r="AC15">
-        <v>78.23013869485108</v>
+        <v>76.53274884974184</v>
       </c>
       <c r="AD15" t="s">
         <v>78</v>
@@ -2162,49 +2162,49 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
       </c>
       <c r="C16">
-        <v>0.632</v>
+        <v>1.92</v>
       </c>
       <c r="D16">
-        <v>0.416</v>
+        <v>1.584</v>
       </c>
       <c r="E16">
-        <v>0.6558051063869967</v>
+        <v>1.52157415011752</v>
       </c>
       <c r="F16">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="G16">
-        <v>0.530474583992273</v>
+        <v>1.762071575099091</v>
       </c>
       <c r="J16" t="s">
         <v>94</v>
       </c>
       <c r="K16">
-        <v>0.6558051063869967</v>
+        <v>1.52157415011752</v>
       </c>
       <c r="L16">
-        <v>0.7620693762924241</v>
+        <v>1.157976831184469</v>
       </c>
       <c r="M16">
         <v>1.038416113387647</v>
       </c>
       <c r="N16">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="s">
         <v>118</v>
       </c>
       <c r="P16">
-        <v>0.7484613503089816</v>
+        <v>1.299486100486649</v>
       </c>
       <c r="Q16">
-        <v>1.141286249557361</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -2213,37 +2213,37 @@
         <v>119</v>
       </c>
       <c r="T16">
-        <v>0.0926562439219849</v>
+        <v>-0.2220880496308713</v>
       </c>
       <c r="U16">
-        <v>0.2515386496910184</v>
+        <v>-0.2994861004866491</v>
       </c>
       <c r="V16" t="s">
         <v>96</v>
       </c>
       <c r="W16">
-        <v>0.530474583992273</v>
+        <v>1.762071575099091</v>
       </c>
       <c r="X16">
-        <v>0.1253305223947238</v>
+        <v>0.2404974249815708</v>
       </c>
       <c r="Y16">
-        <v>0.3441948936130033</v>
+        <v>0.5215741501175204</v>
       </c>
       <c r="Z16">
-        <v>0.1644607778421363</v>
+        <v>0.2076875965951506</v>
       </c>
       <c r="AA16">
-        <v>0.4516582142265844</v>
+        <v>0.4504184678583023</v>
       </c>
       <c r="AB16">
-        <v>0.95258672036553</v>
+        <v>0.8271263079889064</v>
       </c>
       <c r="AC16">
-        <v>76.72213858724069</v>
+        <v>74.62882184844142</v>
       </c>
       <c r="AD16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2356,31 +2356,31 @@
         <v>75</v>
       </c>
       <c r="C2">
-        <v>0.4686639999999987</v>
+        <v>0.4674799999999988</v>
       </c>
       <c r="D2">
-        <v>0.4831359999999993</v>
+        <v>0.4820999999999993</v>
       </c>
       <c r="E2">
-        <v>0.4848653204771308</v>
+        <v>0.4816348617949026</v>
       </c>
       <c r="F2">
         <v>0.484</v>
       </c>
       <c r="G2">
-        <v>0.4749155896970425</v>
+        <v>0.473795522482778</v>
       </c>
       <c r="H2">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="I2">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="J2" t="s">
         <v>97</v>
       </c>
       <c r="K2">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="L2">
         <v>0.01064148394560983</v>
@@ -2395,13 +2395,13 @@
         <v>118</v>
       </c>
       <c r="P2">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="S2" t="s">
         <v>124</v>
@@ -2416,16 +2416,16 @@
         <v>96</v>
       </c>
       <c r="W2">
-        <v>0.4749155896970425</v>
+        <v>0.473795522482778</v>
       </c>
       <c r="X2">
-        <v>0.02479748585957076</v>
+        <v>0.02656335899988149</v>
       </c>
       <c r="Y2">
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>2.330265777434267</v>
+        <v>2.496208154393755</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>0.2764021804054501</v>
       </c>
       <c r="AC2">
-        <v>21.98801276749871</v>
+        <v>19.73976019256996</v>
       </c>
       <c r="AD2" t="s">
         <v>77</v>
@@ -2448,31 +2448,31 @@
         <v>75</v>
       </c>
       <c r="C3">
-        <v>0.5025559999999998</v>
+        <v>0.5035359999999998</v>
       </c>
       <c r="D3">
-        <v>0.4879279999999993</v>
+        <v>0.4889879999999993</v>
       </c>
       <c r="E3">
-        <v>0.4850537176443364</v>
+        <v>0.4880998606769701</v>
       </c>
       <c r="F3">
         <v>0.4868</v>
       </c>
       <c r="G3">
-        <v>0.4962370216909646</v>
+        <v>0.4972515799535244</v>
       </c>
       <c r="H3">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="I3">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="J3" t="s">
         <v>97</v>
       </c>
       <c r="K3">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="L3">
         <v>0.01323492690170848</v>
@@ -2487,13 +2487,13 @@
         <v>118</v>
       </c>
       <c r="P3">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
       <c r="R3">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="S3" t="s">
         <v>124</v>
@@ -2508,16 +2508,16 @@
         <v>96</v>
       </c>
       <c r="W3">
-        <v>0.4962370216909646</v>
+        <v>0.4972515799535244</v>
       </c>
       <c r="X3">
-        <v>0.02444487447156363</v>
+        <v>0.02631625656357905</v>
       </c>
       <c r="Y3">
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>1.8469973165026</v>
+        <v>1.988394553216756</v>
       </c>
       <c r="AA3">
         <v>0</v>
@@ -2526,7 +2526,7 @@
         <v>0.317384338170467</v>
       </c>
       <c r="AC3">
-        <v>30.10291257195357</v>
+        <v>27.45954213735271</v>
       </c>
       <c r="AD3" t="s">
         <v>77</v>
@@ -2540,25 +2540,25 @@
         <v>91</v>
       </c>
       <c r="C4">
-        <v>0.164</v>
+        <v>0.18</v>
       </c>
       <c r="D4">
-        <v>0.268</v>
+        <v>0.264</v>
       </c>
       <c r="E4">
-        <v>0.6905082799680116</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="F4">
         <v>0.2</v>
       </c>
       <c r="G4">
-        <v>0.2128826077074241</v>
+        <v>0.2194821062252271</v>
       </c>
       <c r="J4" t="s">
         <v>94</v>
       </c>
       <c r="K4">
-        <v>0.6905082799680116</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="L4">
         <v>0.4925498319332764</v>
@@ -2573,10 +2573,10 @@
         <v>118</v>
       </c>
       <c r="P4">
-        <v>0.7880676051329962</v>
+        <v>0.7802977676584159</v>
       </c>
       <c r="Q4">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -2585,34 +2585,34 @@
         <v>119</v>
       </c>
       <c r="T4">
-        <v>0.09755932516498467</v>
+        <v>0.101489785235631</v>
       </c>
       <c r="U4">
-        <v>0.2119323948670038</v>
+        <v>0.2197022323415841</v>
       </c>
       <c r="V4" t="s">
         <v>96</v>
       </c>
       <c r="W4">
-        <v>0.2128826077074241</v>
+        <v>0.2194821062252271</v>
       </c>
       <c r="X4">
-        <v>0.4776256722605874</v>
+        <v>0.4593258761975577</v>
       </c>
       <c r="Y4">
-        <v>0.3094917200319884</v>
+        <v>0.3211920175772152</v>
       </c>
       <c r="Z4">
-        <v>0.9697002035020272</v>
+        <v>0.9325470163997145</v>
       </c>
       <c r="AA4">
-        <v>0.6283460067730039</v>
+        <v>0.6521005525806892</v>
       </c>
       <c r="AB4">
         <v>1.231374579833191</v>
       </c>
       <c r="AC4">
-        <v>42.73182468197061</v>
+        <v>43.41388982372007</v>
       </c>
       <c r="AD4" t="s">
         <v>120</v>
@@ -2626,25 +2626,25 @@
         <v>91</v>
       </c>
       <c r="C5">
-        <v>10.028</v>
+        <v>9.932</v>
       </c>
       <c r="D5">
-        <v>11.468</v>
+        <v>11.352</v>
       </c>
       <c r="E5">
-        <v>13.28203815275881</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="F5">
         <v>11.6</v>
       </c>
       <c r="G5">
-        <v>10.70483610671818</v>
+        <v>10.59943560523598</v>
       </c>
       <c r="J5" t="s">
         <v>94</v>
       </c>
       <c r="K5">
-        <v>13.28203815275881</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="L5">
         <v>3.050242274051084</v>
@@ -2659,10 +2659,10 @@
         <v>118</v>
       </c>
       <c r="P5">
-        <v>15.15860750983988</v>
+        <v>14.78818442768141</v>
       </c>
       <c r="Q5">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R5">
         <v>15</v>
@@ -2671,34 +2671,34 @@
         <v>119</v>
       </c>
       <c r="T5">
-        <v>1.876569357081072</v>
+        <v>1.923431956103332</v>
       </c>
       <c r="U5">
-        <v>-0.158607509839884</v>
+        <v>0.2118155723185868</v>
       </c>
       <c r="V5" t="s">
         <v>96</v>
       </c>
       <c r="W5">
-        <v>10.70483610671818</v>
+        <v>10.59943560523598</v>
       </c>
       <c r="X5">
-        <v>2.577202046040632</v>
+        <v>2.265316866342099</v>
       </c>
       <c r="Y5">
-        <v>1.717961847241188</v>
+        <v>2.135247528421919</v>
       </c>
       <c r="Z5">
-        <v>0.8449171621432557</v>
+        <v>0.7426678482602922</v>
       </c>
       <c r="AA5">
-        <v>0.5632214404266095</v>
+        <v>0.7000255509494521</v>
       </c>
       <c r="AB5">
         <v>0.544686120366265</v>
       </c>
       <c r="AC5">
-        <v>47.41063290551929</v>
+        <v>48.29978656895716</v>
       </c>
       <c r="AD5" t="s">
         <v>120</v>
@@ -2712,25 +2712,25 @@
         <v>91</v>
       </c>
       <c r="C6">
-        <v>1.736</v>
+        <v>1.604</v>
       </c>
       <c r="D6">
-        <v>1.98</v>
+        <v>1.924</v>
       </c>
       <c r="E6">
-        <v>0.06755162617559574</v>
+        <v>-0.1313628720128142</v>
       </c>
       <c r="F6">
         <v>2.4</v>
       </c>
       <c r="G6">
-        <v>1.850686118082802</v>
+        <v>1.754408023715151</v>
       </c>
       <c r="J6" t="s">
         <v>94</v>
       </c>
       <c r="K6">
-        <v>0.06755162617559574</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>1.736334852416627</v>
@@ -2745,10 +2745,10 @@
         <v>118</v>
       </c>
       <c r="P6">
-        <v>0.05816049090560802</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2757,34 +2757,34 @@
         <v>119</v>
       </c>
       <c r="T6">
-        <v>-0.009391135269987715</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>-0.05816049090560802</v>
+        <v>0</v>
       </c>
       <c r="V6" t="s">
         <v>96</v>
       </c>
       <c r="W6">
-        <v>1.850686118082802</v>
+        <v>1.754408023715151</v>
       </c>
       <c r="X6">
-        <v>1.783134491907207</v>
+        <v>1.754408023715151</v>
       </c>
       <c r="Y6">
-        <v>0.06755162617559574</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.026953118763609</v>
+        <v>1.010408805233259</v>
       </c>
       <c r="AA6">
-        <v>0.03890472283130038</v>
+        <v>0</v>
       </c>
       <c r="AB6">
         <v>0.5601080169085895</v>
       </c>
       <c r="AC6">
-        <v>50.60417110498163</v>
+        <v>51.85256808577751</v>
       </c>
       <c r="AD6" t="s">
         <v>120</v>
@@ -2798,25 +2798,25 @@
         <v>91</v>
       </c>
       <c r="C7">
-        <v>13.232</v>
+        <v>13.288</v>
       </c>
       <c r="D7">
-        <v>12.328</v>
+        <v>12.416</v>
       </c>
       <c r="E7">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="F7">
         <v>12.4</v>
       </c>
       <c r="G7">
-        <v>12.8070973330047</v>
+        <v>12.87813813537621</v>
       </c>
       <c r="J7" t="s">
         <v>94</v>
       </c>
       <c r="K7">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="L7">
         <v>2.351026032651849</v>
@@ -2831,10 +2831,10 @@
         <v>118</v>
       </c>
       <c r="P7">
-        <v>9.674452691001546</v>
+        <v>9.779145216252848</v>
       </c>
       <c r="Q7">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -2843,34 +2843,34 @@
         <v>119</v>
       </c>
       <c r="T7">
-        <v>-1.562127356038731</v>
+        <v>-1.671300129583011</v>
       </c>
       <c r="U7">
-        <v>0.3255473089984537</v>
+        <v>0.2208547837471517</v>
       </c>
       <c r="V7" t="s">
         <v>96</v>
       </c>
       <c r="W7">
-        <v>12.8070973330047</v>
+        <v>12.87813813537621</v>
       </c>
       <c r="X7">
-        <v>1.570517285964419</v>
+        <v>1.427692789540352</v>
       </c>
       <c r="Y7">
-        <v>1.236580047040277</v>
+        <v>1.45044534583586</v>
       </c>
       <c r="Z7">
-        <v>0.6680135669076143</v>
+        <v>0.6072637094239147</v>
       </c>
       <c r="AA7">
-        <v>0.5259746297430284</v>
+        <v>0.6169414228900835</v>
       </c>
       <c r="AB7">
         <v>0.6530627868477359</v>
       </c>
       <c r="AC7">
-        <v>53.88597538332969</v>
+        <v>54.29973121083951</v>
       </c>
       <c r="AD7" t="s">
         <v>120</v>
@@ -2884,25 +2884,25 @@
         <v>90</v>
       </c>
       <c r="C8">
-        <v>13.58</v>
+        <v>13.548</v>
       </c>
       <c r="D8">
-        <v>14.788</v>
+        <v>14.728</v>
       </c>
       <c r="E8">
-        <v>19.01148659179185</v>
+        <v>18.83927196478475</v>
       </c>
       <c r="F8">
         <v>14.6</v>
       </c>
       <c r="G8">
-        <v>14.16303197882762</v>
+        <v>14.1175179925634</v>
       </c>
       <c r="J8" t="s">
         <v>94</v>
       </c>
       <c r="K8">
-        <v>19.01148659179185</v>
+        <v>18.83927196478475</v>
       </c>
       <c r="L8">
         <v>5.333756871724871</v>
@@ -2917,10 +2917,10 @@
         <v>118</v>
       </c>
       <c r="P8">
-        <v>19.21302027199633</v>
+        <v>19.20064674567716</v>
       </c>
       <c r="Q8">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R8">
         <v>19</v>
@@ -2929,34 +2929,34 @@
         <v>119</v>
       </c>
       <c r="T8">
-        <v>0.2015336802044807</v>
+        <v>0.3613747808924153</v>
       </c>
       <c r="U8">
-        <v>-0.2130202719963314</v>
+        <v>-0.2006467456771617</v>
       </c>
       <c r="V8" t="s">
         <v>96</v>
       </c>
       <c r="W8">
-        <v>14.16303197882762</v>
+        <v>14.1175179925634</v>
       </c>
       <c r="X8">
-        <v>4.848454612964233</v>
+        <v>4.721753972221347</v>
       </c>
       <c r="Y8">
-        <v>0.01148659179185074</v>
+        <v>0.1607280352152536</v>
       </c>
       <c r="Z8">
-        <v>0.909013052069676</v>
+        <v>0.8852585683558519</v>
       </c>
       <c r="AA8">
-        <v>0.00215356493895383</v>
+        <v>0.03013411354898824</v>
       </c>
       <c r="AB8">
         <v>1.088521810556096</v>
       </c>
       <c r="AC8">
-        <v>55.34343008256245</v>
+        <v>55.65685088619063</v>
       </c>
       <c r="AD8" t="s">
         <v>120</v>
@@ -2970,25 +2970,25 @@
         <v>91</v>
       </c>
       <c r="C9">
-        <v>1.084</v>
+        <v>1.12</v>
       </c>
       <c r="D9">
-        <v>1.172</v>
+        <v>1.168</v>
       </c>
       <c r="E9">
-        <v>1.761149755943273</v>
+        <v>1.780416614874208</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>1.125362206521666</v>
+        <v>1.142561203557273</v>
       </c>
       <c r="J9" t="s">
         <v>94</v>
       </c>
       <c r="K9">
-        <v>1.761149755943273</v>
+        <v>1.780416614874208</v>
       </c>
       <c r="L9">
         <v>0.8500971208676269</v>
@@ -3003,10 +3003,10 @@
         <v>118</v>
       </c>
       <c r="P9">
-        <v>2.00997599986936</v>
+        <v>2.046609860316908</v>
       </c>
       <c r="Q9">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R9">
         <v>2</v>
@@ -3015,34 +3015,34 @@
         <v>119</v>
       </c>
       <c r="T9">
-        <v>0.2488262439260871</v>
+        <v>0.2661932454427003</v>
       </c>
       <c r="U9">
-        <v>-0.009975999869360042</v>
+        <v>-0.04660986031690806</v>
       </c>
       <c r="V9" t="s">
         <v>96</v>
       </c>
       <c r="W9">
-        <v>1.125362206521666</v>
+        <v>1.142561203557273</v>
       </c>
       <c r="X9">
-        <v>0.6357875494216065</v>
+        <v>0.6378554113169352</v>
       </c>
       <c r="Y9">
-        <v>0.2388502440567271</v>
+        <v>0.2195833851257922</v>
       </c>
       <c r="Z9">
-        <v>0.7478998973349168</v>
+        <v>0.7503323980981451</v>
       </c>
       <c r="AA9">
-        <v>0.2809681837446426</v>
+        <v>0.2583038805044779</v>
       </c>
       <c r="AB9">
         <v>1.700194241735254</v>
       </c>
       <c r="AC9">
-        <v>55.73990894075605</v>
+        <v>56.09506097814787</v>
       </c>
       <c r="AD9" t="s">
         <v>120</v>
@@ -3056,25 +3056,25 @@
         <v>91</v>
       </c>
       <c r="C10">
-        <v>0.552</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D10">
-        <v>0.392</v>
+        <v>0.408</v>
       </c>
       <c r="E10">
-        <v>0.2703407362038964</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="F10">
         <v>0.4</v>
       </c>
       <c r="G10">
-        <v>0.4767959881424244</v>
+        <v>0.4885561887353032</v>
       </c>
       <c r="J10" t="s">
         <v>94</v>
       </c>
       <c r="K10">
-        <v>0.2703407362038964</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="L10">
         <v>0.3921195507989373</v>
@@ -3089,10 +3089,10 @@
         <v>118</v>
       </c>
       <c r="P10">
-        <v>0.3085361649247209</v>
+        <v>0.3618566504167141</v>
       </c>
       <c r="Q10">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3101,34 +3101,34 @@
         <v>119</v>
       </c>
       <c r="T10">
-        <v>0.03819542872082443</v>
+        <v>0.04706505036799469</v>
       </c>
       <c r="U10">
-        <v>-0.3085361649247209</v>
+        <v>-0.3618566504167141</v>
       </c>
       <c r="V10" t="s">
         <v>96</v>
       </c>
       <c r="W10">
-        <v>0.4767959881424244</v>
+        <v>0.4885561887353032</v>
       </c>
       <c r="X10">
-        <v>0.206455251938528</v>
+        <v>0.1737645886865837</v>
       </c>
       <c r="Y10">
-        <v>0.2703407362038964</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="Z10">
-        <v>0.526510987574781</v>
+        <v>0.4431418640884933</v>
       </c>
       <c r="AA10">
-        <v>0.6894344738819614</v>
+        <v>0.8027949624223952</v>
       </c>
       <c r="AB10">
         <v>0.6535325846648956</v>
       </c>
       <c r="AC10">
-        <v>55.79230620253968</v>
+        <v>56.60796713936882</v>
       </c>
       <c r="AD10" t="s">
         <v>120</v>
@@ -3142,25 +3142,25 @@
         <v>91</v>
       </c>
       <c r="C11">
-        <v>0.716</v>
+        <v>0.74</v>
       </c>
       <c r="D11">
-        <v>0.66</v>
+        <v>0.672</v>
       </c>
       <c r="E11">
-        <v>0.9608490161719081</v>
+        <v>0.9935995824715044</v>
       </c>
       <c r="F11">
         <v>0.6</v>
       </c>
       <c r="G11">
-        <v>0.6896785958498485</v>
+        <v>0.7080382949605304</v>
       </c>
       <c r="J11" t="s">
         <v>94</v>
       </c>
       <c r="K11">
-        <v>0.9608490161719081</v>
+        <v>0.9935995824715044</v>
       </c>
       <c r="L11">
         <v>0.3332002265469857</v>
@@ -3175,10 +3175,10 @@
         <v>118</v>
       </c>
       <c r="P11">
-        <v>1.096603770057717</v>
+        <v>1.14215441807513</v>
       </c>
       <c r="Q11">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -3187,34 +3187,34 @@
         <v>119</v>
       </c>
       <c r="T11">
-        <v>0.135754753885809</v>
+        <v>0.1485548356036258</v>
       </c>
       <c r="U11">
-        <v>-0.09660377005771714</v>
+        <v>-0.1421544180751302</v>
       </c>
       <c r="V11" t="s">
         <v>96</v>
       </c>
       <c r="W11">
-        <v>0.6896785958498485</v>
+        <v>0.7080382949605304</v>
       </c>
       <c r="X11">
-        <v>0.2711704203220596</v>
+        <v>0.285561287510974</v>
       </c>
       <c r="Y11">
-        <v>0.0391509838280919</v>
+        <v>0.006400417528495628</v>
       </c>
       <c r="Z11">
-        <v>0.813836242346675</v>
+        <v>0.8570260904990893</v>
       </c>
       <c r="AA11">
-        <v>0.1174998715751806</v>
+        <v>0.01920892309955583</v>
       </c>
       <c r="AB11">
         <v>0.5553337109116429</v>
       </c>
       <c r="AC11">
-        <v>56.54584207939454</v>
+        <v>56.90482321607101</v>
       </c>
       <c r="AD11" t="s">
         <v>120</v>
@@ -3228,25 +3228,25 @@
         <v>90</v>
       </c>
       <c r="C12">
-        <v>1.832</v>
+        <v>1.904</v>
       </c>
       <c r="D12">
-        <v>1.772</v>
+        <v>1.796</v>
       </c>
       <c r="E12">
-        <v>2.554644495322226</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="F12">
         <v>1.6</v>
       </c>
       <c r="G12">
-        <v>1.803041458005251</v>
+        <v>1.851874624409452</v>
       </c>
       <c r="J12" t="s">
         <v>94</v>
       </c>
       <c r="K12">
-        <v>2.554644495322226</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="L12">
         <v>1.198624596172324</v>
@@ -3261,46 +3261,46 @@
         <v>118</v>
       </c>
       <c r="P12">
-        <v>2.528722469358031</v>
+        <v>2.557215395085126</v>
       </c>
       <c r="Q12">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12" t="s">
         <v>119</v>
       </c>
       <c r="T12">
-        <v>-0.02592202596419435</v>
+        <v>-0.04703542507679881</v>
       </c>
       <c r="U12">
-        <v>-0.5287224693580312</v>
+        <v>0.4427846049148738</v>
       </c>
       <c r="V12" t="s">
         <v>96</v>
       </c>
       <c r="W12">
-        <v>1.803041458005251</v>
+        <v>1.851874624409452</v>
       </c>
       <c r="X12">
-        <v>0.7516030373169746</v>
+        <v>0.7523761957524733</v>
       </c>
       <c r="Y12">
-        <v>0.5546444953222256</v>
+        <v>0.395749179838075</v>
       </c>
       <c r="Z12">
-        <v>0.627054575483547</v>
+        <v>0.6276996135029299</v>
       </c>
       <c r="AA12">
-        <v>0.4627341179994319</v>
+        <v>0.3301694134275707</v>
       </c>
       <c r="AB12">
         <v>0.7491403726077025</v>
       </c>
       <c r="AC12">
-        <v>56.57842736664286</v>
+        <v>59.24054223283283</v>
       </c>
       <c r="AD12" t="s">
         <v>120</v>
@@ -3314,25 +3314,25 @@
         <v>90</v>
       </c>
       <c r="C13">
-        <v>8.612</v>
+        <v>8.763999999999999</v>
       </c>
       <c r="D13">
-        <v>6.564</v>
+        <v>6.752</v>
       </c>
       <c r="E13">
-        <v>3.808811132083866</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="F13">
         <v>6.6</v>
       </c>
       <c r="G13">
-        <v>7.623548433245896</v>
+        <v>7.792923558442745</v>
       </c>
       <c r="J13" t="s">
         <v>94</v>
       </c>
       <c r="K13">
-        <v>3.808811132083866</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="L13">
         <v>4.673523904256721</v>
@@ -3347,10 +3347,10 @@
         <v>118</v>
       </c>
       <c r="P13">
-        <v>3.770163053558897</v>
+        <v>4.224092654695784</v>
       </c>
       <c r="Q13">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R13">
         <v>4</v>
@@ -3359,120 +3359,120 @@
         <v>119</v>
       </c>
       <c r="T13">
-        <v>-0.03864807852496854</v>
+        <v>-0.07769466504826283</v>
       </c>
       <c r="U13">
-        <v>0.229836946441103</v>
+        <v>-0.2240926546957844</v>
       </c>
       <c r="V13" t="s">
         <v>96</v>
       </c>
       <c r="W13">
-        <v>7.623548433245896</v>
+        <v>7.792923558442745</v>
       </c>
       <c r="X13">
-        <v>3.81473730116203</v>
+        <v>3.491136238698697</v>
       </c>
       <c r="Y13">
-        <v>0.1911888679161344</v>
+        <v>0.3017873197440473</v>
       </c>
       <c r="Z13">
-        <v>0.816244311425797</v>
+        <v>0.747002970396474</v>
       </c>
       <c r="AA13">
-        <v>0.04090893121184135</v>
+        <v>0.06457382607354901</v>
       </c>
       <c r="AB13">
         <v>0.5563718933638954</v>
       </c>
       <c r="AC13">
-        <v>57.99131498158366</v>
+        <v>60.16058574846904</v>
       </c>
       <c r="AD13" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
         <v>90</v>
       </c>
       <c r="C14">
-        <v>3.54</v>
+        <v>173.496</v>
       </c>
       <c r="D14">
-        <v>4.812</v>
+        <v>170.784</v>
       </c>
       <c r="E14">
-        <v>5.586198698614951</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>169.2</v>
       </c>
       <c r="G14">
-        <v>4.153921090288683</v>
+        <v>172.1870739018374</v>
       </c>
       <c r="J14" t="s">
         <v>94</v>
       </c>
       <c r="K14">
-        <v>5.586198698614951</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="L14">
-        <v>2.262338789582505</v>
+        <v>4.764861070548267</v>
       </c>
       <c r="M14">
         <v>5.24749619700716</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>13.2</v>
       </c>
       <c r="O14" t="s">
         <v>118</v>
       </c>
       <c r="P14">
-        <v>5.645415907992541</v>
+        <v>176.9807039529099</v>
       </c>
       <c r="Q14">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R14">
-        <v>6</v>
+        <v>177</v>
       </c>
       <c r="S14" t="s">
         <v>119</v>
       </c>
       <c r="T14">
-        <v>0.05921720937758934</v>
+        <v>3.330948376911721</v>
       </c>
       <c r="U14">
-        <v>0.3545840920074594</v>
+        <v>0.01929604709013688</v>
       </c>
       <c r="V14" t="s">
         <v>96</v>
       </c>
       <c r="W14">
-        <v>4.153921090288683</v>
+        <v>172.1870739018374</v>
       </c>
       <c r="X14">
-        <v>1.432277608326268</v>
+        <v>1.462681674160791</v>
       </c>
       <c r="Y14">
-        <v>0.4138013013850488</v>
+        <v>3.350244424001858</v>
       </c>
       <c r="Z14">
-        <v>0.633095986737947</v>
+        <v>0.3069725753814032</v>
       </c>
       <c r="AA14">
-        <v>0.1829086356519627</v>
+        <v>0.7031148179135396</v>
       </c>
       <c r="AB14">
-        <v>0.452467757916501</v>
+        <v>0.3609743235263839</v>
       </c>
       <c r="AC14">
-        <v>62.15552874778314</v>
+        <v>64.04255765445993</v>
       </c>
       <c r="AD14" t="s">
         <v>79</v>
@@ -3486,19 +3486,19 @@
         <v>91</v>
       </c>
       <c r="C15">
-        <v>0.676</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="D15">
-        <v>0.612</v>
+        <v>0.608</v>
       </c>
       <c r="E15">
-        <v>-0.005331174175850051</v>
+        <v>-0.01550360442781762</v>
       </c>
       <c r="F15">
         <v>0.6</v>
       </c>
       <c r="G15">
-        <v>0.6459183952569697</v>
+        <v>0.6503979940712121</v>
       </c>
       <c r="J15" t="s">
         <v>94</v>
@@ -3522,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>96</v>
       </c>
       <c r="W15">
-        <v>0.6459183952569697</v>
+        <v>0.6503979940712121</v>
       </c>
       <c r="X15">
-        <v>0.6459183952569697</v>
+        <v>0.6503979940712121</v>
       </c>
       <c r="Y15">
         <v>0</v>
       </c>
       <c r="Z15">
-        <v>0.642420983273117</v>
+        <v>0.6468763266973739</v>
       </c>
       <c r="AA15">
         <v>0</v>
@@ -3558,7 +3558,7 @@
         <v>1.117160124789949</v>
       </c>
       <c r="AC15">
-        <v>65.86429881671735</v>
+        <v>65.67383349516004</v>
       </c>
       <c r="AD15" t="s">
         <v>79</v>
@@ -3572,25 +3572,25 @@
         <v>91</v>
       </c>
       <c r="C16">
-        <v>0.368</v>
+        <v>0.38</v>
       </c>
       <c r="D16">
-        <v>0.512</v>
+        <v>0.496</v>
       </c>
       <c r="E16">
-        <v>0.8003007397713651</v>
+        <v>0.7868170324027036</v>
       </c>
       <c r="F16">
         <v>0.4</v>
       </c>
       <c r="G16">
-        <v>0.4356836106718179</v>
+        <v>0.4345229085967423</v>
       </c>
       <c r="J16" t="s">
         <v>94</v>
       </c>
       <c r="K16">
-        <v>0.8003007397713651</v>
+        <v>0.7868170324027036</v>
       </c>
       <c r="L16">
         <v>0.8079772006265793</v>
@@ -3605,10 +3605,10 @@
         <v>118</v>
       </c>
       <c r="P16">
-        <v>0.689041649067501</v>
+        <v>0.6719736906377493</v>
       </c>
       <c r="Q16">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -3617,34 +3617,34 @@
         <v>119</v>
       </c>
       <c r="T16">
-        <v>-0.1112590907038641</v>
+        <v>-0.1148433417649544</v>
       </c>
       <c r="U16">
-        <v>0.310958350932499</v>
+        <v>0.3280263093622507</v>
       </c>
       <c r="V16" t="s">
         <v>96</v>
       </c>
       <c r="W16">
-        <v>0.4356836106718179</v>
+        <v>0.4345229085967423</v>
       </c>
       <c r="X16">
-        <v>0.3646171290995471</v>
+        <v>0.3522941238059614</v>
       </c>
       <c r="Y16">
-        <v>0.1996992602286349</v>
+        <v>0.2131829675972964</v>
       </c>
       <c r="Z16">
-        <v>0.4512715566934187</v>
+        <v>0.4360198821609822</v>
       </c>
       <c r="AA16">
-        <v>0.247159523899647</v>
+        <v>0.2638477514365193</v>
       </c>
       <c r="AB16">
         <v>1.346628667710966</v>
       </c>
       <c r="AC16">
-        <v>68.39760714610466</v>
+        <v>68.6767387081441</v>
       </c>
       <c r="AD16" t="s">
         <v>79</v>
@@ -3676,10 +3676,10 @@
         <v>18</v>
       </c>
       <c r="B2">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="C2">
-        <v>52.07</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3687,10 +3687,10 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="C3">
-        <v>45.01</v>
+        <v>44.72</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3698,7 +3698,7 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>0.0292</v>
+        <v>0.02920000000000006</v>
       </c>
       <c r="C4">
         <v>2.92</v>
@@ -3742,22 +3742,22 @@
         <v>33</v>
       </c>
       <c r="B2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3812,13 +3812,13 @@
         <v>39</v>
       </c>
       <c r="B2">
-        <v>1.026071324842432</v>
+        <v>0.966548112280941</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>-0.03694832434740891</v>
+        <v>0.01491156870087162</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3826,13 +3826,13 @@
         <v>40</v>
       </c>
       <c r="B3">
-        <v>1.699906626866217</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>0.2820732968571464</v>
+        <v>0.4987195719777766</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3840,13 +3840,13 @@
         <v>41</v>
       </c>
       <c r="B4">
-        <v>10.0582691946606</v>
+        <v>9.770258645592461</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4">
-        <v>-0.1648931557853732</v>
+        <v>0.04232832252854557</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3854,13 +3854,13 @@
         <v>42</v>
       </c>
       <c r="B5">
-        <v>5.586198698614951</v>
+        <v>5.170440884727479</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>0.3545840920074594</v>
+        <v>-0.269620245019544</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3868,13 +3868,13 @@
         <v>43</v>
       </c>
       <c r="B6">
-        <v>19.01148659179185</v>
+        <v>18.83927196478475</v>
       </c>
       <c r="C6">
         <v>19</v>
       </c>
       <c r="D6">
-        <v>-0.2130202719963314</v>
+        <v>-0.2006467456771617</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3882,13 +3882,13 @@
         <v>44</v>
       </c>
       <c r="B7">
-        <v>1.550377686812013</v>
+        <v>0.8437214709471421</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0.433187337447319</v>
+        <v>0.1400942697955107</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3896,13 +3896,13 @@
         <v>45</v>
       </c>
       <c r="B8">
-        <v>172.6467820636017</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="C8">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D8">
-        <v>-0.4769462223457026</v>
+        <v>0.01929604709013688</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3910,13 +3910,13 @@
         <v>46</v>
       </c>
       <c r="B9">
-        <v>1.16567981478854</v>
+        <v>0.2404700937671027</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>-0.1780367518371049</v>
+        <v>-0.2450827893961431</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3924,13 +3924,13 @@
         <v>47</v>
       </c>
       <c r="B10">
-        <v>3.475459163737268</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>-0.4401936139338187</v>
+        <v>0.409407880120741</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3938,13 +3938,13 @@
         <v>48</v>
       </c>
       <c r="B11">
-        <v>2.554644495322226</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>-0.5287224693580312</v>
+        <v>0.4427846049148738</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3952,13 +3952,13 @@
         <v>49</v>
       </c>
       <c r="B12">
-        <v>12.98388364583827</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="C12">
         <v>13</v>
       </c>
       <c r="D12">
-        <v>0.1478640668473066</v>
+        <v>-0.1147345811896248</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3966,13 +3966,13 @@
         <v>50</v>
       </c>
       <c r="B13">
-        <v>3.808811132083866</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="C13">
         <v>4</v>
       </c>
       <c r="D13">
-        <v>0.229836946441103</v>
+        <v>-0.2240926546957844</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3980,13 +3980,13 @@
         <v>51</v>
       </c>
       <c r="B14">
-        <v>15.00521451603779</v>
+        <v>15.0529980979447</v>
       </c>
       <c r="C14">
         <v>15</v>
       </c>
       <c r="D14">
-        <v>0.1470436791808698</v>
+        <v>0.2188743955707473</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3994,13 +3994,13 @@
         <v>52</v>
       </c>
       <c r="B15">
-        <v>4.801946011202828</v>
+        <v>5.212253933741241</v>
       </c>
       <c r="C15">
         <v>5</v>
       </c>
       <c r="D15">
-        <v>0.2467794257059026</v>
+        <v>-0.11811531334273</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4008,13 +4008,13 @@
         <v>53</v>
       </c>
       <c r="B16">
-        <v>175.5898630732044</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="C16">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D16">
-        <v>0.1918505851803616</v>
+        <v>-0.4018190334304563</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4022,13 +4022,13 @@
         <v>54</v>
       </c>
       <c r="B17">
-        <v>4.035405960595082</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="C17">
         <v>4</v>
       </c>
       <c r="D17">
-        <v>0.005541379936312207</v>
+        <v>-0.2123052979477622</v>
       </c>
     </row>
   </sheetData>
@@ -4060,13 +4060,13 @@
         <v>55</v>
       </c>
       <c r="B2">
-        <v>0.8003007397713651</v>
+        <v>0.7868170324027036</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.310958350932499</v>
+        <v>0.3280263093622507</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4088,13 +4088,13 @@
         <v>57</v>
       </c>
       <c r="B4">
-        <v>1.234402433809649</v>
+        <v>1.138895095514905</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>-0.06279383028951013</v>
+        <v>0.02733734900811324</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4102,13 +4102,13 @@
         <v>58</v>
       </c>
       <c r="B5">
-        <v>0.3293773794100608</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>-0.2835868085528425</v>
+        <v>-0.2767323416308665</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4116,13 +4116,13 @@
         <v>59</v>
       </c>
       <c r="B6">
-        <v>1.430889012604439</v>
+        <v>1.52157415011752</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>-0.2319645301829925</v>
+        <v>-0.2994861004866491</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4144,13 +4144,13 @@
         <v>61</v>
       </c>
       <c r="B8">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="C8">
         <v>10</v>
       </c>
       <c r="D8">
-        <v>0.3255473089984537</v>
+        <v>0.2208547837471517</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4158,13 +4158,13 @@
         <v>62</v>
       </c>
       <c r="B9">
-        <v>0.06755162617559574</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>-0.05816049090560802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4172,13 +4172,13 @@
         <v>63</v>
       </c>
       <c r="B10">
-        <v>0.6905082799680116</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>0.2119323948670038</v>
+        <v>0.2197022323415841</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4186,13 +4186,13 @@
         <v>64</v>
       </c>
       <c r="B11">
-        <v>0.6558051063869967</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.2515386496910184</v>
+        <v>0.1343074487636272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -4206,7 +4206,7 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>-0.141286249557361</v>
+        <v>-0.1495117733786751</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4214,13 +4214,13 @@
         <v>66</v>
       </c>
       <c r="B13">
-        <v>0.9608490161719081</v>
+        <v>0.9935995824715044</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>-0.09660377005771714</v>
+        <v>-0.1421544180751302</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4228,13 +4228,13 @@
         <v>67</v>
       </c>
       <c r="B14">
-        <v>1.761149755943273</v>
+        <v>1.780416614874208</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14">
-        <v>-0.009975999869360042</v>
+        <v>-0.04660986031690806</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4242,13 +4242,13 @@
         <v>68</v>
       </c>
       <c r="B15">
-        <v>0.2703407362038964</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>-0.3085361649247209</v>
+        <v>-0.3618566504167141</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4256,13 +4256,13 @@
         <v>69</v>
       </c>
       <c r="B16">
-        <v>13.28203815275881</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16">
-        <v>-0.158607509839884</v>
+        <v>0.2118155723185868</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4270,13 +4270,13 @@
         <v>70</v>
       </c>
       <c r="B17">
-        <v>0.6558051063869967</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>0.2515386496910184</v>
+        <v>0.1343074487636272</v>
       </c>
     </row>
   </sheetData>
@@ -4308,7 +4308,7 @@
         <v>75</v>
       </c>
       <c r="B2">
-        <v>26.045</v>
+        <v>23.6</v>
       </c>
       <c r="C2" t="s">
         <v>77</v>
@@ -4322,7 +4322,7 @@
         <v>33</v>
       </c>
       <c r="B3">
-        <v>78.65300000000001</v>
+        <v>77.158</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -4336,7 +4336,7 @@
         <v>34</v>
       </c>
       <c r="B4">
-        <v>66.76300000000001</v>
+        <v>66.666</v>
       </c>
       <c r="C4" t="s">
         <v>79</v>
@@ -4391,13 +4391,13 @@
         <v>90</v>
       </c>
       <c r="B2">
-        <v>78.65300000000001</v>
+        <v>77.158</v>
       </c>
       <c r="C2">
-        <v>1.479</v>
+        <v>1.549</v>
       </c>
       <c r="D2">
-        <v>0.365</v>
+        <v>0.65</v>
       </c>
       <c r="E2">
         <v>5.247</v>
@@ -4408,10 +4408,10 @@
         <v>75</v>
       </c>
       <c r="B3">
-        <v>26.045</v>
+        <v>23.6</v>
       </c>
       <c r="C3">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>91</v>
       </c>
       <c r="B4">
-        <v>66.76300000000001</v>
+        <v>66.666</v>
       </c>
       <c r="C4">
-        <v>0.603</v>
+        <v>0.582</v>
       </c>
       <c r="D4">
-        <v>0.36</v>
+        <v>0.384</v>
       </c>
       <c r="E4">
         <v>1.038</v>
@@ -4541,260 +4541,260 @@
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C2">
-        <v>10.028</v>
+        <v>171.868</v>
       </c>
       <c r="D2">
-        <v>11.468</v>
+        <v>174.552</v>
       </c>
       <c r="E2">
-        <v>13.28203815275881</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="F2">
-        <v>11.6</v>
+        <v>172.6</v>
       </c>
       <c r="G2">
-        <v>10.70483610671818</v>
+        <v>173.1634121118985</v>
       </c>
       <c r="J2" t="s">
         <v>94</v>
       </c>
       <c r="K2">
-        <v>13.28203815275881</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="L2">
-        <v>3.050242274051084</v>
+        <v>24.70132137894479</v>
       </c>
       <c r="M2">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N2">
-        <v>5.6</v>
+        <v>18.7</v>
       </c>
       <c r="O2" t="s">
         <v>118</v>
       </c>
       <c r="P2">
-        <v>15.15860750983988</v>
+        <v>172.4018190334305</v>
       </c>
       <c r="Q2">
-        <v>1.141286249557361</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R2">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="S2" t="s">
         <v>119</v>
       </c>
       <c r="T2">
-        <v>1.876569357081072</v>
+        <v>-3.171024567518231</v>
       </c>
       <c r="U2">
-        <v>-0.158607509839884</v>
+        <v>-0.4018190334304563</v>
       </c>
       <c r="V2" t="s">
         <v>96</v>
       </c>
       <c r="W2">
-        <v>10.70483610671818</v>
+        <v>173.1634121118985</v>
       </c>
       <c r="X2">
-        <v>2.577202046040632</v>
+        <v>2.409431489050235</v>
       </c>
       <c r="Y2">
-        <v>1.717961847241188</v>
+        <v>3.572843600948687</v>
       </c>
       <c r="Z2">
-        <v>0.8449171621432557</v>
+        <v>0.09754261531547112</v>
       </c>
       <c r="AA2">
-        <v>0.5632214404266095</v>
+        <v>0.1446418005797111</v>
       </c>
       <c r="AB2">
-        <v>0.544686120366265</v>
+        <v>1.320926276948919</v>
       </c>
       <c r="AC2">
-        <v>47.41063290551929</v>
+        <v>89.22335706647648</v>
       </c>
       <c r="AD2" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
         <v>90</v>
       </c>
       <c r="C3">
-        <v>172.1</v>
+        <v>173.496</v>
       </c>
       <c r="D3">
-        <v>175.156</v>
+        <v>170.784</v>
       </c>
       <c r="E3">
-        <v>175.5898630732044</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="F3">
-        <v>172.6</v>
+        <v>169.2</v>
       </c>
       <c r="G3">
-        <v>173.5749550722659</v>
+        <v>172.1870739018374</v>
       </c>
       <c r="J3" t="s">
         <v>94</v>
       </c>
       <c r="K3">
-        <v>175.5898630732044</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="L3">
-        <v>24.70132137894479</v>
+        <v>4.764861070548267</v>
       </c>
       <c r="M3">
         <v>5.24749619700716</v>
       </c>
       <c r="N3">
-        <v>18.7</v>
+        <v>13.2</v>
       </c>
       <c r="O3" t="s">
         <v>118</v>
       </c>
       <c r="P3">
-        <v>173.8081494148196</v>
+        <v>176.9807039529099</v>
       </c>
       <c r="Q3">
-        <v>0.9898529811049405</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="S3" t="s">
         <v>119</v>
       </c>
       <c r="T3">
-        <v>-1.781713658384717</v>
+        <v>3.330948376911721</v>
       </c>
       <c r="U3">
-        <v>0.1918505851803616</v>
+        <v>0.01929604709013688</v>
       </c>
       <c r="V3" t="s">
         <v>96</v>
       </c>
       <c r="W3">
-        <v>173.5749550722659</v>
+        <v>172.1870739018374</v>
       </c>
       <c r="X3">
-        <v>2.014908000938448</v>
+        <v>1.462681674160791</v>
       </c>
       <c r="Y3">
-        <v>1.589863073204356</v>
+        <v>3.350244424001858</v>
       </c>
       <c r="Z3">
-        <v>0.08157085890376452</v>
+        <v>0.3069725753814032</v>
       </c>
       <c r="AA3">
-        <v>0.06436348277948976</v>
+        <v>0.7031148179135396</v>
       </c>
       <c r="AB3">
-        <v>1.320926276948919</v>
+        <v>0.3609743235263839</v>
       </c>
       <c r="AC3">
-        <v>92.72349650896915</v>
+        <v>64.04255765445993</v>
       </c>
       <c r="AD3" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4">
-        <v>172.984</v>
+        <v>9.932</v>
       </c>
       <c r="D4">
-        <v>170.488</v>
+        <v>11.352</v>
       </c>
       <c r="E4">
-        <v>172.6467820636017</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="F4">
-        <v>169.2</v>
+        <v>11.6</v>
       </c>
       <c r="G4">
-        <v>171.7793246530184</v>
+        <v>10.59943560523598</v>
       </c>
       <c r="J4" t="s">
         <v>94</v>
       </c>
       <c r="K4">
-        <v>172.6467820636017</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="L4">
-        <v>4.764861070548267</v>
+        <v>3.050242274051084</v>
       </c>
       <c r="M4">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N4">
-        <v>13.2</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="s">
         <v>118</v>
       </c>
       <c r="P4">
-        <v>174.4769462223457</v>
+        <v>14.78818442768141</v>
       </c>
       <c r="Q4">
-        <v>1.010600627112006</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R4">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="S4" t="s">
         <v>119</v>
       </c>
       <c r="T4">
-        <v>1.830164158743969</v>
+        <v>1.923431956103332</v>
       </c>
       <c r="U4">
-        <v>-0.4769462223457026</v>
+        <v>0.2118155723185868</v>
       </c>
       <c r="V4" t="s">
         <v>96</v>
       </c>
       <c r="W4">
-        <v>171.7793246530184</v>
+        <v>10.59943560523598</v>
       </c>
       <c r="X4">
-        <v>0.8674574105832846</v>
+        <v>2.265316866342099</v>
       </c>
       <c r="Y4">
-        <v>1.353217936398266</v>
+        <v>2.135247528421919</v>
       </c>
       <c r="Z4">
-        <v>0.1820530331818197</v>
+        <v>0.7426678482602922</v>
       </c>
       <c r="AA4">
-        <v>0.2839994527358924</v>
+        <v>0.7000255509494521</v>
       </c>
       <c r="AB4">
-        <v>0.3609743235263839</v>
+        <v>0.544686120366265</v>
       </c>
       <c r="AC4">
-        <v>80.43391422492162</v>
+        <v>48.29978656895716</v>
       </c>
       <c r="AD4" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -4805,25 +4805,25 @@
         <v>91</v>
       </c>
       <c r="C5">
-        <v>13.232</v>
+        <v>13.288</v>
       </c>
       <c r="D5">
-        <v>12.328</v>
+        <v>12.416</v>
       </c>
       <c r="E5">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="F5">
         <v>12.4</v>
       </c>
       <c r="G5">
-        <v>12.8070973330047</v>
+        <v>12.87813813537621</v>
       </c>
       <c r="J5" t="s">
         <v>94</v>
       </c>
       <c r="K5">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="L5">
         <v>2.351026032651849</v>
@@ -4838,10 +4838,10 @@
         <v>118</v>
       </c>
       <c r="P5">
-        <v>9.674452691001546</v>
+        <v>9.779145216252848</v>
       </c>
       <c r="Q5">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R5">
         <v>10</v>
@@ -4850,34 +4850,34 @@
         <v>119</v>
       </c>
       <c r="T5">
-        <v>-1.562127356038731</v>
+        <v>-1.671300129583011</v>
       </c>
       <c r="U5">
-        <v>0.3255473089984537</v>
+        <v>0.2208547837471517</v>
       </c>
       <c r="V5" t="s">
         <v>96</v>
       </c>
       <c r="W5">
-        <v>12.8070973330047</v>
+        <v>12.87813813537621</v>
       </c>
       <c r="X5">
-        <v>1.570517285964419</v>
+        <v>1.427692789540352</v>
       </c>
       <c r="Y5">
-        <v>1.236580047040277</v>
+        <v>1.45044534583586</v>
       </c>
       <c r="Z5">
-        <v>0.6680135669076143</v>
+        <v>0.6072637094239147</v>
       </c>
       <c r="AA5">
-        <v>0.5259746297430284</v>
+        <v>0.6169414228900835</v>
       </c>
       <c r="AB5">
         <v>0.6530627868477359</v>
       </c>
       <c r="AC5">
-        <v>53.88597538332969</v>
+        <v>54.29973121083951</v>
       </c>
       <c r="AD5" t="s">
         <v>120</v>
@@ -4885,49 +4885,49 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
         <v>90</v>
       </c>
       <c r="C6">
-        <v>1.832</v>
+        <v>1.344</v>
       </c>
       <c r="D6">
-        <v>1.772</v>
+        <v>1.788</v>
       </c>
       <c r="E6">
-        <v>2.554644495322226</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="F6">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="G6">
-        <v>1.803041458005251</v>
+        <v>1.558293210761144</v>
       </c>
       <c r="J6" t="s">
         <v>94</v>
       </c>
       <c r="K6">
-        <v>2.554644495322226</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="L6">
-        <v>1.198624596172324</v>
+        <v>1.746417103282563</v>
       </c>
       <c r="M6">
         <v>5.24749619700716</v>
       </c>
       <c r="N6">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="s">
         <v>118</v>
       </c>
       <c r="P6">
-        <v>2.528722469358031</v>
+        <v>1.501280428022223</v>
       </c>
       <c r="Q6">
-        <v>0.9898529811049405</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R6">
         <v>2</v>
@@ -4936,464 +4936,464 @@
         <v>119</v>
       </c>
       <c r="T6">
-        <v>-0.02592202596419435</v>
+        <v>0.02825555268635682</v>
       </c>
       <c r="U6">
-        <v>-0.5287224693580312</v>
+        <v>0.4987195719777766</v>
       </c>
       <c r="V6" t="s">
         <v>96</v>
       </c>
       <c r="W6">
-        <v>1.803041458005251</v>
+        <v>1.558293210761144</v>
       </c>
       <c r="X6">
-        <v>0.7516030373169746</v>
+        <v>0.08526833542527745</v>
       </c>
       <c r="Y6">
-        <v>0.5546444953222256</v>
+        <v>0.5269751246641334</v>
       </c>
       <c r="Z6">
-        <v>0.627054575483547</v>
+        <v>0.04882472535627785</v>
       </c>
       <c r="AA6">
-        <v>0.4627341179994319</v>
+        <v>0.3017464291168656</v>
       </c>
       <c r="AB6">
-        <v>0.7491403726077025</v>
+        <v>0.7593117840358968</v>
       </c>
       <c r="AC6">
-        <v>56.57842736664286</v>
+        <v>87.16674245626311</v>
       </c>
       <c r="AD6" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7">
-        <v>3.692</v>
+        <v>1.92</v>
       </c>
       <c r="D7">
-        <v>3.192</v>
+        <v>1.584</v>
       </c>
       <c r="E7">
-        <v>3.475459163737268</v>
+        <v>1.52157415011752</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="G7">
-        <v>3.450678816710424</v>
+        <v>1.762071575099091</v>
       </c>
       <c r="J7" t="s">
         <v>94</v>
       </c>
       <c r="K7">
-        <v>3.475459163737268</v>
+        <v>1.52157415011752</v>
       </c>
       <c r="L7">
-        <v>0.887818750560327</v>
+        <v>1.157976831184469</v>
       </c>
       <c r="M7">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N7">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="O7" t="s">
         <v>118</v>
       </c>
       <c r="P7">
-        <v>3.440193613933819</v>
+        <v>1.299486100486649</v>
       </c>
       <c r="Q7">
-        <v>0.9898529811049405</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S7" t="s">
         <v>119</v>
       </c>
       <c r="T7">
-        <v>-0.03526554980344976</v>
+        <v>-0.2220880496308713</v>
       </c>
       <c r="U7">
-        <v>-0.4401936139338187</v>
+        <v>-0.2994861004866491</v>
       </c>
       <c r="V7" t="s">
         <v>96</v>
       </c>
       <c r="W7">
-        <v>3.450678816710424</v>
+        <v>1.762071575099091</v>
       </c>
       <c r="X7">
-        <v>0.0247803470268444</v>
+        <v>0.2404974249815708</v>
       </c>
       <c r="Y7">
-        <v>0.4754591637372685</v>
+        <v>0.5215741501175204</v>
       </c>
       <c r="Z7">
-        <v>0.02791149320872625</v>
+        <v>0.2076875965951506</v>
       </c>
       <c r="AA7">
-        <v>0.5355362943587225</v>
+        <v>0.4504184678583023</v>
       </c>
       <c r="AB7">
-        <v>0.3551275002241308</v>
+        <v>0.8271263079889064</v>
       </c>
       <c r="AC7">
-        <v>81.41748166151876</v>
+        <v>74.62882184844142</v>
       </c>
       <c r="AD7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
         <v>90</v>
       </c>
       <c r="C8">
-        <v>3.184</v>
+        <v>1.904</v>
       </c>
       <c r="D8">
-        <v>4.004</v>
+        <v>1.796</v>
       </c>
       <c r="E8">
-        <v>1.550377686812013</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="F8">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="G8">
-        <v>3.579766740594905</v>
+        <v>1.851874624409452</v>
       </c>
       <c r="J8" t="s">
         <v>94</v>
       </c>
       <c r="K8">
-        <v>1.550377686812013</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="L8">
-        <v>7.059923274159115</v>
+        <v>1.198624596172324</v>
       </c>
       <c r="M8">
         <v>5.24749619700716</v>
       </c>
       <c r="N8">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="O8" t="s">
         <v>118</v>
       </c>
       <c r="P8">
-        <v>1.566812662552681</v>
+        <v>2.557215395085126</v>
       </c>
       <c r="Q8">
-        <v>1.010600627112006</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S8" t="s">
         <v>119</v>
       </c>
       <c r="T8">
-        <v>0.01643497574066832</v>
+        <v>-0.04703542507679881</v>
       </c>
       <c r="U8">
-        <v>0.433187337447319</v>
+        <v>0.4427846049148738</v>
       </c>
       <c r="V8" t="s">
         <v>96</v>
       </c>
       <c r="W8">
-        <v>3.579766740594905</v>
+        <v>1.851874624409452</v>
       </c>
       <c r="X8">
-        <v>2.029389053782892</v>
+        <v>0.7523761957524733</v>
       </c>
       <c r="Y8">
-        <v>0.4496223131879873</v>
+        <v>0.395749179838075</v>
       </c>
       <c r="Z8">
-        <v>0.2874519984106493</v>
+        <v>0.6276996135029299</v>
       </c>
       <c r="AA8">
-        <v>0.06368657218042365</v>
+        <v>0.3301694134275707</v>
       </c>
       <c r="AB8">
-        <v>0.9289372729156731</v>
+        <v>0.7491403726077025</v>
       </c>
       <c r="AC8">
-        <v>81.12864354622022</v>
+        <v>59.24054223283283</v>
       </c>
       <c r="AD8" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9">
-        <v>1.9</v>
+        <v>13.532</v>
       </c>
       <c r="D9">
-        <v>1.54</v>
+        <v>12.556</v>
       </c>
       <c r="E9">
-        <v>1.430889012604439</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="F9">
-        <v>1.6</v>
+        <v>11.8</v>
       </c>
       <c r="G9">
-        <v>1.730790973320455</v>
+        <v>13.06094105021875</v>
       </c>
       <c r="J9" t="s">
         <v>94</v>
       </c>
       <c r="K9">
-        <v>1.430889012604439</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="L9">
-        <v>1.157976831184469</v>
+        <v>3.125306797245826</v>
       </c>
       <c r="M9">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N9">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="s">
         <v>118</v>
       </c>
       <c r="P9">
-        <v>1.231964530182992</v>
+        <v>13.11473458118962</v>
       </c>
       <c r="Q9">
-        <v>0.8609783982760665</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R9">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="S9" t="s">
         <v>119</v>
       </c>
       <c r="T9">
-        <v>-0.1989244824214469</v>
+        <v>-0.2412221969964765</v>
       </c>
       <c r="U9">
-        <v>-0.2319645301829925</v>
+        <v>-0.1147345811896248</v>
       </c>
       <c r="V9" t="s">
         <v>96</v>
       </c>
       <c r="W9">
-        <v>1.730790973320455</v>
+        <v>13.06094105021875</v>
       </c>
       <c r="X9">
-        <v>0.2999019607160154</v>
+        <v>0.2950157279673533</v>
       </c>
       <c r="Y9">
-        <v>0.4308890126044393</v>
+        <v>0.3559567781861013</v>
       </c>
       <c r="Z9">
-        <v>0.2589878766479743</v>
+        <v>0.09439576563406053</v>
       </c>
       <c r="AA9">
-        <v>0.3721050378561482</v>
+        <v>0.1138949873656525</v>
       </c>
       <c r="AB9">
-        <v>0.8271263079889064</v>
+        <v>0.6511055827595471</v>
       </c>
       <c r="AC9">
-        <v>74.18717584194117</v>
+        <v>90.37337437343564</v>
       </c>
       <c r="AD9" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
         <v>90</v>
       </c>
       <c r="C10">
-        <v>3.54</v>
+        <v>3.784</v>
       </c>
       <c r="D10">
-        <v>4.812</v>
+        <v>3.252</v>
       </c>
       <c r="E10">
-        <v>5.586198698614951</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>4.153921090288683</v>
+        <v>3.527234260979891</v>
       </c>
       <c r="J10" t="s">
         <v>94</v>
       </c>
       <c r="K10">
-        <v>5.586198698614951</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="L10">
-        <v>2.262338789582505</v>
+        <v>0.887818750560327</v>
       </c>
       <c r="M10">
         <v>5.24749619700716</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="s">
         <v>118</v>
       </c>
       <c r="P10">
-        <v>5.645415907992541</v>
+        <v>3.590592119879259</v>
       </c>
       <c r="Q10">
-        <v>1.010600627112006</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S10" t="s">
         <v>119</v>
       </c>
       <c r="T10">
-        <v>0.05921720937758934</v>
+        <v>-0.06604255040874341</v>
       </c>
       <c r="U10">
-        <v>0.3545840920074594</v>
+        <v>0.409407880120741</v>
       </c>
       <c r="V10" t="s">
         <v>96</v>
       </c>
       <c r="W10">
-        <v>4.153921090288683</v>
+        <v>3.527234260979891</v>
       </c>
       <c r="X10">
-        <v>1.432277608326268</v>
+        <v>0.1294004093081114</v>
       </c>
       <c r="Y10">
-        <v>0.4138013013850488</v>
+        <v>0.3433653297119976</v>
       </c>
       <c r="Z10">
-        <v>0.633095986737947</v>
+        <v>0.1457509308363258</v>
       </c>
       <c r="AA10">
-        <v>0.1829086356519627</v>
+        <v>0.3867516083607045</v>
       </c>
       <c r="AB10">
-        <v>0.452467757916501</v>
+        <v>0.3551275002241308</v>
       </c>
       <c r="AC10">
-        <v>62.15552874778314</v>
+        <v>79.44532252176565</v>
       </c>
       <c r="AD10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
         <v>91</v>
       </c>
       <c r="C11">
-        <v>0.632</v>
+        <v>0.6</v>
       </c>
       <c r="D11">
-        <v>0.416</v>
+        <v>0.696</v>
       </c>
       <c r="E11">
-        <v>0.6558051063869967</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="F11">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G11">
-        <v>0.530474583992273</v>
+        <v>0.6451224071145452</v>
       </c>
       <c r="J11" t="s">
         <v>94</v>
       </c>
       <c r="K11">
-        <v>0.6558051063869967</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="L11">
-        <v>0.7620693762924241</v>
+        <v>1.559831022862906</v>
       </c>
       <c r="M11">
         <v>1.038416113387647</v>
       </c>
       <c r="N11">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="s">
         <v>118</v>
       </c>
       <c r="P11">
-        <v>0.7484613503089816</v>
+        <v>0.2767323416308665</v>
       </c>
       <c r="Q11">
-        <v>1.141286249557361</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="s">
         <v>119</v>
       </c>
       <c r="T11">
-        <v>0.0926562439219849</v>
+        <v>-0.04729480830888999</v>
       </c>
       <c r="U11">
-        <v>0.2515386496910184</v>
+        <v>-0.2767323416308665</v>
       </c>
       <c r="V11" t="s">
         <v>96</v>
       </c>
       <c r="W11">
-        <v>0.530474583992273</v>
+        <v>0.6451224071145452</v>
       </c>
       <c r="X11">
-        <v>0.1253305223947238</v>
+        <v>0.3210952571747887</v>
       </c>
       <c r="Y11">
-        <v>0.3441948936130033</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="Z11">
-        <v>0.1644607778421363</v>
+        <v>0.2058525907411766</v>
       </c>
       <c r="AA11">
-        <v>0.4516582142265844</v>
+        <v>0.207732212778432</v>
       </c>
       <c r="AB11">
-        <v>0.95258672036553</v>
+        <v>1.299859185719089</v>
       </c>
       <c r="AC11">
-        <v>76.72213858724069</v>
+        <v>81.34177543201334</v>
       </c>
       <c r="AD11" t="s">
         <v>78</v>
@@ -5401,49 +5401,49 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
         <v>91</v>
       </c>
       <c r="C12">
-        <v>0.632</v>
+        <v>0.18</v>
       </c>
       <c r="D12">
-        <v>0.416</v>
+        <v>0.264</v>
       </c>
       <c r="E12">
-        <v>0.6558051063869967</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="F12">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G12">
-        <v>0.530474583992273</v>
+        <v>0.2194821062252271</v>
       </c>
       <c r="J12" t="s">
         <v>94</v>
       </c>
       <c r="K12">
-        <v>0.6558051063869967</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="L12">
-        <v>0.7620693762924241</v>
+        <v>0.4925498319332764</v>
       </c>
       <c r="M12">
         <v>1.038416113387647</v>
       </c>
       <c r="N12">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="O12" t="s">
         <v>118</v>
       </c>
       <c r="P12">
-        <v>0.7484613503089816</v>
+        <v>0.7802977676584159</v>
       </c>
       <c r="Q12">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -5452,84 +5452,84 @@
         <v>119</v>
       </c>
       <c r="T12">
-        <v>0.0926562439219849</v>
+        <v>0.101489785235631</v>
       </c>
       <c r="U12">
-        <v>0.2515386496910184</v>
+        <v>0.2197022323415841</v>
       </c>
       <c r="V12" t="s">
         <v>96</v>
       </c>
       <c r="W12">
-        <v>0.530474583992273</v>
+        <v>0.2194821062252271</v>
       </c>
       <c r="X12">
-        <v>0.1253305223947238</v>
+        <v>0.4593258761975577</v>
       </c>
       <c r="Y12">
-        <v>0.3441948936130033</v>
+        <v>0.3211920175772152</v>
       </c>
       <c r="Z12">
-        <v>0.1644607778421363</v>
+        <v>0.9325470163997145</v>
       </c>
       <c r="AA12">
-        <v>0.4516582142265844</v>
+        <v>0.6521005525806892</v>
       </c>
       <c r="AB12">
-        <v>0.95258672036553</v>
+        <v>1.231374579833191</v>
       </c>
       <c r="AC12">
-        <v>76.72213858724069</v>
+        <v>43.41388982372007</v>
       </c>
       <c r="AD12" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B13" t="s">
         <v>91</v>
       </c>
       <c r="C13">
-        <v>0.612</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D13">
-        <v>0.732</v>
+        <v>0.408</v>
       </c>
       <c r="E13">
-        <v>0.3293773794100608</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="F13">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G13">
-        <v>0.6684030088931816</v>
+        <v>0.4885561887353032</v>
       </c>
       <c r="J13" t="s">
         <v>94</v>
       </c>
       <c r="K13">
-        <v>0.3293773794100608</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="L13">
-        <v>1.559831022862906</v>
+        <v>0.3921195507989373</v>
       </c>
       <c r="M13">
         <v>1.038416113387647</v>
       </c>
       <c r="N13">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="s">
         <v>118</v>
       </c>
       <c r="P13">
-        <v>0.2835868085528425</v>
+        <v>0.3618566504167141</v>
       </c>
       <c r="Q13">
-        <v>0.8609783982760665</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -5538,295 +5538,295 @@
         <v>119</v>
       </c>
       <c r="T13">
-        <v>-0.04579057085721838</v>
+        <v>0.04706505036799469</v>
       </c>
       <c r="U13">
-        <v>-0.2835868085528425</v>
+        <v>-0.3618566504167141</v>
       </c>
       <c r="V13" t="s">
         <v>96</v>
       </c>
       <c r="W13">
-        <v>0.6684030088931816</v>
+        <v>0.4885561887353032</v>
       </c>
       <c r="X13">
-        <v>0.3390256294831208</v>
+        <v>0.1737645886865837</v>
       </c>
       <c r="Y13">
-        <v>0.3293773794100608</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="Z13">
-        <v>0.2173476642751179</v>
+        <v>0.4431418640884933</v>
       </c>
       <c r="AA13">
-        <v>0.2111622185879616</v>
+        <v>0.8027949624223952</v>
       </c>
       <c r="AB13">
-        <v>1.299859185719089</v>
+        <v>0.6535325846648956</v>
       </c>
       <c r="AC13">
-        <v>80.63940515159102</v>
+        <v>56.60796713936882</v>
       </c>
       <c r="AD13" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14">
-        <v>0.164</v>
+        <v>8.763999999999999</v>
       </c>
       <c r="D14">
-        <v>0.268</v>
+        <v>6.752</v>
       </c>
       <c r="E14">
-        <v>0.6905082799680116</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="F14">
-        <v>0.2</v>
+        <v>6.6</v>
       </c>
       <c r="G14">
-        <v>0.2128826077074241</v>
+        <v>7.792923558442745</v>
       </c>
       <c r="J14" t="s">
         <v>94</v>
       </c>
       <c r="K14">
-        <v>0.6905082799680116</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="L14">
-        <v>0.4925498319332764</v>
+        <v>4.673523904256721</v>
       </c>
       <c r="M14">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N14">
-        <v>0.4</v>
+        <v>8.4</v>
       </c>
       <c r="O14" t="s">
         <v>118</v>
       </c>
       <c r="P14">
-        <v>0.7880676051329962</v>
+        <v>4.224092654695784</v>
       </c>
       <c r="Q14">
-        <v>1.141286249557361</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S14" t="s">
         <v>119</v>
       </c>
       <c r="T14">
-        <v>0.09755932516498467</v>
+        <v>-0.07769466504826283</v>
       </c>
       <c r="U14">
-        <v>0.2119323948670038</v>
+        <v>-0.2240926546957844</v>
       </c>
       <c r="V14" t="s">
         <v>96</v>
       </c>
       <c r="W14">
-        <v>0.2128826077074241</v>
+        <v>7.792923558442745</v>
       </c>
       <c r="X14">
-        <v>0.4776256722605874</v>
+        <v>3.491136238698697</v>
       </c>
       <c r="Y14">
-        <v>0.3094917200319884</v>
+        <v>0.3017873197440473</v>
       </c>
       <c r="Z14">
-        <v>0.9697002035020272</v>
+        <v>0.747002970396474</v>
       </c>
       <c r="AA14">
-        <v>0.6283460067730039</v>
+        <v>0.06457382607354901</v>
       </c>
       <c r="AB14">
-        <v>1.231374579833191</v>
+        <v>0.5563718933638954</v>
       </c>
       <c r="AC14">
-        <v>42.73182468197061</v>
+        <v>60.16058574846904</v>
       </c>
       <c r="AD14" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
         <v>90</v>
       </c>
       <c r="C15">
-        <v>1.412</v>
+        <v>5.384</v>
       </c>
       <c r="D15">
-        <v>1.808</v>
+        <v>4.436</v>
       </c>
       <c r="E15">
-        <v>1.699906626866217</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="F15">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="G15">
-        <v>1.603126377165344</v>
+        <v>4.926455036482963</v>
       </c>
       <c r="J15" t="s">
         <v>94</v>
       </c>
       <c r="K15">
-        <v>1.699906626866217</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="L15">
-        <v>1.746417103282563</v>
+        <v>2.858585552684069</v>
       </c>
       <c r="M15">
         <v>5.24749619700716</v>
       </c>
       <c r="N15">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="s">
         <v>118</v>
       </c>
       <c r="P15">
-        <v>1.717926703142854</v>
+        <v>4.212305297947762</v>
       </c>
       <c r="Q15">
-        <v>1.010600627112006</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S15" t="s">
         <v>119</v>
       </c>
       <c r="T15">
-        <v>0.01802007627663649</v>
+        <v>-0.07747785760363346</v>
       </c>
       <c r="U15">
-        <v>0.2820732968571464</v>
+        <v>-0.2123052979477622</v>
       </c>
       <c r="V15" t="s">
         <v>96</v>
       </c>
       <c r="W15">
-        <v>1.603126377165344</v>
+        <v>4.926455036482963</v>
       </c>
       <c r="X15">
-        <v>0.09678024970087273</v>
+        <v>0.6366718809315675</v>
       </c>
       <c r="Y15">
-        <v>0.3000933731337829</v>
+        <v>0.2897831555513957</v>
       </c>
       <c r="Z15">
-        <v>0.05541645779748992</v>
+        <v>0.2227226959619118</v>
       </c>
       <c r="AA15">
-        <v>0.1718337346615124</v>
+        <v>0.1013729168536879</v>
       </c>
       <c r="AB15">
-        <v>0.7593117840358968</v>
+        <v>0.6972159884595291</v>
       </c>
       <c r="AC15">
-        <v>90.83163983910151</v>
+        <v>83.50611917578671</v>
       </c>
       <c r="AD15" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
       </c>
       <c r="C16">
-        <v>0.552</v>
+        <v>0.632</v>
       </c>
       <c r="D16">
-        <v>0.392</v>
+        <v>0.44</v>
       </c>
       <c r="E16">
-        <v>0.2703407362038964</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="F16">
         <v>0.4</v>
       </c>
       <c r="G16">
-        <v>0.4767959881424244</v>
+        <v>0.5417551857709093</v>
       </c>
       <c r="J16" t="s">
         <v>94</v>
       </c>
       <c r="K16">
-        <v>0.2703407362038964</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="L16">
-        <v>0.3921195507989373</v>
+        <v>0.7620693762924241</v>
       </c>
       <c r="M16">
         <v>1.038416113387647</v>
       </c>
       <c r="N16">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O16" t="s">
         <v>118</v>
       </c>
       <c r="P16">
-        <v>0.3085361649247209</v>
+        <v>0.8656925512363728</v>
       </c>
       <c r="Q16">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="s">
         <v>119</v>
       </c>
       <c r="T16">
-        <v>0.03819542872082443</v>
+        <v>0.1125966967311974</v>
       </c>
       <c r="U16">
-        <v>-0.3085361649247209</v>
+        <v>0.1343074487636272</v>
       </c>
       <c r="V16" t="s">
         <v>96</v>
       </c>
       <c r="W16">
-        <v>0.4767959881424244</v>
+        <v>0.5417551857709093</v>
       </c>
       <c r="X16">
-        <v>0.206455251938528</v>
+        <v>0.211340668734266</v>
       </c>
       <c r="Y16">
-        <v>0.2703407362038964</v>
+        <v>0.2469041454948246</v>
       </c>
       <c r="Z16">
-        <v>0.526510987574781</v>
+        <v>0.2773247099397544</v>
       </c>
       <c r="AA16">
-        <v>0.6894344738819614</v>
+        <v>0.3239916904889269</v>
       </c>
       <c r="AB16">
-        <v>0.6535325846648956</v>
+        <v>0.95258672036553</v>
       </c>
       <c r="AC16">
-        <v>55.79230620253968</v>
+        <v>74.55313054289088</v>
       </c>
       <c r="AD16" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -5939,25 +5939,25 @@
         <v>90</v>
       </c>
       <c r="C2">
-        <v>13.58</v>
+        <v>13.548</v>
       </c>
       <c r="D2">
-        <v>14.788</v>
+        <v>14.728</v>
       </c>
       <c r="E2">
-        <v>19.01148659179185</v>
+        <v>18.83927196478475</v>
       </c>
       <c r="F2">
         <v>14.6</v>
       </c>
       <c r="G2">
-        <v>14.16303197882762</v>
+        <v>14.1175179925634</v>
       </c>
       <c r="J2" t="s">
         <v>94</v>
       </c>
       <c r="K2">
-        <v>19.01148659179185</v>
+        <v>18.83927196478475</v>
       </c>
       <c r="L2">
         <v>5.333756871724871</v>
@@ -5972,10 +5972,10 @@
         <v>118</v>
       </c>
       <c r="P2">
-        <v>19.21302027199633</v>
+        <v>19.20064674567716</v>
       </c>
       <c r="Q2">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R2">
         <v>19</v>
@@ -5984,34 +5984,34 @@
         <v>119</v>
       </c>
       <c r="T2">
-        <v>0.2015336802044807</v>
+        <v>0.3613747808924153</v>
       </c>
       <c r="U2">
-        <v>-0.2130202719963314</v>
+        <v>-0.2006467456771617</v>
       </c>
       <c r="V2" t="s">
         <v>96</v>
       </c>
       <c r="W2">
-        <v>14.16303197882762</v>
+        <v>14.1175179925634</v>
       </c>
       <c r="X2">
-        <v>4.848454612964233</v>
+        <v>4.721753972221347</v>
       </c>
       <c r="Y2">
-        <v>0.01148659179185074</v>
+        <v>0.1607280352152536</v>
       </c>
       <c r="Z2">
-        <v>0.909013052069676</v>
+        <v>0.8852585683558519</v>
       </c>
       <c r="AA2">
-        <v>0.00215356493895383</v>
+        <v>0.03013411354898824</v>
       </c>
       <c r="AB2">
         <v>1.088521810556096</v>
       </c>
       <c r="AC2">
-        <v>55.34343008256245</v>
+        <v>55.65685088619063</v>
       </c>
       <c r="AD2" t="s">
         <v>120</v>
@@ -6019,343 +6019,343 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
         <v>90</v>
       </c>
       <c r="C3">
-        <v>8.612</v>
+        <v>3.444</v>
       </c>
       <c r="D3">
-        <v>6.564</v>
+        <v>4.86</v>
       </c>
       <c r="E3">
-        <v>3.808811132083866</v>
+        <v>0.2404700937671027</v>
       </c>
       <c r="F3">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="G3">
-        <v>7.623548433245896</v>
+        <v>4.127421591076081</v>
       </c>
       <c r="J3" t="s">
         <v>94</v>
       </c>
       <c r="K3">
-        <v>3.808811132083866</v>
+        <v>0.2404700937671027</v>
       </c>
       <c r="L3">
-        <v>4.673523904256721</v>
+        <v>9.933150479214353</v>
       </c>
       <c r="M3">
         <v>5.24749619700716</v>
       </c>
       <c r="N3">
-        <v>8.4</v>
+        <v>10.3</v>
       </c>
       <c r="O3" t="s">
         <v>118</v>
       </c>
       <c r="P3">
-        <v>3.770163053558897</v>
+        <v>0.2450827893961431</v>
       </c>
       <c r="Q3">
-        <v>0.9898529811049405</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S3" t="s">
         <v>119</v>
       </c>
       <c r="T3">
-        <v>-0.03864807852496854</v>
+        <v>0.004612695629040375</v>
       </c>
       <c r="U3">
-        <v>0.229836946441103</v>
+        <v>-0.2450827893961431</v>
       </c>
       <c r="V3" t="s">
         <v>96</v>
       </c>
       <c r="W3">
-        <v>7.623548433245896</v>
+        <v>4.127421591076081</v>
       </c>
       <c r="X3">
-        <v>3.81473730116203</v>
+        <v>3.886951497308978</v>
       </c>
       <c r="Y3">
-        <v>0.1911888679161344</v>
+        <v>0.2404700937671027</v>
       </c>
       <c r="Z3">
-        <v>0.816244311425797</v>
+        <v>0.3913110453166527</v>
       </c>
       <c r="AA3">
-        <v>0.04090893121184135</v>
+        <v>0.02420884434100734</v>
       </c>
       <c r="AB3">
-        <v>0.5563718933638954</v>
+        <v>0.9643835416712964</v>
       </c>
       <c r="AC3">
-        <v>57.99131498158366</v>
+        <v>76.8876227493331</v>
       </c>
       <c r="AD3" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
         <v>90</v>
       </c>
       <c r="C4">
-        <v>3.948</v>
+        <v>8.763999999999999</v>
       </c>
       <c r="D4">
-        <v>4.92</v>
+        <v>6.752</v>
       </c>
       <c r="E4">
-        <v>1.16567981478854</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="F4">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="G4">
-        <v>4.417128380314937</v>
+        <v>7.792923558442745</v>
       </c>
       <c r="J4" t="s">
         <v>94</v>
       </c>
       <c r="K4">
-        <v>1.16567981478854</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="L4">
-        <v>9.933150479214353</v>
+        <v>4.673523904256721</v>
       </c>
       <c r="M4">
         <v>5.24749619700716</v>
       </c>
       <c r="N4">
-        <v>10.3</v>
+        <v>8.4</v>
       </c>
       <c r="O4" t="s">
         <v>118</v>
       </c>
       <c r="P4">
-        <v>1.178036751837105</v>
+        <v>4.224092654695784</v>
       </c>
       <c r="Q4">
-        <v>1.010600627112006</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S4" t="s">
         <v>119</v>
       </c>
       <c r="T4">
-        <v>0.01235693704856522</v>
+        <v>-0.07769466504826283</v>
       </c>
       <c r="U4">
-        <v>-0.1780367518371049</v>
+        <v>-0.2240926546957844</v>
       </c>
       <c r="V4" t="s">
         <v>96</v>
       </c>
       <c r="W4">
-        <v>4.417128380314937</v>
+        <v>7.792923558442745</v>
       </c>
       <c r="X4">
-        <v>3.251448565526397</v>
+        <v>3.491136238698697</v>
       </c>
       <c r="Y4">
-        <v>0.1656798147885397</v>
+        <v>0.3017873197440473</v>
       </c>
       <c r="Z4">
-        <v>0.3273330623884362</v>
+        <v>0.747002970396474</v>
       </c>
       <c r="AA4">
-        <v>0.01667948302356171</v>
+        <v>0.06457382607354901</v>
       </c>
       <c r="AB4">
-        <v>0.9643835416712964</v>
+        <v>0.5563718933638954</v>
       </c>
       <c r="AC4">
-        <v>80.36396477336831</v>
+        <v>60.16058574846904</v>
       </c>
       <c r="AD4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5">
-        <v>10.028</v>
+        <v>2.824</v>
       </c>
       <c r="D5">
-        <v>11.468</v>
+        <v>3.956</v>
       </c>
       <c r="E5">
-        <v>13.28203815275881</v>
+        <v>0.8437214709471421</v>
       </c>
       <c r="F5">
-        <v>11.6</v>
+        <v>5.8</v>
       </c>
       <c r="G5">
-        <v>10.70483610671818</v>
+        <v>3.370351158967601</v>
       </c>
       <c r="J5" t="s">
         <v>94</v>
       </c>
       <c r="K5">
-        <v>13.28203815275881</v>
+        <v>0.8437214709471421</v>
       </c>
       <c r="L5">
-        <v>3.050242274051084</v>
+        <v>7.059923274159115</v>
       </c>
       <c r="M5">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N5">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="O5" t="s">
         <v>118</v>
       </c>
       <c r="P5">
-        <v>15.15860750983988</v>
+        <v>0.8599057302044893</v>
       </c>
       <c r="Q5">
-        <v>1.141286249557361</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="S5" t="s">
         <v>119</v>
       </c>
       <c r="T5">
-        <v>1.876569357081072</v>
+        <v>0.01618425925734723</v>
       </c>
       <c r="U5">
-        <v>-0.158607509839884</v>
+        <v>0.1400942697955107</v>
       </c>
       <c r="V5" t="s">
         <v>96</v>
       </c>
       <c r="W5">
-        <v>10.70483610671818</v>
+        <v>3.370351158967601</v>
       </c>
       <c r="X5">
-        <v>2.577202046040632</v>
+        <v>2.526629688020459</v>
       </c>
       <c r="Y5">
-        <v>1.717961847241188</v>
+        <v>0.1562785290528579</v>
       </c>
       <c r="Z5">
-        <v>0.8449171621432557</v>
+        <v>0.3578834485735112</v>
       </c>
       <c r="AA5">
-        <v>0.5632214404266095</v>
+        <v>0.02213600955478822</v>
       </c>
       <c r="AB5">
-        <v>0.544686120366265</v>
+        <v>0.9289372729156731</v>
       </c>
       <c r="AC5">
-        <v>47.41063290551929</v>
+        <v>78.63354118711212</v>
       </c>
       <c r="AD5" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
         <v>90</v>
       </c>
       <c r="C6">
-        <v>3.184</v>
+        <v>171.868</v>
       </c>
       <c r="D6">
-        <v>4.004</v>
+        <v>174.552</v>
       </c>
       <c r="E6">
-        <v>1.550377686812013</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="F6">
-        <v>5.8</v>
+        <v>172.6</v>
       </c>
       <c r="G6">
-        <v>3.579766740594905</v>
+        <v>173.1634121118985</v>
       </c>
       <c r="J6" t="s">
         <v>94</v>
       </c>
       <c r="K6">
-        <v>1.550377686812013</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="L6">
-        <v>7.059923274159115</v>
+        <v>24.70132137894479</v>
       </c>
       <c r="M6">
         <v>5.24749619700716</v>
       </c>
       <c r="N6">
-        <v>7.6</v>
+        <v>18.7</v>
       </c>
       <c r="O6" t="s">
         <v>118</v>
       </c>
       <c r="P6">
-        <v>1.566812662552681</v>
+        <v>172.4018190334305</v>
       </c>
       <c r="Q6">
-        <v>1.010600627112006</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>172</v>
       </c>
       <c r="S6" t="s">
         <v>119</v>
       </c>
       <c r="T6">
-        <v>0.01643497574066832</v>
+        <v>-3.171024567518231</v>
       </c>
       <c r="U6">
-        <v>0.433187337447319</v>
+        <v>-0.4018190334304563</v>
       </c>
       <c r="V6" t="s">
         <v>96</v>
       </c>
       <c r="W6">
-        <v>3.579766740594905</v>
+        <v>173.1634121118985</v>
       </c>
       <c r="X6">
-        <v>2.029389053782892</v>
+        <v>2.409431489050235</v>
       </c>
       <c r="Y6">
-        <v>0.4496223131879873</v>
+        <v>3.572843600948687</v>
       </c>
       <c r="Z6">
-        <v>0.2874519984106493</v>
+        <v>0.09754261531547112</v>
       </c>
       <c r="AA6">
-        <v>0.06368657218042365</v>
+        <v>0.1446418005797111</v>
       </c>
       <c r="AB6">
-        <v>0.9289372729156731</v>
+        <v>1.320926276948919</v>
       </c>
       <c r="AC6">
-        <v>81.12864354622022</v>
+        <v>89.22335706647648</v>
       </c>
       <c r="AD6" t="s">
         <v>78</v>
@@ -6363,260 +6363,260 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7">
-        <v>172.1</v>
+        <v>9.932</v>
       </c>
       <c r="D7">
-        <v>175.156</v>
+        <v>11.352</v>
       </c>
       <c r="E7">
-        <v>175.5898630732044</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="F7">
-        <v>172.6</v>
+        <v>11.6</v>
       </c>
       <c r="G7">
-        <v>173.5749550722659</v>
+        <v>10.59943560523598</v>
       </c>
       <c r="J7" t="s">
         <v>94</v>
       </c>
       <c r="K7">
-        <v>175.5898630732044</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="L7">
-        <v>24.70132137894479</v>
+        <v>3.050242274051084</v>
       </c>
       <c r="M7">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N7">
-        <v>18.7</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="s">
         <v>118</v>
       </c>
       <c r="P7">
-        <v>173.8081494148196</v>
+        <v>14.78818442768141</v>
       </c>
       <c r="Q7">
-        <v>0.9898529811049405</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R7">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="S7" t="s">
         <v>119</v>
       </c>
       <c r="T7">
-        <v>-1.781713658384717</v>
+        <v>1.923431956103332</v>
       </c>
       <c r="U7">
-        <v>0.1918505851803616</v>
+        <v>0.2118155723185868</v>
       </c>
       <c r="V7" t="s">
         <v>96</v>
       </c>
       <c r="W7">
-        <v>173.5749550722659</v>
+        <v>10.59943560523598</v>
       </c>
       <c r="X7">
-        <v>2.014908000938448</v>
+        <v>2.265316866342099</v>
       </c>
       <c r="Y7">
-        <v>1.589863073204356</v>
+        <v>2.135247528421919</v>
       </c>
       <c r="Z7">
-        <v>0.08157085890376452</v>
+        <v>0.7426678482602922</v>
       </c>
       <c r="AA7">
-        <v>0.06436348277948976</v>
+        <v>0.7000255509494521</v>
       </c>
       <c r="AB7">
-        <v>1.320926276948919</v>
+        <v>0.544686120366265</v>
       </c>
       <c r="AC7">
-        <v>92.72349650896915</v>
+        <v>48.29978656895716</v>
       </c>
       <c r="AD7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8">
-        <v>7.352</v>
+        <v>1.604</v>
       </c>
       <c r="D8">
-        <v>5.764</v>
+        <v>1.924</v>
       </c>
       <c r="E8">
-        <v>4.801946011202828</v>
+        <v>-0.1313628720128142</v>
       </c>
       <c r="F8">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="G8">
-        <v>6.585563921872306</v>
+        <v>1.754408023715151</v>
       </c>
       <c r="J8" t="s">
         <v>94</v>
       </c>
       <c r="K8">
-        <v>4.801946011202828</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>3.997862832988686</v>
+        <v>1.736334852416627</v>
       </c>
       <c r="M8">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N8">
-        <v>6.7</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="s">
         <v>118</v>
       </c>
       <c r="P8">
-        <v>4.753220574294097</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.9898529811049405</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="s">
         <v>119</v>
       </c>
       <c r="T8">
-        <v>-0.04872543690873066</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>0.2467794257059026</v>
+        <v>0</v>
       </c>
       <c r="V8" t="s">
         <v>96</v>
       </c>
       <c r="W8">
-        <v>6.585563921872306</v>
+        <v>1.754408023715151</v>
       </c>
       <c r="X8">
-        <v>1.783617910669478</v>
+        <v>1.754408023715151</v>
       </c>
       <c r="Y8">
-        <v>0.198053988797172</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>0.446142848111699</v>
+        <v>1.010408805233259</v>
       </c>
       <c r="AA8">
-        <v>0.04953996599455929</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.5966959452221919</v>
+        <v>0.5601080169085895</v>
       </c>
       <c r="AC8">
-        <v>73.54065235742672</v>
+        <v>51.85256808577751</v>
       </c>
       <c r="AD8" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9">
-        <v>1.736</v>
+        <v>7.492</v>
       </c>
       <c r="D9">
-        <v>1.98</v>
+        <v>5.94</v>
       </c>
       <c r="E9">
-        <v>0.06755162617559574</v>
+        <v>5.212253933741241</v>
       </c>
       <c r="F9">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="G9">
-        <v>1.850686118082802</v>
+        <v>6.742939047069155</v>
       </c>
       <c r="J9" t="s">
         <v>94</v>
       </c>
       <c r="K9">
-        <v>0.06755162617559574</v>
+        <v>5.212253933741241</v>
       </c>
       <c r="L9">
-        <v>1.736334852416627</v>
+        <v>3.997862832988686</v>
       </c>
       <c r="M9">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>6.7</v>
       </c>
       <c r="O9" t="s">
         <v>118</v>
       </c>
       <c r="P9">
-        <v>0.05816049090560802</v>
+        <v>5.11811531334273</v>
       </c>
       <c r="Q9">
-        <v>0.8609783982760665</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S9" t="s">
         <v>119</v>
       </c>
       <c r="T9">
-        <v>-0.009391135269987715</v>
+        <v>-0.09413862039851129</v>
       </c>
       <c r="U9">
-        <v>-0.05816049090560802</v>
+        <v>-0.11811531334273</v>
       </c>
       <c r="V9" t="s">
         <v>96</v>
       </c>
       <c r="W9">
-        <v>1.850686118082802</v>
+        <v>6.742939047069155</v>
       </c>
       <c r="X9">
-        <v>1.783134491907207</v>
+        <v>1.530685113327914</v>
       </c>
       <c r="Y9">
-        <v>0.06755162617559574</v>
+        <v>0.2122539337412412</v>
       </c>
       <c r="Z9">
-        <v>1.026953118763609</v>
+        <v>0.382875845738714</v>
       </c>
       <c r="AA9">
-        <v>0.03890472283130038</v>
+        <v>0.05309184997289323</v>
       </c>
       <c r="AB9">
-        <v>0.5601080169085895</v>
+        <v>0.5966959452221919</v>
       </c>
       <c r="AC9">
-        <v>50.60417110498163</v>
+        <v>76.53274884974184</v>
       </c>
       <c r="AD9" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -6627,25 +6627,25 @@
         <v>90</v>
       </c>
       <c r="C10">
-        <v>7.968</v>
+        <v>7.772</v>
       </c>
       <c r="D10">
-        <v>8.868</v>
+        <v>8.804</v>
       </c>
       <c r="E10">
-        <v>10.0582691946606</v>
+        <v>9.770258645592461</v>
       </c>
       <c r="F10">
         <v>9.4</v>
       </c>
       <c r="G10">
-        <v>8.402378129921239</v>
+        <v>8.270086922309687</v>
       </c>
       <c r="J10" t="s">
         <v>94</v>
       </c>
       <c r="K10">
-        <v>10.0582691946606</v>
+        <v>9.770258645592461</v>
       </c>
       <c r="L10">
         <v>4.467028425282805</v>
@@ -6660,10 +6660,10 @@
         <v>118</v>
       </c>
       <c r="P10">
-        <v>10.16489315578537</v>
+        <v>9.957671677471454</v>
       </c>
       <c r="Q10">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -6672,34 +6672,34 @@
         <v>119</v>
       </c>
       <c r="T10">
-        <v>0.1066239611247735</v>
+        <v>0.1874130318789931</v>
       </c>
       <c r="U10">
-        <v>-0.1648931557853732</v>
+        <v>0.04232832252854557</v>
       </c>
       <c r="V10" t="s">
         <v>96</v>
       </c>
       <c r="W10">
-        <v>8.402378129921239</v>
+        <v>8.270086922309687</v>
       </c>
       <c r="X10">
-        <v>1.655891064739361</v>
+        <v>1.500171723282774</v>
       </c>
       <c r="Y10">
-        <v>0.05826919466059977</v>
+        <v>0.2297413544075386</v>
       </c>
       <c r="Z10">
-        <v>0.3706918575595425</v>
+        <v>0.3358321417414752</v>
       </c>
       <c r="AA10">
-        <v>0.01304428562191448</v>
+        <v>0.05143046619252122</v>
       </c>
       <c r="AB10">
         <v>0.911638454139348</v>
       </c>
       <c r="AC10">
-        <v>78.23013869485108</v>
+        <v>78.9550442756191</v>
       </c>
       <c r="AD10" t="s">
         <v>78</v>
@@ -6707,518 +6707,518 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11">
-        <v>13.232</v>
+        <v>173.496</v>
       </c>
       <c r="D11">
-        <v>12.328</v>
+        <v>170.784</v>
       </c>
       <c r="E11">
-        <v>11.23658004704028</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="F11">
-        <v>12.4</v>
+        <v>169.2</v>
       </c>
       <c r="G11">
-        <v>12.8070973330047</v>
+        <v>172.1870739018374</v>
       </c>
       <c r="J11" t="s">
         <v>94</v>
       </c>
       <c r="K11">
-        <v>11.23658004704028</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="L11">
-        <v>2.351026032651849</v>
+        <v>4.764861070548267</v>
       </c>
       <c r="M11">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N11">
-        <v>3.6</v>
+        <v>13.2</v>
       </c>
       <c r="O11" t="s">
         <v>118</v>
       </c>
       <c r="P11">
-        <v>9.674452691001546</v>
+        <v>176.9807039529099</v>
       </c>
       <c r="Q11">
-        <v>0.8609783982760665</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R11">
-        <v>10</v>
+        <v>177</v>
       </c>
       <c r="S11" t="s">
         <v>119</v>
       </c>
       <c r="T11">
-        <v>-1.562127356038731</v>
+        <v>3.330948376911721</v>
       </c>
       <c r="U11">
-        <v>0.3255473089984537</v>
+        <v>0.01929604709013688</v>
       </c>
       <c r="V11" t="s">
         <v>96</v>
       </c>
       <c r="W11">
-        <v>12.8070973330047</v>
+        <v>172.1870739018374</v>
       </c>
       <c r="X11">
-        <v>1.570517285964419</v>
+        <v>1.462681674160791</v>
       </c>
       <c r="Y11">
-        <v>1.236580047040277</v>
+        <v>3.350244424001858</v>
       </c>
       <c r="Z11">
-        <v>0.6680135669076143</v>
+        <v>0.3069725753814032</v>
       </c>
       <c r="AA11">
-        <v>0.5259746297430284</v>
+        <v>0.7031148179135396</v>
       </c>
       <c r="AB11">
-        <v>0.6530627868477359</v>
+        <v>0.3609743235263839</v>
       </c>
       <c r="AC11">
-        <v>53.88597538332969</v>
+        <v>64.04255765445993</v>
       </c>
       <c r="AD11" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12">
-        <v>3.54</v>
+        <v>13.288</v>
       </c>
       <c r="D12">
-        <v>4.812</v>
+        <v>12.416</v>
       </c>
       <c r="E12">
-        <v>5.586198698614951</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>12.4</v>
       </c>
       <c r="G12">
-        <v>4.153921090288683</v>
+        <v>12.87813813537621</v>
       </c>
       <c r="J12" t="s">
         <v>94</v>
       </c>
       <c r="K12">
-        <v>5.586198698614951</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="L12">
-        <v>2.262338789582505</v>
+        <v>2.351026032651849</v>
       </c>
       <c r="M12">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="s">
         <v>118</v>
       </c>
       <c r="P12">
-        <v>5.645415907992541</v>
+        <v>9.779145216252848</v>
       </c>
       <c r="Q12">
-        <v>1.010600627112006</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S12" t="s">
         <v>119</v>
       </c>
       <c r="T12">
-        <v>0.05921720937758934</v>
+        <v>-1.671300129583011</v>
       </c>
       <c r="U12">
-        <v>0.3545840920074594</v>
+        <v>0.2208547837471517</v>
       </c>
       <c r="V12" t="s">
         <v>96</v>
       </c>
       <c r="W12">
-        <v>4.153921090288683</v>
+        <v>12.87813813537621</v>
       </c>
       <c r="X12">
-        <v>1.432277608326268</v>
+        <v>1.427692789540352</v>
       </c>
       <c r="Y12">
-        <v>0.4138013013850488</v>
+        <v>1.45044534583586</v>
       </c>
       <c r="Z12">
-        <v>0.633095986737947</v>
+        <v>0.6072637094239147</v>
       </c>
       <c r="AA12">
-        <v>0.1829086356519627</v>
+        <v>0.6169414228900835</v>
       </c>
       <c r="AB12">
-        <v>0.452467757916501</v>
+        <v>0.6530627868477359</v>
       </c>
       <c r="AC12">
-        <v>62.15552874778314</v>
+        <v>54.29973121083951</v>
       </c>
       <c r="AD12" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
         <v>90</v>
       </c>
       <c r="C13">
-        <v>172.984</v>
+        <v>3.44</v>
       </c>
       <c r="D13">
-        <v>170.488</v>
+        <v>4.696</v>
       </c>
       <c r="E13">
-        <v>172.6467820636017</v>
+        <v>5.170440884727479</v>
       </c>
       <c r="F13">
-        <v>169.2</v>
+        <v>5</v>
       </c>
       <c r="G13">
-        <v>171.7793246530184</v>
+        <v>4.046198812423416</v>
       </c>
       <c r="J13" t="s">
         <v>94</v>
       </c>
       <c r="K13">
-        <v>172.6467820636017</v>
+        <v>5.170440884727479</v>
       </c>
       <c r="L13">
-        <v>4.764861070548267</v>
+        <v>2.262338789582505</v>
       </c>
       <c r="M13">
         <v>5.24749619700716</v>
       </c>
       <c r="N13">
-        <v>13.2</v>
+        <v>5</v>
       </c>
       <c r="O13" t="s">
         <v>118</v>
       </c>
       <c r="P13">
-        <v>174.4769462223457</v>
+        <v>5.269620245019544</v>
       </c>
       <c r="Q13">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R13">
-        <v>174</v>
+        <v>5</v>
       </c>
       <c r="S13" t="s">
         <v>119</v>
       </c>
       <c r="T13">
-        <v>1.830164158743969</v>
+        <v>0.09917936029206498</v>
       </c>
       <c r="U13">
-        <v>-0.4769462223457026</v>
+        <v>-0.269620245019544</v>
       </c>
       <c r="V13" t="s">
         <v>96</v>
       </c>
       <c r="W13">
-        <v>171.7793246530184</v>
+        <v>4.046198812423416</v>
       </c>
       <c r="X13">
-        <v>0.8674574105832846</v>
+        <v>1.124242072304063</v>
       </c>
       <c r="Y13">
-        <v>1.353217936398266</v>
+        <v>0.170440884727479</v>
       </c>
       <c r="Z13">
-        <v>0.1820530331818197</v>
+        <v>0.4969379818269978</v>
       </c>
       <c r="AA13">
-        <v>0.2839994527358924</v>
+        <v>0.07533835582553591</v>
       </c>
       <c r="AB13">
-        <v>0.3609743235263839</v>
+        <v>0.452467757916501</v>
       </c>
       <c r="AC13">
-        <v>80.43391422492162</v>
+        <v>70.51264625686264</v>
       </c>
       <c r="AD13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
         <v>90</v>
       </c>
       <c r="C14">
-        <v>5.304</v>
+        <v>1.904</v>
       </c>
       <c r="D14">
-        <v>4.316</v>
+        <v>1.796</v>
       </c>
       <c r="E14">
-        <v>4.035405960595082</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="F14">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="G14">
-        <v>4.827149341819798</v>
+        <v>1.851874624409452</v>
       </c>
       <c r="J14" t="s">
         <v>94</v>
       </c>
       <c r="K14">
-        <v>4.035405960595082</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="L14">
-        <v>2.858585552684069</v>
+        <v>1.198624596172324</v>
       </c>
       <c r="M14">
         <v>5.24749619700716</v>
       </c>
       <c r="N14">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="O14" t="s">
         <v>118</v>
       </c>
       <c r="P14">
-        <v>3.994458620063688</v>
+        <v>2.557215395085126</v>
       </c>
       <c r="Q14">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S14" t="s">
         <v>119</v>
       </c>
       <c r="T14">
-        <v>-0.04094734053139382</v>
+        <v>-0.04703542507679881</v>
       </c>
       <c r="U14">
-        <v>0.005541379936312207</v>
+        <v>0.4427846049148738</v>
       </c>
       <c r="V14" t="s">
         <v>96</v>
       </c>
       <c r="W14">
-        <v>4.827149341819798</v>
+        <v>1.851874624409452</v>
       </c>
       <c r="X14">
-        <v>0.7917433812247161</v>
+        <v>0.7523761957524733</v>
       </c>
       <c r="Y14">
-        <v>0.03540596059508161</v>
+        <v>0.395749179838075</v>
       </c>
       <c r="Z14">
-        <v>0.2769703290780675</v>
+        <v>0.6276996135029299</v>
       </c>
       <c r="AA14">
-        <v>0.01238583206363622</v>
+        <v>0.3301694134275707</v>
       </c>
       <c r="AB14">
-        <v>0.6972159884595291</v>
+        <v>0.7491403726077025</v>
       </c>
       <c r="AC14">
-        <v>83.16315746844765</v>
+        <v>59.24054223283283</v>
       </c>
       <c r="AD14" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15">
-        <v>1.832</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="D15">
-        <v>1.772</v>
+        <v>0.608</v>
       </c>
       <c r="E15">
-        <v>2.554644495322226</v>
+        <v>-0.01550360442781762</v>
       </c>
       <c r="F15">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="G15">
-        <v>1.803041458005251</v>
+        <v>0.6503979940712121</v>
       </c>
       <c r="J15" t="s">
         <v>94</v>
       </c>
       <c r="K15">
-        <v>2.554644495322226</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>1.198624596172324</v>
+        <v>1.005444112310955</v>
       </c>
       <c r="M15">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N15">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="O15" t="s">
         <v>118</v>
       </c>
       <c r="P15">
-        <v>2.528722469358031</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>0.9898529811049405</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="s">
         <v>119</v>
       </c>
       <c r="T15">
-        <v>-0.02592202596419435</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>-0.5287224693580312</v>
+        <v>0</v>
       </c>
       <c r="V15" t="s">
         <v>96</v>
       </c>
       <c r="W15">
-        <v>1.803041458005251</v>
+        <v>0.6503979940712121</v>
       </c>
       <c r="X15">
-        <v>0.7516030373169746</v>
+        <v>0.6503979940712121</v>
       </c>
       <c r="Y15">
-        <v>0.5546444953222256</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>0.627054575483547</v>
+        <v>0.6468763266973739</v>
       </c>
       <c r="AA15">
-        <v>0.4627341179994319</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.7491403726077025</v>
+        <v>1.117160124789949</v>
       </c>
       <c r="AC15">
-        <v>56.57842736664286</v>
+        <v>65.67383349516004</v>
       </c>
       <c r="AD15" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
       </c>
       <c r="C16">
-        <v>0.676</v>
+        <v>1.12</v>
       </c>
       <c r="D16">
-        <v>0.612</v>
+        <v>1.168</v>
       </c>
       <c r="E16">
-        <v>-0.005331174175850051</v>
+        <v>1.780416614874208</v>
       </c>
       <c r="F16">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>0.6459183952569697</v>
+        <v>1.142561203557273</v>
       </c>
       <c r="J16" t="s">
         <v>94</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1.780416614874208</v>
       </c>
       <c r="L16">
-        <v>1.005444112310955</v>
+        <v>0.8500971208676269</v>
       </c>
       <c r="M16">
         <v>1.038416113387647</v>
       </c>
       <c r="N16">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O16" t="s">
         <v>118</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.046609860316908</v>
       </c>
       <c r="Q16">
-        <v>0.8609783982760665</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="s">
         <v>119</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>0.2661932454427003</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>-0.04660986031690806</v>
       </c>
       <c r="V16" t="s">
         <v>96</v>
       </c>
       <c r="W16">
-        <v>0.6459183952569697</v>
+        <v>1.142561203557273</v>
       </c>
       <c r="X16">
-        <v>0.6459183952569697</v>
+        <v>0.6378554113169352</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>0.2195833851257922</v>
       </c>
       <c r="Z16">
-        <v>0.642420983273117</v>
+        <v>0.7503323980981451</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>0.2583038805044779</v>
       </c>
       <c r="AB16">
-        <v>1.117160124789949</v>
+        <v>1.700194241735254</v>
       </c>
       <c r="AC16">
-        <v>65.86429881671735</v>
+        <v>56.09506097814787</v>
       </c>
       <c r="AD16" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5_Election_Projection_Report.xlsx
+++ b/outputs/Block5_Election_Projection_Report.xlsx
@@ -77,7 +77,7 @@
     <t>2.92%</t>
   </si>
   <si>
-    <t>D 223 - R 212</t>
+    <t>D 227 - R 208</t>
   </si>
   <si>
     <t>Democratic</t>
@@ -89,7 +89,7 @@
     <t>Republican</t>
   </si>
   <si>
-    <t>69.1/100</t>
+    <t>78.0/100</t>
   </si>
   <si>
     <t>Party</t>
@@ -260,136 +260,136 @@
     <t>Very high sensitivity</t>
   </si>
   <si>
+    <t>Low sensitivity</t>
+  </si>
+  <si>
+    <t>Moderate sensitivity</t>
+  </si>
+  <si>
+    <t>Deterministic identity</t>
+  </si>
+  <si>
+    <t>Sensitivity to the alternative TreeEnsemble; no seat constraint required.</t>
+  </si>
+  <si>
+    <t>Sensitivity includes normalization to the 435-seat identity.</t>
+  </si>
+  <si>
+    <t>National prior sensitivity includes the contested-seat identity.</t>
+  </si>
+  <si>
+    <t>Calculated directly from constrained seat identities.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Stability</t>
+  </si>
+  <si>
+    <t>AlternativeDifference</t>
+  </si>
+  <si>
+    <t>ConstraintImpact</t>
+  </si>
+  <si>
+    <t>HistoricalMAE</t>
+  </si>
+  <si>
+    <t>House Buckets</t>
+  </si>
+  <si>
+    <t>Senate Buckets</t>
+  </si>
+  <si>
+    <t>ExtraTrees</t>
+  </si>
+  <si>
+    <t>RandomForest</t>
+  </si>
+  <si>
+    <t>Ridge</t>
+  </si>
+  <si>
+    <t>HistoricalMean</t>
+  </si>
+  <si>
+    <t>TreeEnsemble</t>
+  </si>
+  <si>
+    <t>ExpectedVoteAnchor</t>
+  </si>
+  <si>
+    <t>ExpectedVoteErrorCorrected</t>
+  </si>
+  <si>
+    <t>Selected Strategy</t>
+  </si>
+  <si>
+    <t>Historical MAE</t>
+  </si>
+  <si>
+    <t>Group Historical MAE</t>
+  </si>
+  <si>
+    <t>HistoricalMean MAE</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Normalized Quota</t>
+  </si>
+  <si>
+    <t>Scale Factor</t>
+  </si>
+  <si>
+    <t>Constrained Prediction</t>
+  </si>
+  <si>
+    <t>Final Type</t>
+  </si>
+  <si>
+    <t>Rescaling Adjustment</t>
+  </si>
+  <si>
+    <t>Alternative Strategy</t>
+  </si>
+  <si>
+    <t>Alternative Prediction</t>
+  </si>
+  <si>
+    <t>Model Difference</t>
+  </si>
+  <si>
+    <t>Constraint Impact</t>
+  </si>
+  <si>
+    <t>Relative Model Difference</t>
+  </si>
+  <si>
+    <t>Relative Constraint Impact</t>
+  </si>
+  <si>
+    <t>OOF Error Ratio vs Historical Mean</t>
+  </si>
+  <si>
+    <t>Model Stability Score</t>
+  </si>
+  <si>
+    <t>Model Stability</t>
+  </si>
+  <si>
+    <t>ML Predicted</t>
+  </si>
+  <si>
+    <t>Integer</t>
+  </si>
+  <si>
     <t>Moderate-low sensitivity</t>
   </si>
   <si>
-    <t>Moderate sensitivity</t>
-  </si>
-  <si>
-    <t>Deterministic identity</t>
-  </si>
-  <si>
-    <t>Sensitivity to the alternative TreeEnsemble; no seat constraint required.</t>
-  </si>
-  <si>
-    <t>Sensitivity includes normalization to the 435-seat identity.</t>
-  </si>
-  <si>
-    <t>National prior sensitivity includes the contested-seat identity.</t>
-  </si>
-  <si>
-    <t>Calculated directly from constrained seat identities.</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Stability</t>
-  </si>
-  <si>
-    <t>AlternativeDifference</t>
-  </si>
-  <si>
-    <t>ConstraintImpact</t>
-  </si>
-  <si>
-    <t>HistoricalMAE</t>
-  </si>
-  <si>
-    <t>House Buckets</t>
-  </si>
-  <si>
-    <t>Senate Buckets</t>
-  </si>
-  <si>
-    <t>ExtraTrees</t>
-  </si>
-  <si>
-    <t>RandomForest</t>
-  </si>
-  <si>
-    <t>Ridge</t>
-  </si>
-  <si>
-    <t>HistoricalMean</t>
-  </si>
-  <si>
-    <t>TreeEnsemble</t>
-  </si>
-  <si>
-    <t>ExpectedVoteAnchor</t>
-  </si>
-  <si>
-    <t>ExpectedVoteErrorCorrected</t>
-  </si>
-  <si>
-    <t>Selected Strategy</t>
-  </si>
-  <si>
-    <t>Historical MAE</t>
-  </si>
-  <si>
-    <t>Group Historical MAE</t>
-  </si>
-  <si>
-    <t>HistoricalMean MAE</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Normalized Quota</t>
-  </si>
-  <si>
-    <t>Scale Factor</t>
-  </si>
-  <si>
-    <t>Constrained Prediction</t>
-  </si>
-  <si>
-    <t>Final Type</t>
-  </si>
-  <si>
-    <t>Rescaling Adjustment</t>
-  </si>
-  <si>
-    <t>Alternative Strategy</t>
-  </si>
-  <si>
-    <t>Alternative Prediction</t>
-  </si>
-  <si>
-    <t>Model Difference</t>
-  </si>
-  <si>
-    <t>Constraint Impact</t>
-  </si>
-  <si>
-    <t>Relative Model Difference</t>
-  </si>
-  <si>
-    <t>Relative Constraint Impact</t>
-  </si>
-  <si>
-    <t>OOF Error Ratio vs Historical Mean</t>
-  </si>
-  <si>
-    <t>Model Stability Score</t>
-  </si>
-  <si>
-    <t>Model Stability</t>
-  </si>
-  <si>
-    <t>ML Predicted</t>
-  </si>
-  <si>
-    <t>Integer</t>
-  </si>
-  <si>
     <t>High sensitivity</t>
-  </si>
-  <si>
-    <t>Low sensitivity</t>
   </si>
   <si>
     <t>RPP</t>
@@ -812,7 +812,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -820,7 +820,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -985,7 +985,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="J2" t="s">
         <v>94</v>
@@ -994,10 +994,10 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>2.220446049250313E-17</v>
       </c>
       <c r="M2">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -1006,10 +1006,10 @@
         <v>118</v>
       </c>
       <c r="P2">
-        <v>1.149511773378675</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="Q2">
-        <v>1.149511773378675</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -1018,283 +1018,289 @@
         <v>119</v>
       </c>
       <c r="T2">
-        <v>0.1495117733786751</v>
+        <v>0.2322685718485682</v>
       </c>
       <c r="U2">
-        <v>-0.1495117733786751</v>
+        <v>-0.2322685718485682</v>
       </c>
       <c r="V2" t="s">
         <v>96</v>
       </c>
       <c r="W2">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>1.110223024625157E-16</v>
+        <v>0</v>
       </c>
       <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
         <v>0</v>
       </c>
       <c r="AC2">
         <v>100</v>
       </c>
       <c r="AD2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
         <v>90</v>
       </c>
       <c r="C3">
-        <v>15.328</v>
+        <v>3.828</v>
       </c>
       <c r="D3">
-        <v>14.864</v>
+        <v>6.036</v>
       </c>
       <c r="E3">
-        <v>15.0529980979447</v>
+        <v>4.770944606916803</v>
       </c>
       <c r="F3">
-        <v>14.2</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>15.10405394190727</v>
+        <v>4.844607231094189</v>
       </c>
       <c r="J3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K3">
-        <v>15.0529980979447</v>
+        <v>4.844607231094189</v>
       </c>
       <c r="L3">
-        <v>6.129350049043507</v>
+        <v>5.084231521849853</v>
       </c>
       <c r="M3">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N3">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="O3" t="s">
         <v>118</v>
       </c>
       <c r="P3">
-        <v>14.78112560442925</v>
+        <v>5.027637971466064</v>
       </c>
       <c r="Q3">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="S3" t="s">
         <v>119</v>
       </c>
       <c r="T3">
-        <v>-0.2718724935154491</v>
+        <v>0.1830307403718754</v>
       </c>
       <c r="U3">
-        <v>0.2188743955707473</v>
+        <v>-0.02763797146606439</v>
       </c>
       <c r="V3" t="s">
         <v>96</v>
       </c>
       <c r="W3">
-        <v>15.10405394190727</v>
+        <v>4.844607231094189</v>
       </c>
       <c r="X3">
-        <v>0.05105584396257257</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>0.05299809794470178</v>
+        <v>0.155392768905811</v>
       </c>
       <c r="Z3">
-        <v>0.00832973211744366</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.008646609758072507</v>
+        <v>0.03056366891200751</v>
       </c>
       <c r="AB3">
-        <v>0.972912706197382</v>
+        <v>0.6778975362466471</v>
       </c>
       <c r="AC3">
-        <v>99.1594882890594</v>
+        <v>98.93597283506041</v>
       </c>
       <c r="AD3" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
         <v>90</v>
       </c>
       <c r="C4">
-        <v>13.532</v>
+        <v>1.748</v>
       </c>
       <c r="D4">
-        <v>12.556</v>
+        <v>3.744</v>
       </c>
       <c r="E4">
-        <v>13.3559567781861</v>
+        <v>-5.9050260855817</v>
       </c>
       <c r="F4">
-        <v>11.8</v>
+        <v>6.8</v>
       </c>
       <c r="G4">
-        <v>13.06094105021875</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="J4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K4">
-        <v>13.3559567781861</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="L4">
-        <v>3.125306797245826</v>
+        <v>9.299703921130613</v>
       </c>
       <c r="M4">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N4">
-        <v>4.8</v>
+        <v>10.1</v>
       </c>
       <c r="O4" t="s">
         <v>118</v>
       </c>
       <c r="P4">
-        <v>13.11473458118962</v>
+        <v>2.767758209900166</v>
       </c>
       <c r="Q4">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R4">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="S4" t="s">
         <v>119</v>
       </c>
       <c r="T4">
-        <v>-0.2412221969964765</v>
+        <v>0.1007600064291512</v>
       </c>
       <c r="U4">
-        <v>-0.1147345811896248</v>
+        <v>0.2322417900998337</v>
       </c>
       <c r="V4" t="s">
         <v>96</v>
       </c>
       <c r="W4">
-        <v>13.06094105021875</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="X4">
-        <v>0.2950157279673533</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>0.3559567781861013</v>
+        <v>0.3330017965289849</v>
       </c>
       <c r="Z4">
-        <v>0.09439576563406053</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>0.1138949873656525</v>
+        <v>0.03580778478036752</v>
       </c>
       <c r="AB4">
-        <v>0.6511055827595471</v>
+        <v>0.9207627644683776</v>
       </c>
       <c r="AC4">
-        <v>90.37337437343564</v>
+        <v>98.75454828619661</v>
       </c>
       <c r="AD4" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
         <v>90</v>
       </c>
       <c r="C5">
-        <v>171.868</v>
+        <v>14.108</v>
       </c>
       <c r="D5">
-        <v>174.552</v>
+        <v>12.212</v>
       </c>
       <c r="E5">
-        <v>175.5728436009487</v>
+        <v>10.50855707095638</v>
       </c>
       <c r="F5">
-        <v>172.6</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>173.1634121118985</v>
+        <v>13.23504379069086</v>
       </c>
       <c r="J5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K5">
-        <v>175.5728436009487</v>
+        <v>13.23504379069086</v>
       </c>
       <c r="L5">
-        <v>24.70132137894479</v>
+        <v>5.542668330792591</v>
       </c>
       <c r="M5">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N5">
-        <v>18.7</v>
+        <v>7</v>
       </c>
       <c r="O5" t="s">
         <v>118</v>
       </c>
       <c r="P5">
-        <v>172.4018190334305</v>
+        <v>12.80565286246813</v>
       </c>
       <c r="Q5">
-        <v>0.981938980411313</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R5">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="S5" t="s">
         <v>119</v>
       </c>
       <c r="T5">
-        <v>-3.171024567518231</v>
+        <v>-0.4293909282227268</v>
       </c>
       <c r="U5">
-        <v>-0.4018190334304563</v>
+        <v>0.1943471375318673</v>
       </c>
       <c r="V5" t="s">
         <v>96</v>
       </c>
       <c r="W5">
-        <v>173.1634121118985</v>
+        <v>13.23504379069086</v>
       </c>
       <c r="X5">
-        <v>2.409431489050235</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>3.572843600948687</v>
+        <v>0.2350437906908596</v>
       </c>
       <c r="Z5">
-        <v>0.09754261531547112</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>0.1446418005797111</v>
+        <v>0.04240625212680708</v>
       </c>
       <c r="AB5">
-        <v>1.320926276948919</v>
+        <v>0.7918097615417986</v>
       </c>
       <c r="AC5">
-        <v>89.22335706647648</v>
+        <v>98.52674141152615</v>
       </c>
       <c r="AD5" t="s">
         <v>78</v>
@@ -1302,85 +1308,85 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6">
-        <v>1.168</v>
+        <v>10.3</v>
       </c>
       <c r="D6">
-        <v>1.328</v>
+        <v>7.98</v>
       </c>
       <c r="E6">
-        <v>1.138895095514905</v>
+        <v>6.105754884068356</v>
       </c>
       <c r="F6">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="G6">
-        <v>1.243204011857575</v>
+        <v>9.231825735444511</v>
       </c>
       <c r="J6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K6">
-        <v>1.138895095514905</v>
+        <v>9.231825735444511</v>
       </c>
       <c r="L6">
-        <v>0.9319718387197466</v>
+        <v>5.429823374723132</v>
       </c>
       <c r="M6">
-        <v>1.038416113387647</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N6">
-        <v>0.9</v>
+        <v>7.9</v>
       </c>
       <c r="O6" t="s">
         <v>118</v>
       </c>
       <c r="P6">
-        <v>0.9726626509918868</v>
+        <v>8.932313147165718</v>
       </c>
       <c r="Q6">
-        <v>0.8540406002469759</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S6" t="s">
         <v>119</v>
       </c>
       <c r="T6">
-        <v>-0.1662324445230186</v>
+        <v>-0.2995125882787928</v>
       </c>
       <c r="U6">
-        <v>0.02733734900811324</v>
+        <v>0.06768685283428155</v>
       </c>
       <c r="V6" t="s">
         <v>96</v>
       </c>
       <c r="W6">
-        <v>1.243204011857575</v>
+        <v>9.231825735444511</v>
       </c>
       <c r="X6">
-        <v>0.10430891634267</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>0.1388950955149053</v>
+        <v>0.2318257354445112</v>
       </c>
       <c r="Z6">
-        <v>0.1119228199920285</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>0.1490335756343304</v>
+        <v>0.04269489437238501</v>
       </c>
       <c r="AB6">
-        <v>1.035524265244163</v>
+        <v>0.6873194145219155</v>
       </c>
       <c r="AC6">
-        <v>88.25749324682307</v>
+        <v>98.51678827132986</v>
       </c>
       <c r="AD6" t="s">
         <v>78</v>
@@ -1388,85 +1394,85 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
         <v>90</v>
       </c>
       <c r="C7">
-        <v>1.344</v>
+        <v>1.924</v>
       </c>
       <c r="D7">
-        <v>1.788</v>
+        <v>3.576</v>
       </c>
       <c r="E7">
-        <v>1.473024875335867</v>
+        <v>-3.969061584617776</v>
       </c>
       <c r="F7">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="G7">
-        <v>1.558293210761144</v>
+        <v>2.684613743554167</v>
       </c>
       <c r="J7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K7">
-        <v>1.473024875335867</v>
+        <v>2.684613743554167</v>
       </c>
       <c r="L7">
-        <v>1.746417103282563</v>
+        <v>7.332928773632203</v>
       </c>
       <c r="M7">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N7">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="O7" t="s">
         <v>118</v>
       </c>
       <c r="P7">
-        <v>1.501280428022223</v>
+        <v>2.786039270466129</v>
       </c>
       <c r="Q7">
-        <v>1.019181992890591</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7" t="s">
         <v>119</v>
       </c>
       <c r="T7">
-        <v>0.02825555268635682</v>
+        <v>0.1014255269119624</v>
       </c>
       <c r="U7">
-        <v>0.4987195719777766</v>
+        <v>0.2139607295338708</v>
       </c>
       <c r="V7" t="s">
         <v>96</v>
       </c>
       <c r="W7">
-        <v>1.558293210761144</v>
+        <v>2.684613743554167</v>
       </c>
       <c r="X7">
-        <v>0.08526833542527745</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>0.5269751246641334</v>
+        <v>0.3153862564458332</v>
       </c>
       <c r="Z7">
-        <v>0.04882472535627785</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>0.3017464291168656</v>
+        <v>0.04300958950806959</v>
       </c>
       <c r="AB7">
-        <v>0.7593117840358968</v>
+        <v>0.9166160967040253</v>
       </c>
       <c r="AC7">
-        <v>87.16674245626311</v>
+        <v>98.50593790497011</v>
       </c>
       <c r="AD7" t="s">
         <v>78</v>
@@ -1474,85 +1480,85 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
         <v>90</v>
       </c>
       <c r="C8">
-        <v>1.076</v>
+        <v>4.108</v>
       </c>
       <c r="D8">
-        <v>1.236</v>
+        <v>3.604</v>
       </c>
       <c r="E8">
-        <v>0.966548112280941</v>
+        <v>4.670106077902364</v>
       </c>
       <c r="F8">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="G8">
-        <v>1.153222778652665</v>
+        <v>3.875948349424152</v>
       </c>
       <c r="J8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K8">
-        <v>0.966548112280941</v>
+        <v>3.875948349424152</v>
       </c>
       <c r="L8">
-        <v>0.8200692764238203</v>
+        <v>2.527685652926809</v>
       </c>
       <c r="M8">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N8">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="s">
         <v>118</v>
       </c>
       <c r="P8">
-        <v>0.9850884312991284</v>
+        <v>3.75019908211359</v>
       </c>
       <c r="Q8">
-        <v>1.019181992890591</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S8" t="s">
         <v>119</v>
       </c>
       <c r="T8">
-        <v>0.01854031901818742</v>
+        <v>-0.1257492673105625</v>
       </c>
       <c r="U8">
-        <v>0.01491156870087162</v>
+        <v>0.24980091788641</v>
       </c>
       <c r="V8" t="s">
         <v>96</v>
       </c>
       <c r="W8">
-        <v>1.153222778652665</v>
+        <v>3.875948349424152</v>
       </c>
       <c r="X8">
-        <v>0.1866746663717236</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>0.03345188771905905</v>
+        <v>0.1240516505758475</v>
       </c>
       <c r="Z8">
-        <v>0.2276328009577183</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>0.04079153881357063</v>
+        <v>0.0490771668669354</v>
       </c>
       <c r="AB8">
-        <v>0.7455175240216548</v>
+        <v>0.9027448760452889</v>
       </c>
       <c r="AC8">
-        <v>85.02385182059285</v>
+        <v>98.29696753419606</v>
       </c>
       <c r="AD8" t="s">
         <v>78</v>
@@ -1560,85 +1566,85 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
         <v>90</v>
       </c>
       <c r="C9">
-        <v>5.384</v>
+        <v>2.156</v>
       </c>
       <c r="D9">
-        <v>4.436</v>
+        <v>1.984</v>
       </c>
       <c r="E9">
-        <v>4.289783155551396</v>
+        <v>2.747813345994109</v>
       </c>
       <c r="F9">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="G9">
-        <v>4.926455036482963</v>
+        <v>2.076807770041576</v>
       </c>
       <c r="J9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K9">
-        <v>4.289783155551396</v>
+        <v>2.076807770041576</v>
       </c>
       <c r="L9">
-        <v>2.858585552684069</v>
+        <v>1.513347208585617</v>
       </c>
       <c r="M9">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N9">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="s">
         <v>118</v>
       </c>
       <c r="P9">
-        <v>4.212305297947762</v>
+        <v>2.009428890891545</v>
       </c>
       <c r="Q9">
-        <v>0.981938980411313</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S9" t="s">
         <v>119</v>
       </c>
       <c r="T9">
-        <v>-0.07747785760363346</v>
+        <v>-0.06737887915003071</v>
       </c>
       <c r="U9">
-        <v>-0.2123052979477622</v>
+        <v>-0.009428890891545194</v>
       </c>
       <c r="V9" t="s">
         <v>96</v>
       </c>
       <c r="W9">
-        <v>4.926455036482963</v>
+        <v>2.076807770041576</v>
       </c>
       <c r="X9">
-        <v>0.6366718809315675</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>0.2897831555513957</v>
+        <v>0.07680777004157591</v>
       </c>
       <c r="Z9">
-        <v>0.2227226959619118</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>0.1013729168536879</v>
+        <v>0.05075356772446217</v>
       </c>
       <c r="AB9">
-        <v>0.6972159884595291</v>
+        <v>0.9458420053660107</v>
       </c>
       <c r="AC9">
-        <v>83.50611917578671</v>
+        <v>98.23930965871645</v>
       </c>
       <c r="AD9" t="s">
         <v>78</v>
@@ -1646,85 +1652,85 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10">
-        <v>0.6</v>
+        <v>12.34</v>
       </c>
       <c r="D10">
-        <v>0.696</v>
+        <v>10.124</v>
       </c>
       <c r="E10">
-        <v>0.3240271499397565</v>
+        <v>9.224776144749352</v>
       </c>
       <c r="F10">
-        <v>0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G10">
-        <v>0.6451224071145452</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="J10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K10">
-        <v>0.3240271499397565</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="L10">
-        <v>1.559831022862906</v>
+        <v>5.707606654863389</v>
       </c>
       <c r="M10">
-        <v>1.038416113387647</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N10">
-        <v>1.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O10" t="s">
         <v>118</v>
       </c>
       <c r="P10">
-        <v>0.2767323416308665</v>
+        <v>10.95245860103622</v>
       </c>
       <c r="Q10">
-        <v>0.8540406002469759</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S10" t="s">
         <v>119</v>
       </c>
       <c r="T10">
-        <v>-0.04729480830888999</v>
+        <v>-0.3672508083366459</v>
       </c>
       <c r="U10">
-        <v>-0.2767323416308665</v>
+        <v>0.04754139896378362</v>
       </c>
       <c r="V10" t="s">
         <v>96</v>
       </c>
       <c r="W10">
-        <v>0.6451224071145452</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="X10">
-        <v>0.3210952571747887</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>0.3240271499397565</v>
+        <v>0.3197094093728623</v>
       </c>
       <c r="Z10">
-        <v>0.2058525907411766</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>0.207732212778432</v>
+        <v>0.05601461850922075</v>
       </c>
       <c r="AB10">
-        <v>1.299859185719089</v>
+        <v>0.6876634523931793</v>
       </c>
       <c r="AC10">
-        <v>81.34177543201334</v>
+        <v>98.05858140436257</v>
       </c>
       <c r="AD10" t="s">
         <v>78</v>
@@ -1732,85 +1738,85 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
         <v>90</v>
       </c>
       <c r="C11">
-        <v>3.784</v>
+        <v>9.212</v>
       </c>
       <c r="D11">
-        <v>3.252</v>
+        <v>11.748</v>
       </c>
       <c r="E11">
-        <v>3.656634670288002</v>
+        <v>14.36529697727345</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>13.2</v>
       </c>
       <c r="G11">
-        <v>3.527234260979891</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="J11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K11">
-        <v>3.656634670288002</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="L11">
-        <v>0.887818750560327</v>
+        <v>5.848565661247161</v>
       </c>
       <c r="M11">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N11">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O11" t="s">
         <v>118</v>
       </c>
       <c r="P11">
-        <v>3.590592119879259</v>
+        <v>10.77177037254729</v>
       </c>
       <c r="Q11">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R11">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="S11" t="s">
         <v>119</v>
       </c>
       <c r="T11">
-        <v>-0.06604255040874341</v>
+        <v>0.3921454006021552</v>
       </c>
       <c r="U11">
-        <v>0.409407880120741</v>
+        <v>0.2282296274527074</v>
       </c>
       <c r="V11" t="s">
         <v>96</v>
       </c>
       <c r="W11">
-        <v>3.527234260979891</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="X11">
-        <v>0.1294004093081114</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>0.3433653297119976</v>
+        <v>0.6203750280548626</v>
       </c>
       <c r="Z11">
-        <v>0.1457509308363258</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>0.3867516083607045</v>
+        <v>0.1060730209742695</v>
       </c>
       <c r="AB11">
-        <v>0.3551275002241308</v>
+        <v>0.7132397147862392</v>
       </c>
       <c r="AC11">
-        <v>79.44532252176565</v>
+        <v>96.35551463316079</v>
       </c>
       <c r="AD11" t="s">
         <v>78</v>
@@ -1818,85 +1824,85 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
         <v>90</v>
       </c>
       <c r="C12">
-        <v>7.772</v>
+        <v>1.96</v>
       </c>
       <c r="D12">
-        <v>8.804</v>
+        <v>3.288</v>
       </c>
       <c r="E12">
-        <v>9.770258645592461</v>
+        <v>1.85838186252915</v>
       </c>
       <c r="F12">
-        <v>9.4</v>
+        <v>4.6</v>
       </c>
       <c r="G12">
-        <v>8.270086922309687</v>
+        <v>2.571437682469693</v>
       </c>
       <c r="J12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K12">
-        <v>9.770258645592461</v>
+        <v>2.571437682469693</v>
       </c>
       <c r="L12">
-        <v>4.467028425282805</v>
+        <v>3.037968256748472</v>
       </c>
       <c r="M12">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N12">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="s">
         <v>118</v>
       </c>
       <c r="P12">
-        <v>9.957671677471454</v>
+        <v>2.66858738323837</v>
       </c>
       <c r="Q12">
-        <v>1.019181992890591</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R12">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="S12" t="s">
         <v>119</v>
       </c>
       <c r="T12">
-        <v>0.1874130318789931</v>
+        <v>0.09714970076867679</v>
       </c>
       <c r="U12">
-        <v>0.04232832252854557</v>
+        <v>0.33141261676163</v>
       </c>
       <c r="V12" t="s">
         <v>96</v>
       </c>
       <c r="W12">
-        <v>8.270086922309687</v>
+        <v>2.571437682469693</v>
       </c>
       <c r="X12">
-        <v>1.500171723282774</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>0.2297413544075386</v>
+        <v>0.4285623175303068</v>
       </c>
       <c r="Z12">
-        <v>0.3358321417414752</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>0.05143046619252122</v>
+        <v>0.1410687279494473</v>
       </c>
       <c r="AB12">
-        <v>0.911638454139348</v>
+        <v>0.6604278819018417</v>
       </c>
       <c r="AC12">
-        <v>78.9550442756191</v>
+        <v>95.18250283981683</v>
       </c>
       <c r="AD12" t="s">
         <v>78</v>
@@ -1904,85 +1910,85 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
         <v>90</v>
       </c>
       <c r="C13">
-        <v>2.824</v>
+        <v>8.536</v>
       </c>
       <c r="D13">
-        <v>3.956</v>
+        <v>6.736</v>
       </c>
       <c r="E13">
-        <v>0.8437214709471421</v>
+        <v>5.242518257955137</v>
       </c>
       <c r="F13">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="G13">
-        <v>3.370351158967601</v>
+        <v>7.707244105086258</v>
       </c>
       <c r="J13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K13">
-        <v>0.8437214709471421</v>
+        <v>7.707244105086258</v>
       </c>
       <c r="L13">
-        <v>7.059923274159115</v>
+        <v>4.568878458795728</v>
       </c>
       <c r="M13">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N13">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="O13" t="s">
         <v>118</v>
       </c>
       <c r="P13">
-        <v>0.8599057302044893</v>
+        <v>7.457194256165481</v>
       </c>
       <c r="Q13">
-        <v>1.019181992890591</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S13" t="s">
         <v>119</v>
       </c>
       <c r="T13">
-        <v>0.01618425925734723</v>
+        <v>-0.250049848920777</v>
       </c>
       <c r="U13">
-        <v>0.1400942697955107</v>
+        <v>-0.4571942561654811</v>
       </c>
       <c r="V13" t="s">
         <v>96</v>
       </c>
       <c r="W13">
-        <v>3.370351158967601</v>
+        <v>7.707244105086258</v>
       </c>
       <c r="X13">
-        <v>2.526629688020459</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>0.1562785290528579</v>
+        <v>0.7072441050862581</v>
       </c>
       <c r="Z13">
-        <v>0.3578834485735112</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>0.02213600955478822</v>
+        <v>0.1547959989447114</v>
       </c>
       <c r="AB13">
-        <v>0.9289372729156731</v>
+        <v>0.6922543119387468</v>
       </c>
       <c r="AC13">
-        <v>78.63354118711212</v>
+        <v>94.72629105871258</v>
       </c>
       <c r="AD13" t="s">
         <v>78</v>
@@ -1990,85 +1996,85 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
         <v>90</v>
       </c>
       <c r="C14">
-        <v>3.444</v>
+        <v>1.064</v>
       </c>
       <c r="D14">
-        <v>4.86</v>
+        <v>1.632</v>
       </c>
       <c r="E14">
-        <v>0.2404700937671027</v>
+        <v>0.2672118870713838</v>
       </c>
       <c r="F14">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="G14">
-        <v>4.127421591076081</v>
+        <v>1.325518526839447</v>
       </c>
       <c r="J14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K14">
-        <v>0.2404700937671027</v>
+        <v>1.325518526839447</v>
       </c>
       <c r="L14">
-        <v>9.933150479214353</v>
+        <v>1.998268059200945</v>
       </c>
       <c r="M14">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N14">
-        <v>10.3</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="s">
         <v>118</v>
       </c>
       <c r="P14">
-        <v>0.2450827893961431</v>
+        <v>1.375597021497778</v>
       </c>
       <c r="Q14">
-        <v>1.019181992890591</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="s">
         <v>119</v>
       </c>
       <c r="T14">
-        <v>0.004612695629040375</v>
+        <v>0.05007849465833103</v>
       </c>
       <c r="U14">
-        <v>-0.2450827893961431</v>
+        <v>-0.3755970214977782</v>
       </c>
       <c r="V14" t="s">
         <v>96</v>
       </c>
       <c r="W14">
-        <v>4.127421591076081</v>
+        <v>1.325518526839447</v>
       </c>
       <c r="X14">
-        <v>3.886951497308978</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>0.2404700937671027</v>
+        <v>0.3255185268394472</v>
       </c>
       <c r="Z14">
-        <v>0.3913110453166527</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>0.02420884434100734</v>
+        <v>0.1629003302838227</v>
       </c>
       <c r="AB14">
-        <v>0.9643835416712964</v>
+        <v>0.8688121996525846</v>
       </c>
       <c r="AC14">
-        <v>76.8876227493331</v>
+        <v>94.45797913689444</v>
       </c>
       <c r="AD14" t="s">
         <v>78</v>
@@ -2076,85 +2082,85 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s">
         <v>90</v>
       </c>
       <c r="C15">
-        <v>7.492</v>
+        <v>173.236</v>
       </c>
       <c r="D15">
-        <v>5.94</v>
+        <v>177.628</v>
       </c>
       <c r="E15">
-        <v>5.212253933741241</v>
+        <v>196.1769522593794</v>
       </c>
       <c r="F15">
-        <v>5.8</v>
+        <v>180.6</v>
       </c>
       <c r="G15">
-        <v>6.742939047069155</v>
+        <v>175.2581643835895</v>
       </c>
       <c r="J15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K15">
-        <v>5.212253933741241</v>
+        <v>175.2581643835895</v>
       </c>
       <c r="L15">
-        <v>3.997862832988686</v>
+        <v>28.14072386543135</v>
       </c>
       <c r="M15">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N15">
-        <v>6.7</v>
+        <v>26.4</v>
       </c>
       <c r="O15" t="s">
         <v>118</v>
       </c>
       <c r="P15">
-        <v>5.11811531334273</v>
+        <v>169.5721789744432</v>
       </c>
       <c r="Q15">
-        <v>0.981938980411313</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R15">
-        <v>5</v>
+        <v>170</v>
       </c>
       <c r="S15" t="s">
         <v>119</v>
       </c>
       <c r="T15">
-        <v>-0.09413862039851129</v>
+        <v>-5.685985409146298</v>
       </c>
       <c r="U15">
-        <v>-0.11811531334273</v>
+        <v>0.4278210255567672</v>
       </c>
       <c r="V15" t="s">
         <v>96</v>
       </c>
       <c r="W15">
-        <v>6.742939047069155</v>
+        <v>175.2581643835895</v>
       </c>
       <c r="X15">
-        <v>1.530685113327914</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>0.2122539337412412</v>
+        <v>5.258164383589531</v>
       </c>
       <c r="Z15">
-        <v>0.382875845738714</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>0.05309184997289323</v>
+        <v>0.1868524920941628</v>
       </c>
       <c r="AB15">
-        <v>0.5966959452221919</v>
+        <v>1.065936510054218</v>
       </c>
       <c r="AC15">
-        <v>76.53274884974184</v>
+        <v>93.6694236066221</v>
       </c>
       <c r="AD15" t="s">
         <v>78</v>
@@ -2162,88 +2168,88 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C16">
-        <v>1.92</v>
+        <v>5.116</v>
       </c>
       <c r="D16">
-        <v>1.584</v>
+        <v>4.152</v>
       </c>
       <c r="E16">
-        <v>1.52157415011752</v>
+        <v>3.0173797501092</v>
       </c>
       <c r="F16">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="G16">
-        <v>1.762071575099091</v>
+        <v>4.67215517627953</v>
       </c>
       <c r="J16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K16">
-        <v>1.52157415011752</v>
+        <v>4.67215517627953</v>
       </c>
       <c r="L16">
-        <v>1.157976831184469</v>
+        <v>2.590285563576617</v>
       </c>
       <c r="M16">
-        <v>1.038416113387647</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N16">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="O16" t="s">
         <v>118</v>
       </c>
       <c r="P16">
-        <v>1.299486100486649</v>
+        <v>4.520574185716101</v>
       </c>
       <c r="Q16">
-        <v>0.8540406002469759</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S16" t="s">
         <v>119</v>
       </c>
       <c r="T16">
-        <v>-0.2220880496308713</v>
+        <v>-0.1515809905634287</v>
       </c>
       <c r="U16">
-        <v>-0.2994861004866491</v>
+        <v>-0.520574185716101</v>
       </c>
       <c r="V16" t="s">
         <v>96</v>
       </c>
       <c r="W16">
-        <v>1.762071575099091</v>
+        <v>4.67215517627953</v>
       </c>
       <c r="X16">
-        <v>0.2404974249815708</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>0.5215741501175204</v>
+        <v>0.6721551762795297</v>
       </c>
       <c r="Z16">
-        <v>0.2076875965951506</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>0.4504184678583023</v>
+        <v>0.2594907626136134</v>
       </c>
       <c r="AB16">
-        <v>0.8271263079889064</v>
+        <v>0.7195237676601712</v>
       </c>
       <c r="AC16">
-        <v>74.62882184844142</v>
+        <v>91.31804553655472</v>
       </c>
       <c r="AD16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2356,19 +2362,19 @@
         <v>75</v>
       </c>
       <c r="C2">
-        <v>0.4674799999999988</v>
+        <v>0.4593799999999982</v>
       </c>
       <c r="D2">
-        <v>0.4820999999999993</v>
+        <v>0.4739999999999988</v>
       </c>
       <c r="E2">
-        <v>0.4816348617949026</v>
+        <v>0.4731870983260868</v>
       </c>
       <c r="F2">
         <v>0.484</v>
       </c>
       <c r="G2">
-        <v>0.473795522482778</v>
+        <v>0.4653280968183968</v>
       </c>
       <c r="H2">
         <v>0.4472321634828965</v>
@@ -2416,16 +2422,16 @@
         <v>96</v>
       </c>
       <c r="W2">
-        <v>0.473795522482778</v>
+        <v>0.4653280968183968</v>
       </c>
       <c r="X2">
-        <v>0.02656335899988149</v>
+        <v>0.01809593333550036</v>
       </c>
       <c r="Y2">
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>2.496208154393755</v>
+        <v>1.700508446753414</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -2434,7 +2440,7 @@
         <v>0.2764021804054501</v>
       </c>
       <c r="AC2">
-        <v>19.73976019256996</v>
+        <v>33.11014383145091</v>
       </c>
       <c r="AD2" t="s">
         <v>77</v>
@@ -2442,91 +2448,85 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C3">
-        <v>0.5035359999999998</v>
+        <v>0.132</v>
       </c>
       <c r="D3">
-        <v>0.4889879999999993</v>
+        <v>0.236</v>
       </c>
       <c r="E3">
-        <v>0.4880998606769701</v>
+        <v>0.6297196965274399</v>
       </c>
       <c r="F3">
-        <v>0.4868</v>
+        <v>0.2</v>
       </c>
       <c r="G3">
-        <v>0.4972515799535244</v>
-      </c>
-      <c r="H3">
-        <v>0.5235678365171035</v>
-      </c>
-      <c r="I3">
-        <v>0.5235678365171035</v>
+        <v>0.1794951897484802</v>
       </c>
       <c r="J3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K3">
-        <v>0.5235678365171035</v>
+        <v>0.6297196965274399</v>
       </c>
       <c r="L3">
-        <v>0.01323492690170848</v>
+        <v>0.4196830443219419</v>
       </c>
       <c r="M3">
-        <v>0.01193820542365915</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N3">
-        <v>0.04170000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="O3" t="s">
         <v>118</v>
       </c>
       <c r="P3">
-        <v>0.5235678365171035</v>
+        <v>0.7759837911047821</v>
       </c>
       <c r="Q3">
+        <v>1.232268571848568</v>
+      </c>
+      <c r="R3">
         <v>1</v>
       </c>
-      <c r="R3">
-        <v>0.5235678365171035</v>
-      </c>
       <c r="S3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.1462640945773422</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.2240162088952179</v>
       </c>
       <c r="V3" t="s">
         <v>96</v>
       </c>
       <c r="W3">
-        <v>0.4972515799535244</v>
+        <v>0.1794951897484802</v>
       </c>
       <c r="X3">
-        <v>0.02631625656357905</v>
+        <v>0.4502245067789596</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>0.3702803034725601</v>
       </c>
       <c r="Z3">
-        <v>1.988394553216756</v>
+        <v>1.072772686126412</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.8822855926209767</v>
       </c>
       <c r="AB3">
-        <v>0.317384338170467</v>
+        <v>1.049207610804855</v>
       </c>
       <c r="AC3">
-        <v>27.45954213735271</v>
+        <v>36.56414014265842</v>
       </c>
       <c r="AD3" t="s">
         <v>77</v>
@@ -2534,565 +2534,571 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
         <v>91</v>
       </c>
       <c r="C4">
-        <v>0.18</v>
+        <v>1.124</v>
       </c>
       <c r="D4">
-        <v>0.264</v>
+        <v>1.14</v>
       </c>
       <c r="E4">
-        <v>0.6788079824227848</v>
+        <v>1.941748773991384</v>
       </c>
       <c r="F4">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0.2194821062252271</v>
+        <v>1.131306952268997</v>
       </c>
       <c r="J4" t="s">
         <v>94</v>
       </c>
       <c r="K4">
-        <v>0.6788079824227848</v>
+        <v>1.941748773991384</v>
       </c>
       <c r="L4">
-        <v>0.4925498319332764</v>
+        <v>0.5888547436899401</v>
       </c>
       <c r="M4">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N4">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="s">
         <v>118</v>
       </c>
       <c r="P4">
-        <v>0.7802977676584159</v>
+        <v>2.392755988615071</v>
       </c>
       <c r="Q4">
-        <v>1.149511773378675</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="s">
         <v>119</v>
       </c>
       <c r="T4">
-        <v>0.101489785235631</v>
+        <v>0.4510072146236872</v>
       </c>
       <c r="U4">
-        <v>0.2197022323415841</v>
+        <v>-0.3927559886150713</v>
       </c>
       <c r="V4" t="s">
         <v>96</v>
       </c>
       <c r="W4">
-        <v>0.2194821062252271</v>
+        <v>1.131306952268997</v>
       </c>
       <c r="X4">
-        <v>0.4593258761975577</v>
+        <v>0.8104418217223872</v>
       </c>
       <c r="Y4">
-        <v>0.3211920175772152</v>
+        <v>0.05825122600861588</v>
       </c>
       <c r="Z4">
-        <v>0.9325470163997145</v>
+        <v>1.376301762713019</v>
       </c>
       <c r="AA4">
-        <v>0.6521005525806892</v>
+        <v>0.09892291203021693</v>
       </c>
       <c r="AB4">
-        <v>1.231374579833191</v>
+        <v>1.17770948737988</v>
       </c>
       <c r="AC4">
-        <v>43.41388982372007</v>
+        <v>39.4861912039952</v>
       </c>
       <c r="AD4" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C5">
-        <v>9.932</v>
+        <v>0.5128880000000006</v>
       </c>
       <c r="D5">
-        <v>11.352</v>
+        <v>0.4971799999999998</v>
       </c>
       <c r="E5">
-        <v>12.86475247157808</v>
+        <v>0.4974436169072992</v>
       </c>
       <c r="F5">
-        <v>11.6</v>
+        <v>0.4868</v>
       </c>
       <c r="G5">
-        <v>10.59943560523598</v>
+        <v>0.5064972541160466</v>
+      </c>
+      <c r="H5">
+        <v>0.5235678365171035</v>
+      </c>
+      <c r="I5">
+        <v>0.5235678365171035</v>
       </c>
       <c r="J5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K5">
-        <v>12.86475247157808</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="L5">
-        <v>3.050242274051084</v>
+        <v>0.01323492690170848</v>
       </c>
       <c r="M5">
-        <v>1.038416113387647</v>
+        <v>0.01193820542365915</v>
       </c>
       <c r="N5">
-        <v>5.6</v>
+        <v>0.04170000000000001</v>
       </c>
       <c r="O5" t="s">
         <v>118</v>
       </c>
       <c r="P5">
-        <v>14.78818442768141</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="Q5">
-        <v>1.149511773378675</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>15</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="S5" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="T5">
-        <v>1.923431956103332</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>0.2118155723185868</v>
+        <v>0</v>
       </c>
       <c r="V5" t="s">
         <v>96</v>
       </c>
       <c r="W5">
-        <v>10.59943560523598</v>
+        <v>0.5064972541160466</v>
       </c>
       <c r="X5">
-        <v>2.265316866342099</v>
+        <v>0.01707058240105686</v>
       </c>
       <c r="Y5">
-        <v>2.135247528421919</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>0.7426678482602922</v>
+        <v>1.289813123097283</v>
       </c>
       <c r="AA5">
-        <v>0.7000255509494521</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.544686120366265</v>
+        <v>0.317384338170467</v>
       </c>
       <c r="AC5">
-        <v>48.29978656895716</v>
+        <v>43.24110969117353</v>
       </c>
       <c r="AD5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
         <v>91</v>
       </c>
       <c r="C6">
-        <v>1.604</v>
+        <v>14.476</v>
       </c>
       <c r="D6">
-        <v>1.924</v>
+        <v>13.084</v>
       </c>
       <c r="E6">
-        <v>-0.1313628720128142</v>
+        <v>12.1475539711821</v>
       </c>
       <c r="F6">
-        <v>2.4</v>
+        <v>12.4</v>
       </c>
       <c r="G6">
-        <v>1.754408023715151</v>
+        <v>13.84029515259726</v>
       </c>
       <c r="J6" t="s">
         <v>94</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>12.1475539711821</v>
       </c>
       <c r="L6">
-        <v>1.736334852416627</v>
+        <v>2.777213034732671</v>
       </c>
       <c r="M6">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="s">
         <v>118</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>9.555673875500363</v>
       </c>
       <c r="Q6">
-        <v>0.8540406002469759</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S6" t="s">
         <v>119</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>-2.591880095681738</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>-0.5556738755003625</v>
       </c>
       <c r="V6" t="s">
         <v>96</v>
       </c>
       <c r="W6">
-        <v>1.754408023715151</v>
+        <v>13.84029515259726</v>
       </c>
       <c r="X6">
-        <v>1.754408023715151</v>
+        <v>1.692741181415164</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>3.1475539711821</v>
       </c>
       <c r="Z6">
-        <v>1.010408805233259</v>
+        <v>0.6095107434126327</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.133349848145545</v>
       </c>
       <c r="AB6">
-        <v>0.5601080169085895</v>
+        <v>0.7714480652035196</v>
       </c>
       <c r="AC6">
-        <v>51.85256808577751</v>
+        <v>45.25511742057672</v>
       </c>
       <c r="AD6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
         <v>91</v>
       </c>
       <c r="C7">
-        <v>13.288</v>
+        <v>0.764</v>
       </c>
       <c r="D7">
-        <v>12.416</v>
+        <v>0.532</v>
       </c>
       <c r="E7">
-        <v>11.45044534583586</v>
+        <v>0.4302454583585212</v>
       </c>
       <c r="F7">
-        <v>12.4</v>
+        <v>0.4</v>
       </c>
       <c r="G7">
-        <v>12.87813813537621</v>
+        <v>0.6580491920995442</v>
       </c>
       <c r="J7" t="s">
         <v>94</v>
       </c>
       <c r="K7">
-        <v>11.45044534583586</v>
+        <v>0.4302454583585212</v>
       </c>
       <c r="L7">
-        <v>2.351026032651849</v>
+        <v>0.4552884680086201</v>
       </c>
       <c r="M7">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="O7" t="s">
         <v>118</v>
       </c>
       <c r="P7">
-        <v>9.779145216252848</v>
+        <v>0.5301779565157876</v>
       </c>
       <c r="Q7">
-        <v>0.8540406002469759</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S7" t="s">
         <v>119</v>
       </c>
       <c r="T7">
-        <v>-1.671300129583011</v>
+        <v>0.09993249815726635</v>
       </c>
       <c r="U7">
-        <v>0.2208547837471517</v>
+        <v>0.4698220434842124</v>
       </c>
       <c r="V7" t="s">
         <v>96</v>
       </c>
       <c r="W7">
-        <v>12.87813813537621</v>
+        <v>0.6580491920995442</v>
       </c>
       <c r="X7">
-        <v>1.427692789540352</v>
+        <v>0.2278037337410229</v>
       </c>
       <c r="Y7">
-        <v>1.45044534583586</v>
+        <v>0.5697545416414788</v>
       </c>
       <c r="Z7">
-        <v>0.6072637094239147</v>
+        <v>0.5003503267662599</v>
       </c>
       <c r="AA7">
-        <v>0.6169414228900835</v>
+        <v>1.251414392579545</v>
       </c>
       <c r="AB7">
-        <v>0.6530627868477359</v>
+        <v>0.7588141133477002</v>
       </c>
       <c r="AC7">
-        <v>54.29973121083951</v>
+        <v>46.61616811374733</v>
       </c>
       <c r="AD7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8">
-        <v>13.548</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="D8">
-        <v>14.728</v>
+        <v>10.476</v>
       </c>
       <c r="E8">
-        <v>18.83927196478475</v>
+        <v>11.06324335018592</v>
       </c>
       <c r="F8">
-        <v>14.6</v>
+        <v>11.6</v>
       </c>
       <c r="G8">
-        <v>14.1175179925634</v>
+        <v>9.232894174466566</v>
       </c>
       <c r="J8" t="s">
         <v>94</v>
       </c>
       <c r="K8">
-        <v>18.83927196478475</v>
+        <v>11.06324335018592</v>
       </c>
       <c r="L8">
-        <v>5.333756871724871</v>
+        <v>3.004822768461589</v>
       </c>
       <c r="M8">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N8">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="s">
         <v>118</v>
       </c>
       <c r="P8">
-        <v>19.20064674567716</v>
+        <v>13.63288708314677</v>
       </c>
       <c r="Q8">
-        <v>1.019181992890591</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R8">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="S8" t="s">
         <v>119</v>
       </c>
       <c r="T8">
-        <v>0.3613747808924153</v>
+        <v>2.569643732960854</v>
       </c>
       <c r="U8">
-        <v>-0.2006467456771617</v>
+        <v>0.3671129168532268</v>
       </c>
       <c r="V8" t="s">
         <v>96</v>
       </c>
       <c r="W8">
-        <v>14.1175179925634</v>
+        <v>9.232894174466566</v>
       </c>
       <c r="X8">
-        <v>4.721753972221347</v>
+        <v>1.830349175719354</v>
       </c>
       <c r="Y8">
-        <v>0.1607280352152536</v>
+        <v>2.936756649814081</v>
       </c>
       <c r="Z8">
-        <v>0.8852585683558519</v>
+        <v>0.6091371494287687</v>
       </c>
       <c r="AA8">
-        <v>0.03013411354898824</v>
+        <v>0.977347709368444</v>
       </c>
       <c r="AB8">
-        <v>1.088521810556096</v>
+        <v>0.536575494368141</v>
       </c>
       <c r="AC8">
-        <v>55.65685088619063</v>
+        <v>47.8063913390236</v>
       </c>
       <c r="AD8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
         <v>91</v>
       </c>
       <c r="C9">
-        <v>1.12</v>
+        <v>0.228</v>
       </c>
       <c r="D9">
-        <v>1.168</v>
+        <v>0.372</v>
       </c>
       <c r="E9">
-        <v>1.780416614874208</v>
+        <v>0.8817836191054232</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G9">
-        <v>1.142561203557273</v>
+        <v>0.2937625704209726</v>
       </c>
       <c r="J9" t="s">
         <v>94</v>
       </c>
       <c r="K9">
-        <v>1.780416614874208</v>
+        <v>0.8817836191054232</v>
       </c>
       <c r="L9">
-        <v>0.8500971208676269</v>
+        <v>0.7453408782506382</v>
       </c>
       <c r="M9">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N9">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O9" t="s">
         <v>118</v>
       </c>
       <c r="P9">
-        <v>2.046609860316908</v>
+        <v>0.6936406055835702</v>
       </c>
       <c r="Q9">
-        <v>1.149511773378675</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" t="s">
         <v>119</v>
       </c>
       <c r="T9">
-        <v>0.2661932454427003</v>
+        <v>-0.188143013521853</v>
       </c>
       <c r="U9">
-        <v>-0.04660986031690806</v>
+        <v>0.3063593944164298</v>
       </c>
       <c r="V9" t="s">
         <v>96</v>
       </c>
       <c r="W9">
-        <v>1.142561203557273</v>
+        <v>0.2937625704209726</v>
       </c>
       <c r="X9">
-        <v>0.6378554113169352</v>
+        <v>0.5880210486844506</v>
       </c>
       <c r="Y9">
-        <v>0.2195833851257922</v>
+        <v>0.1182163808945768</v>
       </c>
       <c r="Z9">
-        <v>0.7503323980981451</v>
+        <v>0.7889290200539824</v>
       </c>
       <c r="AA9">
-        <v>0.2583038805044779</v>
+        <v>0.1586071344591189</v>
       </c>
       <c r="AB9">
-        <v>1.700194241735254</v>
+        <v>1.242234797084397</v>
       </c>
       <c r="AC9">
-        <v>56.09506097814787</v>
+        <v>56.64783818764582</v>
       </c>
       <c r="AD9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
         <v>91</v>
       </c>
       <c r="C10">
-        <v>0.5600000000000001</v>
+        <v>0.328</v>
       </c>
       <c r="D10">
-        <v>0.408</v>
+        <v>0.212</v>
       </c>
       <c r="E10">
-        <v>0.3147916000487194</v>
+        <v>-0.001836660305252591</v>
       </c>
       <c r="F10">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G10">
-        <v>0.4885561887353032</v>
+        <v>0.275024596049772</v>
       </c>
       <c r="J10" t="s">
         <v>94</v>
       </c>
       <c r="K10">
-        <v>0.3147916000487194</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>0.3921195507989373</v>
+        <v>0.4029126890988887</v>
       </c>
       <c r="M10">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N10">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="O10" t="s">
         <v>118</v>
       </c>
       <c r="P10">
-        <v>0.3618566504167141</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.149511773378675</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3101,84 +3107,84 @@
         <v>119</v>
       </c>
       <c r="T10">
-        <v>0.04706505036799469</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>-0.3618566504167141</v>
+        <v>0</v>
       </c>
       <c r="V10" t="s">
         <v>96</v>
       </c>
       <c r="W10">
-        <v>0.4885561887353032</v>
+        <v>0.275024596049772</v>
       </c>
       <c r="X10">
-        <v>0.1737645886865837</v>
+        <v>0.275024596049772</v>
       </c>
       <c r="Y10">
-        <v>0.3147916000487194</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>0.4431418640884933</v>
+        <v>0.682591051338846</v>
       </c>
       <c r="AA10">
-        <v>0.8027949624223952</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.6535325846648956</v>
+        <v>1.007281722747221</v>
       </c>
       <c r="AC10">
-        <v>56.60796713936882</v>
+        <v>64.16680382679213</v>
       </c>
       <c r="AD10" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
         <v>91</v>
       </c>
       <c r="C11">
-        <v>0.74</v>
+        <v>2.432</v>
       </c>
       <c r="D11">
-        <v>0.672</v>
+        <v>1.928</v>
       </c>
       <c r="E11">
-        <v>0.9935995824715044</v>
+        <v>1.608426994139059</v>
       </c>
       <c r="F11">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="G11">
-        <v>0.7080382949605304</v>
+        <v>2.201831003526596</v>
       </c>
       <c r="J11" t="s">
         <v>94</v>
       </c>
       <c r="K11">
-        <v>0.9935995824715044</v>
+        <v>1.608426994139059</v>
       </c>
       <c r="L11">
-        <v>0.3332002265469857</v>
+        <v>1.357115480819956</v>
       </c>
       <c r="M11">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N11">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="O11" t="s">
         <v>118</v>
       </c>
       <c r="P11">
-        <v>1.14215441807513</v>
+        <v>1.265242685482676</v>
       </c>
       <c r="Q11">
-        <v>1.149511773378675</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -3187,206 +3193,206 @@
         <v>119</v>
       </c>
       <c r="T11">
-        <v>0.1485548356036258</v>
+        <v>-0.3431843086563835</v>
       </c>
       <c r="U11">
-        <v>-0.1421544180751302</v>
+        <v>-0.2652426854826757</v>
       </c>
       <c r="V11" t="s">
         <v>96</v>
       </c>
       <c r="W11">
-        <v>0.7080382949605304</v>
+        <v>2.201831003526596</v>
       </c>
       <c r="X11">
-        <v>0.285561287510974</v>
+        <v>0.5934040093875366</v>
       </c>
       <c r="Y11">
-        <v>0.006400417528495628</v>
+        <v>0.6084269941390592</v>
       </c>
       <c r="Z11">
-        <v>0.8570260904990893</v>
+        <v>0.4372538798459565</v>
       </c>
       <c r="AA11">
-        <v>0.01920892309955583</v>
+        <v>0.4483236708577323</v>
       </c>
       <c r="AB11">
-        <v>0.5553337109116429</v>
+        <v>0.9693682005856831</v>
       </c>
       <c r="AC11">
-        <v>56.90482321607101</v>
+        <v>64.33101602736564</v>
       </c>
       <c r="AD11" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12">
-        <v>1.904</v>
+        <v>0.752</v>
       </c>
       <c r="D12">
-        <v>1.796</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E12">
-        <v>2.604250820161925</v>
+        <v>0.2483906019674781</v>
       </c>
       <c r="F12">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="G12">
-        <v>1.851874624409452</v>
+        <v>0.6643165727720365</v>
       </c>
       <c r="J12" t="s">
         <v>94</v>
       </c>
       <c r="K12">
-        <v>2.604250820161925</v>
+        <v>0.2483906019674781</v>
       </c>
       <c r="L12">
-        <v>1.198624596172324</v>
+        <v>0.9284964811104729</v>
       </c>
       <c r="M12">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N12">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="O12" t="s">
         <v>118</v>
       </c>
       <c r="P12">
-        <v>2.557215395085126</v>
+        <v>0.1953923886052483</v>
       </c>
       <c r="Q12">
-        <v>0.981938980411313</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="s">
         <v>119</v>
       </c>
       <c r="T12">
-        <v>-0.04703542507679881</v>
+        <v>-0.05299821336222987</v>
       </c>
       <c r="U12">
-        <v>0.4427846049148738</v>
+        <v>-0.1953923886052483</v>
       </c>
       <c r="V12" t="s">
         <v>96</v>
       </c>
       <c r="W12">
-        <v>1.851874624409452</v>
+        <v>0.6643165727720365</v>
       </c>
       <c r="X12">
-        <v>0.7523761957524733</v>
+        <v>0.4159259708045583</v>
       </c>
       <c r="Y12">
-        <v>0.395749179838075</v>
+        <v>0.2483906019674781</v>
       </c>
       <c r="Z12">
-        <v>0.6276996135029299</v>
+        <v>0.4479564320018907</v>
       </c>
       <c r="AA12">
-        <v>0.3301694134275707</v>
+        <v>0.2675191635302757</v>
       </c>
       <c r="AB12">
-        <v>0.7491403726077025</v>
+        <v>1.031662756789414</v>
       </c>
       <c r="AC12">
-        <v>59.24054223283283</v>
+        <v>68.05844340927169</v>
       </c>
       <c r="AD12" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13">
-        <v>8.763999999999999</v>
+        <v>0.896</v>
       </c>
       <c r="D13">
-        <v>6.752</v>
+        <v>0.768</v>
       </c>
       <c r="E13">
-        <v>4.301787319744047</v>
+        <v>1.059965154885961</v>
       </c>
       <c r="F13">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="G13">
-        <v>7.792923558442745</v>
+        <v>0.8375443818480244</v>
       </c>
       <c r="J13" t="s">
         <v>94</v>
       </c>
       <c r="K13">
-        <v>4.301787319744047</v>
+        <v>1.059965154885961</v>
       </c>
       <c r="L13">
-        <v>4.673523904256721</v>
+        <v>0.4515884075301241</v>
       </c>
       <c r="M13">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N13">
-        <v>8.4</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="s">
         <v>118</v>
       </c>
       <c r="P13">
-        <v>4.224092654695784</v>
+        <v>1.30616174762057</v>
       </c>
       <c r="Q13">
-        <v>0.981938980411313</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S13" t="s">
         <v>119</v>
       </c>
       <c r="T13">
-        <v>-0.07769466504826283</v>
+        <v>0.2461965927346088</v>
       </c>
       <c r="U13">
-        <v>-0.2240926546957844</v>
+        <v>-0.3061617476205698</v>
       </c>
       <c r="V13" t="s">
         <v>96</v>
       </c>
       <c r="W13">
-        <v>7.792923558442745</v>
+        <v>0.8375443818480244</v>
       </c>
       <c r="X13">
-        <v>3.491136238698697</v>
+        <v>0.2224207730379366</v>
       </c>
       <c r="Y13">
-        <v>0.3017873197440473</v>
+        <v>0.05996515488596099</v>
       </c>
       <c r="Z13">
-        <v>0.747002970396474</v>
+        <v>0.4925298553486442</v>
       </c>
       <c r="AA13">
-        <v>0.06457382607354901</v>
+        <v>0.1327871882582834</v>
       </c>
       <c r="AB13">
-        <v>0.5563718933638954</v>
+        <v>0.7526473458835402</v>
       </c>
       <c r="AC13">
-        <v>60.16058574846904</v>
+        <v>69.3073016888561</v>
       </c>
       <c r="AD13" t="s">
         <v>79</v>
@@ -3394,85 +3400,85 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C14">
-        <v>173.496</v>
+        <v>0.856</v>
       </c>
       <c r="D14">
-        <v>170.784</v>
+        <v>1.468</v>
       </c>
       <c r="E14">
-        <v>173.6497555759981</v>
+        <v>-0.6136915121990012</v>
       </c>
       <c r="F14">
-        <v>169.2</v>
+        <v>2.4</v>
       </c>
       <c r="G14">
-        <v>172.1870739018374</v>
+        <v>1.135490924289134</v>
       </c>
       <c r="J14" t="s">
         <v>94</v>
       </c>
       <c r="K14">
-        <v>173.6497555759981</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>4.764861070548267</v>
+        <v>2.225665663703473</v>
       </c>
       <c r="M14">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N14">
-        <v>13.2</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="s">
         <v>118</v>
       </c>
       <c r="P14">
-        <v>176.9807039529099</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>1.019181992890591</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R14">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="S14" t="s">
         <v>119</v>
       </c>
       <c r="T14">
-        <v>3.330948376911721</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>0.01929604709013688</v>
+        <v>0</v>
       </c>
       <c r="V14" t="s">
         <v>96</v>
       </c>
       <c r="W14">
-        <v>172.1870739018374</v>
+        <v>1.135490924289134</v>
       </c>
       <c r="X14">
-        <v>1.462681674160791</v>
+        <v>1.135490924289134</v>
       </c>
       <c r="Y14">
-        <v>3.350244424001858</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>0.3069725753814032</v>
+        <v>0.5101803666233026</v>
       </c>
       <c r="AA14">
-        <v>0.7031148179135396</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.3609743235263839</v>
+        <v>0.7179566657107976</v>
       </c>
       <c r="AC14">
-        <v>64.04255765445993</v>
+        <v>71.77620020831648</v>
       </c>
       <c r="AD14" t="s">
         <v>79</v>
@@ -3480,37 +3486,37 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
         <v>91</v>
       </c>
       <c r="C15">
-        <v>0.6879999999999999</v>
+        <v>1.032</v>
       </c>
       <c r="D15">
-        <v>0.608</v>
+        <v>1.224</v>
       </c>
       <c r="E15">
-        <v>-0.01550360442781762</v>
+        <v>0.883771840094469</v>
       </c>
       <c r="F15">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="G15">
-        <v>0.6503979940712121</v>
+        <v>1.119683427227963</v>
       </c>
       <c r="J15" t="s">
         <v>94</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>0.883771840094469</v>
       </c>
       <c r="L15">
-        <v>1.005444112310955</v>
+        <v>0.9957719791398976</v>
       </c>
       <c r="M15">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N15">
         <v>0.9</v>
@@ -3519,96 +3525,96 @@
         <v>118</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>0.6952046069791448</v>
       </c>
       <c r="Q15">
-        <v>0.8540406002469759</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="s">
         <v>119</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>-0.1885672331153242</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>0.3047953930208552</v>
       </c>
       <c r="V15" t="s">
         <v>96</v>
       </c>
       <c r="W15">
-        <v>0.6503979940712121</v>
+        <v>1.119683427227963</v>
       </c>
       <c r="X15">
-        <v>0.6503979940712121</v>
+        <v>0.2359115871334945</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>0.116228159905531</v>
       </c>
       <c r="Z15">
-        <v>0.6468763266973739</v>
+        <v>0.2369132613444939</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>0.1167216615252858</v>
       </c>
       <c r="AB15">
-        <v>1.117160124789949</v>
+        <v>1.106413310155442</v>
       </c>
       <c r="AC15">
-        <v>65.67383349516004</v>
+        <v>82.29612186002319</v>
       </c>
       <c r="AD15" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
       </c>
       <c r="C16">
-        <v>0.38</v>
+        <v>0.288</v>
       </c>
       <c r="D16">
-        <v>0.496</v>
+        <v>0.408</v>
       </c>
       <c r="E16">
-        <v>0.7868170324027036</v>
+        <v>0.7561917677339507</v>
       </c>
       <c r="F16">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G16">
-        <v>0.4345229085967423</v>
+        <v>0.3428021420174772</v>
       </c>
       <c r="J16" t="s">
         <v>94</v>
       </c>
       <c r="K16">
-        <v>0.7868170324027036</v>
+        <v>0.7561917677339507</v>
       </c>
       <c r="L16">
-        <v>0.8079772006265793</v>
+        <v>1.908933484234525</v>
       </c>
       <c r="M16">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N16">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="O16" t="s">
         <v>118</v>
       </c>
       <c r="P16">
-        <v>0.6719736906377493</v>
+        <v>0.5948458378489989</v>
       </c>
       <c r="Q16">
-        <v>0.8540406002469759</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -3617,37 +3623,37 @@
         <v>119</v>
       </c>
       <c r="T16">
-        <v>-0.1148433417649544</v>
+        <v>-0.1613459298849518</v>
       </c>
       <c r="U16">
-        <v>0.3280263093622507</v>
+        <v>0.4051541621510011</v>
       </c>
       <c r="V16" t="s">
         <v>96</v>
       </c>
       <c r="W16">
-        <v>0.4345229085967423</v>
+        <v>0.3428021420174772</v>
       </c>
       <c r="X16">
-        <v>0.3522941238059614</v>
+        <v>0.4133896257164735</v>
       </c>
       <c r="Y16">
-        <v>0.2131829675972964</v>
+        <v>0.2438082322660493</v>
       </c>
       <c r="Z16">
-        <v>0.4360198821609822</v>
+        <v>0.2165552802811467</v>
       </c>
       <c r="AA16">
-        <v>0.2638477514365193</v>
+        <v>0.1277196058844426</v>
       </c>
       <c r="AB16">
-        <v>1.346628667710966</v>
+        <v>1.590777903528771</v>
       </c>
       <c r="AC16">
-        <v>68.6767387081441</v>
+        <v>83.07197425634185</v>
       </c>
       <c r="AD16" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -3742,22 +3748,22 @@
         <v>33</v>
       </c>
       <c r="B2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>-8</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3812,13 +3818,13 @@
         <v>39</v>
       </c>
       <c r="B2">
-        <v>0.966548112280941</v>
+        <v>1.351825510892524</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.01491156870087162</v>
+        <v>-0.4028978914405681</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3826,13 +3832,13 @@
         <v>40</v>
       </c>
       <c r="B3">
-        <v>1.473024875335867</v>
+        <v>1.325518526839447</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>0.4987195719777766</v>
+        <v>-0.3755970214977782</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3840,13 +3846,13 @@
         <v>41</v>
       </c>
       <c r="B4">
-        <v>9.770258645592461</v>
+        <v>4.844607231094189</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>0.04232832252854557</v>
+        <v>-0.02763797146606439</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3854,13 +3860,13 @@
         <v>42</v>
       </c>
       <c r="B5">
-        <v>5.170440884727479</v>
+        <v>2.571437682469693</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>-0.269620245019544</v>
+        <v>0.33141261676163</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3868,13 +3874,13 @@
         <v>43</v>
       </c>
       <c r="B6">
-        <v>18.83927196478475</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>-0.2006467456771617</v>
+        <v>0.2282296274527074</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3882,13 +3888,13 @@
         <v>44</v>
       </c>
       <c r="B7">
-        <v>0.8437214709471421</v>
+        <v>2.684613743554167</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>0.1400942697955107</v>
+        <v>0.2139607295338708</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3896,13 +3902,13 @@
         <v>45</v>
       </c>
       <c r="B8">
-        <v>173.6497555759981</v>
+        <v>181.348317089571</v>
       </c>
       <c r="C8">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="D8">
-        <v>0.01929604709013688</v>
+        <v>-0.1997118794436403</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3910,13 +3916,13 @@
         <v>46</v>
       </c>
       <c r="B9">
-        <v>0.2404700937671027</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>-0.2450827893961431</v>
+        <v>0.2322417900998337</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3924,13 +3930,13 @@
         <v>47</v>
       </c>
       <c r="B10">
-        <v>3.656634670288002</v>
+        <v>3.875948349424152</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10">
-        <v>0.409407880120741</v>
+        <v>0.24980091788641</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3938,13 +3944,13 @@
         <v>48</v>
       </c>
       <c r="B11">
-        <v>2.604250820161925</v>
+        <v>2.076807770041576</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>0.4427846049148738</v>
+        <v>-0.009428890891545194</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3952,13 +3958,13 @@
         <v>49</v>
       </c>
       <c r="B12">
-        <v>13.3559567781861</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="C12">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D12">
-        <v>-0.1147345811896248</v>
+        <v>0.04754139896378362</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3966,13 +3972,13 @@
         <v>50</v>
       </c>
       <c r="B13">
-        <v>4.301787319744047</v>
+        <v>9.231825735444511</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>-0.2240926546957844</v>
+        <v>0.06768685283428155</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3980,13 +3986,13 @@
         <v>51</v>
       </c>
       <c r="B14">
-        <v>15.0529980979447</v>
+        <v>13.23504379069086</v>
       </c>
       <c r="C14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D14">
-        <v>0.2188743955707473</v>
+        <v>0.1943471375318673</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3994,13 +4000,13 @@
         <v>52</v>
       </c>
       <c r="B15">
-        <v>5.212253933741241</v>
+        <v>7.707244105086258</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>-0.11811531334273</v>
+        <v>-0.4571942561654811</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4008,13 +4014,13 @@
         <v>53</v>
       </c>
       <c r="B16">
-        <v>175.5728436009487</v>
+        <v>175.2581643835895</v>
       </c>
       <c r="C16">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D16">
-        <v>-0.4018190334304563</v>
+        <v>0.4278210255567672</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4022,13 +4028,13 @@
         <v>54</v>
       </c>
       <c r="B17">
-        <v>4.289783155551396</v>
+        <v>4.67215517627953</v>
       </c>
       <c r="C17">
         <v>4</v>
       </c>
       <c r="D17">
-        <v>-0.2123052979477622</v>
+        <v>-0.520574185716101</v>
       </c>
     </row>
   </sheetData>
@@ -4060,13 +4066,13 @@
         <v>55</v>
       </c>
       <c r="B2">
-        <v>0.7868170324027036</v>
+        <v>0.8817836191054232</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.3280263093622507</v>
+        <v>0.3063593944164298</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4088,13 +4094,13 @@
         <v>57</v>
       </c>
       <c r="B4">
-        <v>1.138895095514905</v>
+        <v>0.883771840094469</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>0.02733734900811324</v>
+        <v>0.3047953930208552</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4102,13 +4108,13 @@
         <v>58</v>
       </c>
       <c r="B5">
-        <v>0.3240271499397565</v>
+        <v>0.7561917677339507</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>-0.2767323416308665</v>
+        <v>0.4051541621510011</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4116,13 +4122,13 @@
         <v>59</v>
       </c>
       <c r="B6">
-        <v>1.52157415011752</v>
+        <v>1.608426994139059</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>-0.2994861004866491</v>
+        <v>-0.2652426854826757</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4130,13 +4136,13 @@
         <v>60</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.2483906019674781</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-0.1953923886052483</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4144,13 +4150,13 @@
         <v>61</v>
       </c>
       <c r="B8">
-        <v>11.45044534583586</v>
+        <v>12.1475539711821</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>0.2208547837471517</v>
+        <v>-0.5556738755003625</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4172,13 +4178,13 @@
         <v>63</v>
       </c>
       <c r="B10">
-        <v>0.6788079824227848</v>
+        <v>0.6297196965274399</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>0.2197022323415841</v>
+        <v>0.2240162088952179</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4186,13 +4192,13 @@
         <v>64</v>
       </c>
       <c r="B11">
-        <v>0.7530958545051754</v>
+        <v>0.8641642373275472</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.1343074487636272</v>
+        <v>-0.06488243057422394</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -4206,7 +4212,7 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>-0.1495117733786751</v>
+        <v>-0.2322685718485682</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4214,13 +4220,13 @@
         <v>66</v>
       </c>
       <c r="B13">
-        <v>0.9935995824715044</v>
+        <v>1.059965154885961</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>-0.1421544180751302</v>
+        <v>-0.3061617476205698</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4228,13 +4234,13 @@
         <v>67</v>
       </c>
       <c r="B14">
-        <v>1.780416614874208</v>
+        <v>1.941748773991384</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14">
-        <v>-0.04660986031690806</v>
+        <v>-0.3927559886150713</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4242,13 +4248,13 @@
         <v>68</v>
       </c>
       <c r="B15">
-        <v>0.3147916000487194</v>
+        <v>0.4302454583585212</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>-0.3618566504167141</v>
+        <v>0.4698220434842124</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4256,13 +4262,13 @@
         <v>69</v>
       </c>
       <c r="B16">
-        <v>12.86475247157808</v>
+        <v>11.06324335018592</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16">
-        <v>0.2118155723185868</v>
+        <v>0.3671129168532268</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4270,13 +4276,13 @@
         <v>70</v>
       </c>
       <c r="B17">
-        <v>0.7530958545051754</v>
+        <v>0.8641642373275472</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>0.1343074487636272</v>
+        <v>-0.06488243057422394</v>
       </c>
     </row>
   </sheetData>
@@ -4308,7 +4314,7 @@
         <v>75</v>
       </c>
       <c r="B2">
-        <v>23.6</v>
+        <v>38.176</v>
       </c>
       <c r="C2" t="s">
         <v>77</v>
@@ -4322,7 +4328,7 @@
         <v>33</v>
       </c>
       <c r="B3">
-        <v>77.158</v>
+        <v>95.55800000000001</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -4336,7 +4342,7 @@
         <v>34</v>
       </c>
       <c r="B4">
-        <v>66.666</v>
+        <v>65.32599999999999</v>
       </c>
       <c r="C4" t="s">
         <v>79</v>
@@ -4391,16 +4397,16 @@
         <v>90</v>
       </c>
       <c r="B2">
-        <v>77.158</v>
+        <v>95.55800000000001</v>
       </c>
       <c r="C2">
-        <v>1.549</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0.65</v>
+        <v>1.05</v>
       </c>
       <c r="E2">
-        <v>5.247</v>
+        <v>6.526</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4408,10 +4414,10 @@
         <v>75</v>
       </c>
       <c r="B3">
-        <v>23.6</v>
+        <v>38.176</v>
       </c>
       <c r="C3">
-        <v>0.026</v>
+        <v>0.018</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -4425,16 +4431,16 @@
         <v>91</v>
       </c>
       <c r="B4">
-        <v>66.666</v>
+        <v>65.32599999999999</v>
       </c>
       <c r="C4">
-        <v>0.582</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="D4">
-        <v>0.384</v>
+        <v>0.547</v>
       </c>
       <c r="E4">
-        <v>1.038</v>
+        <v>1.101</v>
       </c>
     </row>
   </sheetData>
@@ -4541,429 +4547,429 @@
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
         <v>90</v>
       </c>
       <c r="C2">
-        <v>171.868</v>
+        <v>183.632</v>
       </c>
       <c r="D2">
-        <v>174.552</v>
+        <v>178.672</v>
       </c>
       <c r="E2">
-        <v>175.5728436009487</v>
+        <v>184.2285869624531</v>
       </c>
       <c r="F2">
         <v>172.6</v>
       </c>
       <c r="G2">
-        <v>173.1634121118985</v>
+        <v>181.348317089571</v>
       </c>
       <c r="J2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K2">
-        <v>175.5728436009487</v>
+        <v>181.348317089571</v>
       </c>
       <c r="L2">
-        <v>24.70132137894479</v>
+        <v>14.61847816170942</v>
       </c>
       <c r="M2">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N2">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="O2" t="s">
         <v>118</v>
       </c>
       <c r="P2">
-        <v>172.4018190334305</v>
+        <v>188.1997118794436</v>
       </c>
       <c r="Q2">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R2">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="S2" t="s">
         <v>119</v>
       </c>
       <c r="T2">
-        <v>-3.171024567518231</v>
+        <v>6.851394789872614</v>
       </c>
       <c r="U2">
-        <v>-0.4018190334304563</v>
+        <v>-0.1997118794436403</v>
       </c>
       <c r="V2" t="s">
         <v>96</v>
       </c>
       <c r="W2">
-        <v>173.1634121118985</v>
+        <v>181.348317089571</v>
       </c>
       <c r="X2">
-        <v>2.409431489050235</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>3.572843600948687</v>
+        <v>6.651682910428974</v>
       </c>
       <c r="Z2">
-        <v>0.09754261531547112</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>0.1446418005797111</v>
+        <v>0.4550188355345981</v>
       </c>
       <c r="AB2">
-        <v>1.320926276948919</v>
+        <v>0.7734644530004987</v>
       </c>
       <c r="AC2">
-        <v>89.22335706647648</v>
+        <v>85.27775146326397</v>
       </c>
       <c r="AD2" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
         <v>90</v>
       </c>
       <c r="C3">
-        <v>173.496</v>
+        <v>173.236</v>
       </c>
       <c r="D3">
-        <v>170.784</v>
+        <v>177.628</v>
       </c>
       <c r="E3">
-        <v>173.6497555759981</v>
+        <v>196.1769522593794</v>
       </c>
       <c r="F3">
-        <v>169.2</v>
+        <v>180.6</v>
       </c>
       <c r="G3">
-        <v>172.1870739018374</v>
+        <v>175.2581643835895</v>
       </c>
       <c r="J3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K3">
-        <v>173.6497555759981</v>
+        <v>175.2581643835895</v>
       </c>
       <c r="L3">
-        <v>4.764861070548267</v>
+        <v>28.14072386543135</v>
       </c>
       <c r="M3">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N3">
-        <v>13.2</v>
+        <v>26.4</v>
       </c>
       <c r="O3" t="s">
         <v>118</v>
       </c>
       <c r="P3">
-        <v>176.9807039529099</v>
+        <v>169.5721789744432</v>
       </c>
       <c r="Q3">
-        <v>1.019181992890591</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R3">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="S3" t="s">
         <v>119</v>
       </c>
       <c r="T3">
-        <v>3.330948376911721</v>
+        <v>-5.685985409146298</v>
       </c>
       <c r="U3">
-        <v>0.01929604709013688</v>
+        <v>0.4278210255567672</v>
       </c>
       <c r="V3" t="s">
         <v>96</v>
       </c>
       <c r="W3">
-        <v>172.1870739018374</v>
+        <v>175.2581643835895</v>
       </c>
       <c r="X3">
-        <v>1.462681674160791</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>3.350244424001858</v>
+        <v>5.258164383589531</v>
       </c>
       <c r="Z3">
-        <v>0.3069725753814032</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.7031148179135396</v>
+        <v>0.1868524920941628</v>
       </c>
       <c r="AB3">
-        <v>0.3609743235263839</v>
+        <v>1.065936510054218</v>
       </c>
       <c r="AC3">
-        <v>64.04255765445993</v>
+        <v>93.6694236066221</v>
       </c>
       <c r="AD3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
         <v>91</v>
       </c>
       <c r="C4">
-        <v>9.932</v>
+        <v>14.476</v>
       </c>
       <c r="D4">
-        <v>11.352</v>
+        <v>13.084</v>
       </c>
       <c r="E4">
-        <v>12.86475247157808</v>
+        <v>12.1475539711821</v>
       </c>
       <c r="F4">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="G4">
-        <v>10.59943560523598</v>
+        <v>13.84029515259726</v>
       </c>
       <c r="J4" t="s">
         <v>94</v>
       </c>
       <c r="K4">
-        <v>12.86475247157808</v>
+        <v>12.1475539711821</v>
       </c>
       <c r="L4">
-        <v>3.050242274051084</v>
+        <v>2.777213034732671</v>
       </c>
       <c r="M4">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N4">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="s">
         <v>118</v>
       </c>
       <c r="P4">
-        <v>14.78818442768141</v>
+        <v>9.555673875500363</v>
       </c>
       <c r="Q4">
-        <v>1.149511773378675</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="S4" t="s">
         <v>119</v>
       </c>
       <c r="T4">
-        <v>1.923431956103332</v>
+        <v>-2.591880095681738</v>
       </c>
       <c r="U4">
-        <v>0.2118155723185868</v>
+        <v>-0.5556738755003625</v>
       </c>
       <c r="V4" t="s">
         <v>96</v>
       </c>
       <c r="W4">
-        <v>10.59943560523598</v>
+        <v>13.84029515259726</v>
       </c>
       <c r="X4">
-        <v>2.265316866342099</v>
+        <v>1.692741181415164</v>
       </c>
       <c r="Y4">
-        <v>2.135247528421919</v>
+        <v>3.1475539711821</v>
       </c>
       <c r="Z4">
-        <v>0.7426678482602922</v>
+        <v>0.6095107434126327</v>
       </c>
       <c r="AA4">
-        <v>0.7000255509494521</v>
+        <v>1.133349848145545</v>
       </c>
       <c r="AB4">
-        <v>0.544686120366265</v>
+        <v>0.7714480652035196</v>
       </c>
       <c r="AC4">
-        <v>48.29978656895716</v>
+        <v>45.25511742057672</v>
       </c>
       <c r="AD4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
         <v>91</v>
       </c>
       <c r="C5">
-        <v>13.288</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="D5">
-        <v>12.416</v>
+        <v>10.476</v>
       </c>
       <c r="E5">
-        <v>11.45044534583586</v>
+        <v>11.06324335018592</v>
       </c>
       <c r="F5">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="G5">
-        <v>12.87813813537621</v>
+        <v>9.232894174466566</v>
       </c>
       <c r="J5" t="s">
         <v>94</v>
       </c>
       <c r="K5">
-        <v>11.45044534583586</v>
+        <v>11.06324335018592</v>
       </c>
       <c r="L5">
-        <v>2.351026032651849</v>
+        <v>3.004822768461589</v>
       </c>
       <c r="M5">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="O5" t="s">
         <v>118</v>
       </c>
       <c r="P5">
-        <v>9.779145216252848</v>
+        <v>13.63288708314677</v>
       </c>
       <c r="Q5">
-        <v>0.8540406002469759</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R5">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S5" t="s">
         <v>119</v>
       </c>
       <c r="T5">
-        <v>-1.671300129583011</v>
+        <v>2.569643732960854</v>
       </c>
       <c r="U5">
-        <v>0.2208547837471517</v>
+        <v>0.3671129168532268</v>
       </c>
       <c r="V5" t="s">
         <v>96</v>
       </c>
       <c r="W5">
-        <v>12.87813813537621</v>
+        <v>9.232894174466566</v>
       </c>
       <c r="X5">
-        <v>1.427692789540352</v>
+        <v>1.830349175719354</v>
       </c>
       <c r="Y5">
-        <v>1.45044534583586</v>
+        <v>2.936756649814081</v>
       </c>
       <c r="Z5">
-        <v>0.6072637094239147</v>
+        <v>0.6091371494287687</v>
       </c>
       <c r="AA5">
-        <v>0.6169414228900835</v>
+        <v>0.977347709368444</v>
       </c>
       <c r="AB5">
-        <v>0.6530627868477359</v>
+        <v>0.536575494368141</v>
       </c>
       <c r="AC5">
-        <v>54.29973121083951</v>
+        <v>47.8063913390236</v>
       </c>
       <c r="AD5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
         <v>90</v>
       </c>
       <c r="C6">
-        <v>1.344</v>
+        <v>8.536</v>
       </c>
       <c r="D6">
-        <v>1.788</v>
+        <v>6.736</v>
       </c>
       <c r="E6">
-        <v>1.473024875335867</v>
+        <v>5.242518257955137</v>
       </c>
       <c r="F6">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="G6">
-        <v>1.558293210761144</v>
+        <v>7.707244105086258</v>
       </c>
       <c r="J6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K6">
-        <v>1.473024875335867</v>
+        <v>7.707244105086258</v>
       </c>
       <c r="L6">
-        <v>1.746417103282563</v>
+        <v>4.568878458795728</v>
       </c>
       <c r="M6">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N6">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="O6" t="s">
         <v>118</v>
       </c>
       <c r="P6">
-        <v>1.501280428022223</v>
+        <v>7.457194256165481</v>
       </c>
       <c r="Q6">
-        <v>1.019181992890591</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S6" t="s">
         <v>119</v>
       </c>
       <c r="T6">
-        <v>0.02825555268635682</v>
+        <v>-0.250049848920777</v>
       </c>
       <c r="U6">
-        <v>0.4987195719777766</v>
+        <v>-0.4571942561654811</v>
       </c>
       <c r="V6" t="s">
         <v>96</v>
       </c>
       <c r="W6">
-        <v>1.558293210761144</v>
+        <v>7.707244105086258</v>
       </c>
       <c r="X6">
-        <v>0.08526833542527745</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>0.5269751246641334</v>
+        <v>0.7072441050862581</v>
       </c>
       <c r="Z6">
-        <v>0.04882472535627785</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>0.3017464291168656</v>
+        <v>0.1547959989447114</v>
       </c>
       <c r="AB6">
-        <v>0.7593117840358968</v>
+        <v>0.6922543119387468</v>
       </c>
       <c r="AC6">
-        <v>87.16674245626311</v>
+        <v>94.72629105871258</v>
       </c>
       <c r="AD6" t="s">
         <v>78</v>
@@ -4971,429 +4977,429 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7">
-        <v>1.92</v>
+        <v>5.116</v>
       </c>
       <c r="D7">
-        <v>1.584</v>
+        <v>4.152</v>
       </c>
       <c r="E7">
-        <v>1.52157415011752</v>
+        <v>3.0173797501092</v>
       </c>
       <c r="F7">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="G7">
-        <v>1.762071575099091</v>
+        <v>4.67215517627953</v>
       </c>
       <c r="J7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K7">
-        <v>1.52157415011752</v>
+        <v>4.67215517627953</v>
       </c>
       <c r="L7">
-        <v>1.157976831184469</v>
+        <v>2.590285563576617</v>
       </c>
       <c r="M7">
-        <v>1.038416113387647</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N7">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="s">
         <v>118</v>
       </c>
       <c r="P7">
-        <v>1.299486100486649</v>
+        <v>4.520574185716101</v>
       </c>
       <c r="Q7">
-        <v>0.8540406002469759</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S7" t="s">
         <v>119</v>
       </c>
       <c r="T7">
-        <v>-0.2220880496308713</v>
+        <v>-0.1515809905634287</v>
       </c>
       <c r="U7">
-        <v>-0.2994861004866491</v>
+        <v>-0.520574185716101</v>
       </c>
       <c r="V7" t="s">
         <v>96</v>
       </c>
       <c r="W7">
-        <v>1.762071575099091</v>
+        <v>4.67215517627953</v>
       </c>
       <c r="X7">
-        <v>0.2404974249815708</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>0.5215741501175204</v>
+        <v>0.6721551762795297</v>
       </c>
       <c r="Z7">
-        <v>0.2076875965951506</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>0.4504184678583023</v>
+        <v>0.2594907626136134</v>
       </c>
       <c r="AB7">
-        <v>0.8271263079889064</v>
+        <v>0.7195237676601712</v>
       </c>
       <c r="AC7">
-        <v>74.62882184844142</v>
+        <v>91.31804553655472</v>
       </c>
       <c r="AD7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
         <v>90</v>
       </c>
       <c r="C8">
-        <v>1.904</v>
+        <v>9.212</v>
       </c>
       <c r="D8">
-        <v>1.796</v>
+        <v>11.748</v>
       </c>
       <c r="E8">
-        <v>2.604250820161925</v>
+        <v>14.36529697727345</v>
       </c>
       <c r="F8">
-        <v>1.6</v>
+        <v>13.2</v>
       </c>
       <c r="G8">
-        <v>1.851874624409452</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="J8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K8">
-        <v>2.604250820161925</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="L8">
-        <v>1.198624596172324</v>
+        <v>5.848565661247161</v>
       </c>
       <c r="M8">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N8">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O8" t="s">
         <v>118</v>
       </c>
       <c r="P8">
-        <v>2.557215395085126</v>
+        <v>10.77177037254729</v>
       </c>
       <c r="Q8">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S8" t="s">
         <v>119</v>
       </c>
       <c r="T8">
-        <v>-0.04703542507679881</v>
+        <v>0.3921454006021552</v>
       </c>
       <c r="U8">
-        <v>0.4427846049148738</v>
+        <v>0.2282296274527074</v>
       </c>
       <c r="V8" t="s">
         <v>96</v>
       </c>
       <c r="W8">
-        <v>1.851874624409452</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="X8">
-        <v>0.7523761957524733</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>0.395749179838075</v>
+        <v>0.6203750280548626</v>
       </c>
       <c r="Z8">
-        <v>0.6276996135029299</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>0.3301694134275707</v>
+        <v>0.1060730209742695</v>
       </c>
       <c r="AB8">
-        <v>0.7491403726077025</v>
+        <v>0.7132397147862392</v>
       </c>
       <c r="AC8">
-        <v>59.24054223283283</v>
+        <v>96.35551463316079</v>
       </c>
       <c r="AD8" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9">
-        <v>13.532</v>
+        <v>2.432</v>
       </c>
       <c r="D9">
-        <v>12.556</v>
+        <v>1.928</v>
       </c>
       <c r="E9">
-        <v>13.3559567781861</v>
+        <v>1.608426994139059</v>
       </c>
       <c r="F9">
-        <v>11.8</v>
+        <v>1.6</v>
       </c>
       <c r="G9">
-        <v>13.06094105021875</v>
+        <v>2.201831003526596</v>
       </c>
       <c r="J9" t="s">
         <v>94</v>
       </c>
       <c r="K9">
-        <v>13.3559567781861</v>
+        <v>1.608426994139059</v>
       </c>
       <c r="L9">
-        <v>3.125306797245826</v>
+        <v>1.357115480819956</v>
       </c>
       <c r="M9">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N9">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="s">
         <v>118</v>
       </c>
       <c r="P9">
-        <v>13.11473458118962</v>
+        <v>1.265242685482676</v>
       </c>
       <c r="Q9">
-        <v>0.981938980411313</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R9">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="S9" t="s">
         <v>119</v>
       </c>
       <c r="T9">
-        <v>-0.2412221969964765</v>
+        <v>-0.3431843086563835</v>
       </c>
       <c r="U9">
-        <v>-0.1147345811896248</v>
+        <v>-0.2652426854826757</v>
       </c>
       <c r="V9" t="s">
         <v>96</v>
       </c>
       <c r="W9">
-        <v>13.06094105021875</v>
+        <v>2.201831003526596</v>
       </c>
       <c r="X9">
-        <v>0.2950157279673533</v>
+        <v>0.5934040093875366</v>
       </c>
       <c r="Y9">
-        <v>0.3559567781861013</v>
+        <v>0.6084269941390592</v>
       </c>
       <c r="Z9">
-        <v>0.09439576563406053</v>
+        <v>0.4372538798459565</v>
       </c>
       <c r="AA9">
-        <v>0.1138949873656525</v>
+        <v>0.4483236708577323</v>
       </c>
       <c r="AB9">
-        <v>0.6511055827595471</v>
+        <v>0.9693682005856831</v>
       </c>
       <c r="AC9">
-        <v>90.37337437343564</v>
+        <v>64.33101602736564</v>
       </c>
       <c r="AD9" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10">
-        <v>3.784</v>
+        <v>0.764</v>
       </c>
       <c r="D10">
-        <v>3.252</v>
+        <v>0.532</v>
       </c>
       <c r="E10">
-        <v>3.656634670288002</v>
+        <v>0.4302454583585212</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="G10">
-        <v>3.527234260979891</v>
+        <v>0.6580491920995442</v>
       </c>
       <c r="J10" t="s">
         <v>94</v>
       </c>
       <c r="K10">
-        <v>3.656634670288002</v>
+        <v>0.4302454583585212</v>
       </c>
       <c r="L10">
-        <v>0.887818750560327</v>
+        <v>0.4552884680086201</v>
       </c>
       <c r="M10">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N10">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="O10" t="s">
         <v>118</v>
       </c>
       <c r="P10">
-        <v>3.590592119879259</v>
+        <v>0.5301779565157876</v>
       </c>
       <c r="Q10">
-        <v>0.981938980411313</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S10" t="s">
         <v>119</v>
       </c>
       <c r="T10">
-        <v>-0.06604255040874341</v>
+        <v>0.09993249815726635</v>
       </c>
       <c r="U10">
-        <v>0.409407880120741</v>
+        <v>0.4698220434842124</v>
       </c>
       <c r="V10" t="s">
         <v>96</v>
       </c>
       <c r="W10">
-        <v>3.527234260979891</v>
+        <v>0.6580491920995442</v>
       </c>
       <c r="X10">
-        <v>0.1294004093081114</v>
+        <v>0.2278037337410229</v>
       </c>
       <c r="Y10">
-        <v>0.3433653297119976</v>
+        <v>0.5697545416414788</v>
       </c>
       <c r="Z10">
-        <v>0.1457509308363258</v>
+        <v>0.5003503267662599</v>
       </c>
       <c r="AA10">
-        <v>0.3867516083607045</v>
+        <v>1.251414392579545</v>
       </c>
       <c r="AB10">
-        <v>0.3551275002241308</v>
+        <v>0.7588141133477002</v>
       </c>
       <c r="AC10">
-        <v>79.44532252176565</v>
+        <v>46.61616811374733</v>
       </c>
       <c r="AD10" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11">
-        <v>0.6</v>
+        <v>1.96</v>
       </c>
       <c r="D11">
-        <v>0.696</v>
+        <v>3.288</v>
       </c>
       <c r="E11">
-        <v>0.3240271499397565</v>
+        <v>1.85838186252915</v>
       </c>
       <c r="F11">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="G11">
-        <v>0.6451224071145452</v>
+        <v>2.571437682469693</v>
       </c>
       <c r="J11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K11">
-        <v>0.3240271499397565</v>
+        <v>2.571437682469693</v>
       </c>
       <c r="L11">
-        <v>1.559831022862906</v>
+        <v>3.037968256748472</v>
       </c>
       <c r="M11">
-        <v>1.038416113387647</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N11">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="s">
         <v>118</v>
       </c>
       <c r="P11">
-        <v>0.2767323416308665</v>
+        <v>2.66858738323837</v>
       </c>
       <c r="Q11">
-        <v>0.8540406002469759</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="s">
         <v>119</v>
       </c>
       <c r="T11">
-        <v>-0.04729480830888999</v>
+        <v>0.09714970076867679</v>
       </c>
       <c r="U11">
-        <v>-0.2767323416308665</v>
+        <v>0.33141261676163</v>
       </c>
       <c r="V11" t="s">
         <v>96</v>
       </c>
       <c r="W11">
-        <v>0.6451224071145452</v>
+        <v>2.571437682469693</v>
       </c>
       <c r="X11">
-        <v>0.3210952571747887</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>0.3240271499397565</v>
+        <v>0.4285623175303068</v>
       </c>
       <c r="Z11">
-        <v>0.2058525907411766</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>0.207732212778432</v>
+        <v>0.1410687279494473</v>
       </c>
       <c r="AB11">
-        <v>1.299859185719089</v>
+        <v>0.6604278819018417</v>
       </c>
       <c r="AC11">
-        <v>81.34177543201334</v>
+        <v>95.18250283981683</v>
       </c>
       <c r="AD11" t="s">
         <v>78</v>
@@ -5407,31 +5413,31 @@
         <v>91</v>
       </c>
       <c r="C12">
-        <v>0.18</v>
+        <v>0.132</v>
       </c>
       <c r="D12">
-        <v>0.264</v>
+        <v>0.236</v>
       </c>
       <c r="E12">
-        <v>0.6788079824227848</v>
+        <v>0.6297196965274399</v>
       </c>
       <c r="F12">
         <v>0.2</v>
       </c>
       <c r="G12">
-        <v>0.2194821062252271</v>
+        <v>0.1794951897484802</v>
       </c>
       <c r="J12" t="s">
         <v>94</v>
       </c>
       <c r="K12">
-        <v>0.6788079824227848</v>
+        <v>0.6297196965274399</v>
       </c>
       <c r="L12">
-        <v>0.4925498319332764</v>
+        <v>0.4196830443219419</v>
       </c>
       <c r="M12">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N12">
         <v>0.4</v>
@@ -5440,10 +5446,10 @@
         <v>118</v>
       </c>
       <c r="P12">
-        <v>0.7802977676584159</v>
+        <v>0.7759837911047821</v>
       </c>
       <c r="Q12">
-        <v>1.149511773378675</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -5452,292 +5458,292 @@
         <v>119</v>
       </c>
       <c r="T12">
-        <v>0.101489785235631</v>
+        <v>0.1462640945773422</v>
       </c>
       <c r="U12">
-        <v>0.2197022323415841</v>
+        <v>0.2240162088952179</v>
       </c>
       <c r="V12" t="s">
         <v>96</v>
       </c>
       <c r="W12">
-        <v>0.2194821062252271</v>
+        <v>0.1794951897484802</v>
       </c>
       <c r="X12">
-        <v>0.4593258761975577</v>
+        <v>0.4502245067789596</v>
       </c>
       <c r="Y12">
-        <v>0.3211920175772152</v>
+        <v>0.3702803034725601</v>
       </c>
       <c r="Z12">
-        <v>0.9325470163997145</v>
+        <v>1.072772686126412</v>
       </c>
       <c r="AA12">
-        <v>0.6521005525806892</v>
+        <v>0.8822855926209767</v>
       </c>
       <c r="AB12">
-        <v>1.231374579833191</v>
+        <v>1.049207610804855</v>
       </c>
       <c r="AC12">
-        <v>43.41388982372007</v>
+        <v>36.56414014265842</v>
       </c>
       <c r="AD12" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="D13">
-        <v>0.408</v>
+        <v>1.436</v>
       </c>
       <c r="E13">
-        <v>0.3147916000487194</v>
+        <v>1.061924546619121</v>
       </c>
       <c r="F13">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="G13">
-        <v>0.4885561887353032</v>
+        <v>1.351825510892524</v>
       </c>
       <c r="J13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K13">
-        <v>0.3147916000487194</v>
+        <v>1.351825510892524</v>
       </c>
       <c r="L13">
-        <v>0.3921195507989373</v>
+        <v>1.18177630190794</v>
       </c>
       <c r="M13">
-        <v>1.038416113387647</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N13">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="O13" t="s">
         <v>118</v>
       </c>
       <c r="P13">
-        <v>0.3618566504167141</v>
+        <v>1.402897891440568</v>
       </c>
       <c r="Q13">
-        <v>1.149511773378675</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="s">
         <v>119</v>
       </c>
       <c r="T13">
-        <v>0.04706505036799469</v>
+        <v>0.05107238054804397</v>
       </c>
       <c r="U13">
-        <v>-0.3618566504167141</v>
+        <v>-0.4028978914405681</v>
       </c>
       <c r="V13" t="s">
         <v>96</v>
       </c>
       <c r="W13">
-        <v>0.4885561887353032</v>
+        <v>1.351825510892524</v>
       </c>
       <c r="X13">
-        <v>0.1737645886865837</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>0.3147916000487194</v>
+        <v>0.3518255108925241</v>
       </c>
       <c r="Z13">
-        <v>0.4431418640884933</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>0.8027949624223952</v>
+        <v>0.2977090590871665</v>
       </c>
       <c r="AB13">
-        <v>0.6535325846648956</v>
+        <v>1.074342092643582</v>
       </c>
       <c r="AC13">
-        <v>56.60796713936882</v>
+        <v>90.10467186858428</v>
       </c>
       <c r="AD13" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
         <v>90</v>
       </c>
       <c r="C14">
-        <v>8.763999999999999</v>
+        <v>1.748</v>
       </c>
       <c r="D14">
-        <v>6.752</v>
+        <v>3.744</v>
       </c>
       <c r="E14">
-        <v>4.301787319744047</v>
+        <v>-5.9050260855817</v>
       </c>
       <c r="F14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="G14">
-        <v>7.792923558442745</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="J14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K14">
-        <v>4.301787319744047</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="L14">
-        <v>4.673523904256721</v>
+        <v>9.299703921130613</v>
       </c>
       <c r="M14">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N14">
-        <v>8.4</v>
+        <v>10.1</v>
       </c>
       <c r="O14" t="s">
         <v>118</v>
       </c>
       <c r="P14">
-        <v>4.224092654695784</v>
+        <v>2.767758209900166</v>
       </c>
       <c r="Q14">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S14" t="s">
         <v>119</v>
       </c>
       <c r="T14">
-        <v>-0.07769466504826283</v>
+        <v>0.1007600064291512</v>
       </c>
       <c r="U14">
-        <v>-0.2240926546957844</v>
+        <v>0.2322417900998337</v>
       </c>
       <c r="V14" t="s">
         <v>96</v>
       </c>
       <c r="W14">
-        <v>7.792923558442745</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="X14">
-        <v>3.491136238698697</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>0.3017873197440473</v>
+        <v>0.3330017965289849</v>
       </c>
       <c r="Z14">
-        <v>0.747002970396474</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>0.06457382607354901</v>
+        <v>0.03580778478036752</v>
       </c>
       <c r="AB14">
-        <v>0.5563718933638954</v>
+        <v>0.9207627644683776</v>
       </c>
       <c r="AC14">
-        <v>60.16058574846904</v>
+        <v>98.75454828619661</v>
       </c>
       <c r="AD14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
         <v>90</v>
       </c>
       <c r="C15">
-        <v>5.384</v>
+        <v>1.064</v>
       </c>
       <c r="D15">
-        <v>4.436</v>
+        <v>1.632</v>
       </c>
       <c r="E15">
-        <v>4.289783155551396</v>
+        <v>0.2672118870713838</v>
       </c>
       <c r="F15">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="G15">
-        <v>4.926455036482963</v>
+        <v>1.325518526839447</v>
       </c>
       <c r="J15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K15">
-        <v>4.289783155551396</v>
+        <v>1.325518526839447</v>
       </c>
       <c r="L15">
-        <v>2.858585552684069</v>
+        <v>1.998268059200945</v>
       </c>
       <c r="M15">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N15">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="s">
         <v>118</v>
       </c>
       <c r="P15">
-        <v>4.212305297947762</v>
+        <v>1.375597021497778</v>
       </c>
       <c r="Q15">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S15" t="s">
         <v>119</v>
       </c>
       <c r="T15">
-        <v>-0.07747785760363346</v>
+        <v>0.05007849465833103</v>
       </c>
       <c r="U15">
-        <v>-0.2123052979477622</v>
+        <v>-0.3755970214977782</v>
       </c>
       <c r="V15" t="s">
         <v>96</v>
       </c>
       <c r="W15">
-        <v>4.926455036482963</v>
+        <v>1.325518526839447</v>
       </c>
       <c r="X15">
-        <v>0.6366718809315675</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>0.2897831555513957</v>
+        <v>0.3255185268394472</v>
       </c>
       <c r="Z15">
-        <v>0.2227226959619118</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>0.1013729168536879</v>
+        <v>0.1629003302838227</v>
       </c>
       <c r="AB15">
-        <v>0.6972159884595291</v>
+        <v>0.8688121996525846</v>
       </c>
       <c r="AC15">
-        <v>83.50611917578671</v>
+        <v>94.45797913689444</v>
       </c>
       <c r="AD15" t="s">
         <v>78</v>
@@ -5745,88 +5751,88 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C16">
-        <v>0.632</v>
+        <v>12.34</v>
       </c>
       <c r="D16">
-        <v>0.44</v>
+        <v>10.124</v>
       </c>
       <c r="E16">
-        <v>0.7530958545051754</v>
+        <v>9.224776144749352</v>
       </c>
       <c r="F16">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G16">
-        <v>0.5417551857709093</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="J16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K16">
-        <v>0.7530958545051754</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="L16">
-        <v>0.7620693762924241</v>
+        <v>5.707606654863389</v>
       </c>
       <c r="M16">
-        <v>1.038416113387647</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N16">
-        <v>0.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O16" t="s">
         <v>118</v>
       </c>
       <c r="P16">
-        <v>0.8656925512363728</v>
+        <v>10.95245860103622</v>
       </c>
       <c r="Q16">
-        <v>1.149511773378675</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R16">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="S16" t="s">
         <v>119</v>
       </c>
       <c r="T16">
-        <v>0.1125966967311974</v>
+        <v>-0.3672508083366459</v>
       </c>
       <c r="U16">
-        <v>0.1343074487636272</v>
+        <v>0.04754139896378362</v>
       </c>
       <c r="V16" t="s">
         <v>96</v>
       </c>
       <c r="W16">
-        <v>0.5417551857709093</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="X16">
-        <v>0.211340668734266</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>0.2469041454948246</v>
+        <v>0.3197094093728623</v>
       </c>
       <c r="Z16">
-        <v>0.2773247099397544</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>0.3239916904889269</v>
+        <v>0.05601461850922075</v>
       </c>
       <c r="AB16">
-        <v>0.95258672036553</v>
+        <v>0.6876634523931793</v>
       </c>
       <c r="AC16">
-        <v>74.55313054289088</v>
+        <v>98.05858140436257</v>
       </c>
       <c r="AD16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -5933,257 +5939,257 @@
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2">
-        <v>13.548</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="D2">
-        <v>14.728</v>
+        <v>10.476</v>
       </c>
       <c r="E2">
-        <v>18.83927196478475</v>
+        <v>11.06324335018592</v>
       </c>
       <c r="F2">
-        <v>14.6</v>
+        <v>11.6</v>
       </c>
       <c r="G2">
-        <v>14.1175179925634</v>
+        <v>9.232894174466566</v>
       </c>
       <c r="J2" t="s">
         <v>94</v>
       </c>
       <c r="K2">
-        <v>18.83927196478475</v>
+        <v>11.06324335018592</v>
       </c>
       <c r="L2">
-        <v>5.333756871724871</v>
+        <v>3.004822768461589</v>
       </c>
       <c r="M2">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N2">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="s">
         <v>118</v>
       </c>
       <c r="P2">
-        <v>19.20064674567716</v>
+        <v>13.63288708314677</v>
       </c>
       <c r="Q2">
-        <v>1.019181992890591</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="S2" t="s">
         <v>119</v>
       </c>
       <c r="T2">
-        <v>0.3613747808924153</v>
+        <v>2.569643732960854</v>
       </c>
       <c r="U2">
-        <v>-0.2006467456771617</v>
+        <v>0.3671129168532268</v>
       </c>
       <c r="V2" t="s">
         <v>96</v>
       </c>
       <c r="W2">
-        <v>14.1175179925634</v>
+        <v>9.232894174466566</v>
       </c>
       <c r="X2">
-        <v>4.721753972221347</v>
+        <v>1.830349175719354</v>
       </c>
       <c r="Y2">
-        <v>0.1607280352152536</v>
+        <v>2.936756649814081</v>
       </c>
       <c r="Z2">
-        <v>0.8852585683558519</v>
+        <v>0.6091371494287687</v>
       </c>
       <c r="AA2">
-        <v>0.03013411354898824</v>
+        <v>0.977347709368444</v>
       </c>
       <c r="AB2">
-        <v>1.088521810556096</v>
+        <v>0.536575494368141</v>
       </c>
       <c r="AC2">
-        <v>55.65685088619063</v>
+        <v>47.8063913390236</v>
       </c>
       <c r="AD2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3">
-        <v>3.444</v>
+        <v>14.476</v>
       </c>
       <c r="D3">
-        <v>4.86</v>
+        <v>13.084</v>
       </c>
       <c r="E3">
-        <v>0.2404700937671027</v>
+        <v>12.1475539711821</v>
       </c>
       <c r="F3">
-        <v>7.4</v>
+        <v>12.4</v>
       </c>
       <c r="G3">
-        <v>4.127421591076081</v>
+        <v>13.84029515259726</v>
       </c>
       <c r="J3" t="s">
         <v>94</v>
       </c>
       <c r="K3">
-        <v>0.2404700937671027</v>
+        <v>12.1475539711821</v>
       </c>
       <c r="L3">
-        <v>9.933150479214353</v>
+        <v>2.777213034732671</v>
       </c>
       <c r="M3">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N3">
-        <v>10.3</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="s">
         <v>118</v>
       </c>
       <c r="P3">
-        <v>0.2450827893961431</v>
+        <v>9.555673875500363</v>
       </c>
       <c r="Q3">
-        <v>1.019181992890591</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S3" t="s">
         <v>119</v>
       </c>
       <c r="T3">
-        <v>0.004612695629040375</v>
+        <v>-2.591880095681738</v>
       </c>
       <c r="U3">
-        <v>-0.2450827893961431</v>
+        <v>-0.5556738755003625</v>
       </c>
       <c r="V3" t="s">
         <v>96</v>
       </c>
       <c r="W3">
-        <v>4.127421591076081</v>
+        <v>13.84029515259726</v>
       </c>
       <c r="X3">
-        <v>3.886951497308978</v>
+        <v>1.692741181415164</v>
       </c>
       <c r="Y3">
-        <v>0.2404700937671027</v>
+        <v>3.1475539711821</v>
       </c>
       <c r="Z3">
-        <v>0.3913110453166527</v>
+        <v>0.6095107434126327</v>
       </c>
       <c r="AA3">
-        <v>0.02420884434100734</v>
+        <v>1.133349848145545</v>
       </c>
       <c r="AB3">
-        <v>0.9643835416712964</v>
+        <v>0.7714480652035196</v>
       </c>
       <c r="AC3">
-        <v>76.8876227493331</v>
+        <v>45.25511742057672</v>
       </c>
       <c r="AD3" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4">
-        <v>8.763999999999999</v>
+        <v>0.856</v>
       </c>
       <c r="D4">
-        <v>6.752</v>
+        <v>1.468</v>
       </c>
       <c r="E4">
-        <v>4.301787319744047</v>
+        <v>-0.6136915121990012</v>
       </c>
       <c r="F4">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="G4">
-        <v>7.792923558442745</v>
+        <v>1.135490924289134</v>
       </c>
       <c r="J4" t="s">
         <v>94</v>
       </c>
       <c r="K4">
-        <v>4.301787319744047</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>4.673523904256721</v>
+        <v>2.225665663703473</v>
       </c>
       <c r="M4">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N4">
-        <v>8.4</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="s">
         <v>118</v>
       </c>
       <c r="P4">
-        <v>4.224092654695784</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>0.981938980411313</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S4" t="s">
         <v>119</v>
       </c>
       <c r="T4">
-        <v>-0.07769466504826283</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>-0.2240926546957844</v>
+        <v>0</v>
       </c>
       <c r="V4" t="s">
         <v>96</v>
       </c>
       <c r="W4">
-        <v>7.792923558442745</v>
+        <v>1.135490924289134</v>
       </c>
       <c r="X4">
-        <v>3.491136238698697</v>
+        <v>1.135490924289134</v>
       </c>
       <c r="Y4">
-        <v>0.3017873197440473</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>0.747002970396474</v>
+        <v>0.5101803666233026</v>
       </c>
       <c r="AA4">
-        <v>0.06457382607354901</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.5563718933638954</v>
+        <v>0.7179566657107976</v>
       </c>
       <c r="AC4">
-        <v>60.16058574846904</v>
+        <v>71.77620020831648</v>
       </c>
       <c r="AD4" t="s">
         <v>79</v>
@@ -6191,601 +6197,601 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5">
-        <v>2.824</v>
+        <v>1.124</v>
       </c>
       <c r="D5">
-        <v>3.956</v>
+        <v>1.14</v>
       </c>
       <c r="E5">
-        <v>0.8437214709471421</v>
+        <v>1.941748773991384</v>
       </c>
       <c r="F5">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>3.370351158967601</v>
+        <v>1.131306952268997</v>
       </c>
       <c r="J5" t="s">
         <v>94</v>
       </c>
       <c r="K5">
-        <v>0.8437214709471421</v>
+        <v>1.941748773991384</v>
       </c>
       <c r="L5">
-        <v>7.059923274159115</v>
+        <v>0.5888547436899401</v>
       </c>
       <c r="M5">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N5">
-        <v>7.6</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="s">
         <v>118</v>
       </c>
       <c r="P5">
-        <v>0.8599057302044893</v>
+        <v>2.392755988615071</v>
       </c>
       <c r="Q5">
-        <v>1.019181992890591</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="s">
         <v>119</v>
       </c>
       <c r="T5">
-        <v>0.01618425925734723</v>
+        <v>0.4510072146236872</v>
       </c>
       <c r="U5">
-        <v>0.1400942697955107</v>
+        <v>-0.3927559886150713</v>
       </c>
       <c r="V5" t="s">
         <v>96</v>
       </c>
       <c r="W5">
-        <v>3.370351158967601</v>
+        <v>1.131306952268997</v>
       </c>
       <c r="X5">
-        <v>2.526629688020459</v>
+        <v>0.8104418217223872</v>
       </c>
       <c r="Y5">
-        <v>0.1562785290528579</v>
+        <v>0.05825122600861588</v>
       </c>
       <c r="Z5">
-        <v>0.3578834485735112</v>
+        <v>1.376301762713019</v>
       </c>
       <c r="AA5">
-        <v>0.02213600955478822</v>
+        <v>0.09892291203021693</v>
       </c>
       <c r="AB5">
-        <v>0.9289372729156731</v>
+        <v>1.17770948737988</v>
       </c>
       <c r="AC5">
-        <v>78.63354118711212</v>
+        <v>39.4861912039952</v>
       </c>
       <c r="AD5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6">
-        <v>171.868</v>
+        <v>2.432</v>
       </c>
       <c r="D6">
-        <v>174.552</v>
+        <v>1.928</v>
       </c>
       <c r="E6">
-        <v>175.5728436009487</v>
+        <v>1.608426994139059</v>
       </c>
       <c r="F6">
-        <v>172.6</v>
+        <v>1.6</v>
       </c>
       <c r="G6">
-        <v>173.1634121118985</v>
+        <v>2.201831003526596</v>
       </c>
       <c r="J6" t="s">
         <v>94</v>
       </c>
       <c r="K6">
-        <v>175.5728436009487</v>
+        <v>1.608426994139059</v>
       </c>
       <c r="L6">
-        <v>24.70132137894479</v>
+        <v>1.357115480819956</v>
       </c>
       <c r="M6">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N6">
-        <v>18.7</v>
+        <v>1.4</v>
       </c>
       <c r="O6" t="s">
         <v>118</v>
       </c>
       <c r="P6">
-        <v>172.4018190334305</v>
+        <v>1.265242685482676</v>
       </c>
       <c r="Q6">
-        <v>0.981938980411313</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R6">
-        <v>172</v>
+        <v>1</v>
       </c>
       <c r="S6" t="s">
         <v>119</v>
       </c>
       <c r="T6">
-        <v>-3.171024567518231</v>
+        <v>-0.3431843086563835</v>
       </c>
       <c r="U6">
-        <v>-0.4018190334304563</v>
+        <v>-0.2652426854826757</v>
       </c>
       <c r="V6" t="s">
         <v>96</v>
       </c>
       <c r="W6">
-        <v>173.1634121118985</v>
+        <v>2.201831003526596</v>
       </c>
       <c r="X6">
-        <v>2.409431489050235</v>
+        <v>0.5934040093875366</v>
       </c>
       <c r="Y6">
-        <v>3.572843600948687</v>
+        <v>0.6084269941390592</v>
       </c>
       <c r="Z6">
-        <v>0.09754261531547112</v>
+        <v>0.4372538798459565</v>
       </c>
       <c r="AA6">
-        <v>0.1446418005797111</v>
+        <v>0.4483236708577323</v>
       </c>
       <c r="AB6">
-        <v>1.320926276948919</v>
+        <v>0.9693682005856831</v>
       </c>
       <c r="AC6">
-        <v>89.22335706647648</v>
+        <v>64.33101602736564</v>
       </c>
       <c r="AD6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
         <v>91</v>
       </c>
       <c r="C7">
-        <v>9.932</v>
+        <v>0.228</v>
       </c>
       <c r="D7">
-        <v>11.352</v>
+        <v>0.372</v>
       </c>
       <c r="E7">
-        <v>12.86475247157808</v>
+        <v>0.8817836191054232</v>
       </c>
       <c r="F7">
-        <v>11.6</v>
+        <v>0.4</v>
       </c>
       <c r="G7">
-        <v>10.59943560523598</v>
+        <v>0.2937625704209726</v>
       </c>
       <c r="J7" t="s">
         <v>94</v>
       </c>
       <c r="K7">
-        <v>12.86475247157808</v>
+        <v>0.8817836191054232</v>
       </c>
       <c r="L7">
-        <v>3.050242274051084</v>
+        <v>0.7453408782506382</v>
       </c>
       <c r="M7">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N7">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="O7" t="s">
         <v>118</v>
       </c>
       <c r="P7">
-        <v>14.78818442768141</v>
+        <v>0.6936406055835702</v>
       </c>
       <c r="Q7">
-        <v>1.149511773378675</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R7">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="S7" t="s">
         <v>119</v>
       </c>
       <c r="T7">
-        <v>1.923431956103332</v>
+        <v>-0.188143013521853</v>
       </c>
       <c r="U7">
-        <v>0.2118155723185868</v>
+        <v>0.3063593944164298</v>
       </c>
       <c r="V7" t="s">
         <v>96</v>
       </c>
       <c r="W7">
-        <v>10.59943560523598</v>
+        <v>0.2937625704209726</v>
       </c>
       <c r="X7">
-        <v>2.265316866342099</v>
+        <v>0.5880210486844506</v>
       </c>
       <c r="Y7">
-        <v>2.135247528421919</v>
+        <v>0.1182163808945768</v>
       </c>
       <c r="Z7">
-        <v>0.7426678482602922</v>
+        <v>0.7889290200539824</v>
       </c>
       <c r="AA7">
-        <v>0.7000255509494521</v>
+        <v>0.1586071344591189</v>
       </c>
       <c r="AB7">
-        <v>0.544686120366265</v>
+        <v>1.242234797084397</v>
       </c>
       <c r="AC7">
-        <v>48.29978656895716</v>
+        <v>56.64783818764582</v>
       </c>
       <c r="AD7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
         <v>91</v>
       </c>
       <c r="C8">
-        <v>1.604</v>
+        <v>0.132</v>
       </c>
       <c r="D8">
-        <v>1.924</v>
+        <v>0.236</v>
       </c>
       <c r="E8">
-        <v>-0.1313628720128142</v>
+        <v>0.6297196965274399</v>
       </c>
       <c r="F8">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="G8">
-        <v>1.754408023715151</v>
+        <v>0.1794951897484802</v>
       </c>
       <c r="J8" t="s">
         <v>94</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>0.6297196965274399</v>
       </c>
       <c r="L8">
-        <v>1.736334852416627</v>
+        <v>0.4196830443219419</v>
       </c>
       <c r="M8">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="O8" t="s">
         <v>118</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>0.7759837911047821</v>
       </c>
       <c r="Q8">
-        <v>0.8540406002469759</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="s">
         <v>119</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.1462640945773422</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>0.2240162088952179</v>
       </c>
       <c r="V8" t="s">
         <v>96</v>
       </c>
       <c r="W8">
-        <v>1.754408023715151</v>
+        <v>0.1794951897484802</v>
       </c>
       <c r="X8">
-        <v>1.754408023715151</v>
+        <v>0.4502245067789596</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>0.3702803034725601</v>
       </c>
       <c r="Z8">
-        <v>1.010408805233259</v>
+        <v>1.072772686126412</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>0.8822855926209767</v>
       </c>
       <c r="AB8">
-        <v>0.5601080169085895</v>
+        <v>1.049207610804855</v>
       </c>
       <c r="AC8">
-        <v>51.85256808577751</v>
+        <v>36.56414014265842</v>
       </c>
       <c r="AD8" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9">
-        <v>7.492</v>
+        <v>0.752</v>
       </c>
       <c r="D9">
-        <v>5.94</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E9">
-        <v>5.212253933741241</v>
+        <v>0.2483906019674781</v>
       </c>
       <c r="F9">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="G9">
-        <v>6.742939047069155</v>
+        <v>0.6643165727720365</v>
       </c>
       <c r="J9" t="s">
         <v>94</v>
       </c>
       <c r="K9">
-        <v>5.212253933741241</v>
+        <v>0.2483906019674781</v>
       </c>
       <c r="L9">
-        <v>3.997862832988686</v>
+        <v>0.9284964811104729</v>
       </c>
       <c r="M9">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N9">
-        <v>6.7</v>
+        <v>0.9</v>
       </c>
       <c r="O9" t="s">
         <v>118</v>
       </c>
       <c r="P9">
-        <v>5.11811531334273</v>
+        <v>0.1953923886052483</v>
       </c>
       <c r="Q9">
-        <v>0.981938980411313</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="s">
         <v>119</v>
       </c>
       <c r="T9">
-        <v>-0.09413862039851129</v>
+        <v>-0.05299821336222987</v>
       </c>
       <c r="U9">
-        <v>-0.11811531334273</v>
+        <v>-0.1953923886052483</v>
       </c>
       <c r="V9" t="s">
         <v>96</v>
       </c>
       <c r="W9">
-        <v>6.742939047069155</v>
+        <v>0.6643165727720365</v>
       </c>
       <c r="X9">
-        <v>1.530685113327914</v>
+        <v>0.4159259708045583</v>
       </c>
       <c r="Y9">
-        <v>0.2122539337412412</v>
+        <v>0.2483906019674781</v>
       </c>
       <c r="Z9">
-        <v>0.382875845738714</v>
+        <v>0.4479564320018907</v>
       </c>
       <c r="AA9">
-        <v>0.05309184997289323</v>
+        <v>0.2675191635302757</v>
       </c>
       <c r="AB9">
-        <v>0.5966959452221919</v>
+        <v>1.031662756789414</v>
       </c>
       <c r="AC9">
-        <v>76.53274884974184</v>
+        <v>68.05844340927169</v>
       </c>
       <c r="AD9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10">
-        <v>7.772</v>
+        <v>0.288</v>
       </c>
       <c r="D10">
-        <v>8.804</v>
+        <v>0.408</v>
       </c>
       <c r="E10">
-        <v>9.770258645592461</v>
+        <v>0.7561917677339507</v>
       </c>
       <c r="F10">
-        <v>9.4</v>
+        <v>0.6</v>
       </c>
       <c r="G10">
-        <v>8.270086922309687</v>
+        <v>0.3428021420174772</v>
       </c>
       <c r="J10" t="s">
         <v>94</v>
       </c>
       <c r="K10">
-        <v>9.770258645592461</v>
+        <v>0.7561917677339507</v>
       </c>
       <c r="L10">
-        <v>4.467028425282805</v>
+        <v>1.908933484234525</v>
       </c>
       <c r="M10">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N10">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="s">
         <v>118</v>
       </c>
       <c r="P10">
-        <v>9.957671677471454</v>
+        <v>0.5948458378489989</v>
       </c>
       <c r="Q10">
-        <v>1.019181992890591</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S10" t="s">
         <v>119</v>
       </c>
       <c r="T10">
-        <v>0.1874130318789931</v>
+        <v>-0.1613459298849518</v>
       </c>
       <c r="U10">
-        <v>0.04232832252854557</v>
+        <v>0.4051541621510011</v>
       </c>
       <c r="V10" t="s">
         <v>96</v>
       </c>
       <c r="W10">
-        <v>8.270086922309687</v>
+        <v>0.3428021420174772</v>
       </c>
       <c r="X10">
-        <v>1.500171723282774</v>
+        <v>0.4133896257164735</v>
       </c>
       <c r="Y10">
-        <v>0.2297413544075386</v>
+        <v>0.2438082322660493</v>
       </c>
       <c r="Z10">
-        <v>0.3358321417414752</v>
+        <v>0.2165552802811467</v>
       </c>
       <c r="AA10">
-        <v>0.05143046619252122</v>
+        <v>0.1277196058844426</v>
       </c>
       <c r="AB10">
-        <v>0.911638454139348</v>
+        <v>1.590777903528771</v>
       </c>
       <c r="AC10">
-        <v>78.9550442756191</v>
+        <v>83.07197425634185</v>
       </c>
       <c r="AD10" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11">
-        <v>173.496</v>
+        <v>0.328</v>
       </c>
       <c r="D11">
-        <v>170.784</v>
+        <v>0.212</v>
       </c>
       <c r="E11">
-        <v>173.6497555759981</v>
+        <v>-0.001836660305252591</v>
       </c>
       <c r="F11">
-        <v>169.2</v>
+        <v>0.2</v>
       </c>
       <c r="G11">
-        <v>172.1870739018374</v>
+        <v>0.275024596049772</v>
       </c>
       <c r="J11" t="s">
         <v>94</v>
       </c>
       <c r="K11">
-        <v>173.6497555759981</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>4.764861070548267</v>
+        <v>0.4029126890988887</v>
       </c>
       <c r="M11">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N11">
-        <v>13.2</v>
+        <v>0.4</v>
       </c>
       <c r="O11" t="s">
         <v>118</v>
       </c>
       <c r="P11">
-        <v>176.9807039529099</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.019181992890591</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R11">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="S11" t="s">
         <v>119</v>
       </c>
       <c r="T11">
-        <v>3.330948376911721</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>0.01929604709013688</v>
+        <v>0</v>
       </c>
       <c r="V11" t="s">
         <v>96</v>
       </c>
       <c r="W11">
-        <v>172.1870739018374</v>
+        <v>0.275024596049772</v>
       </c>
       <c r="X11">
-        <v>1.462681674160791</v>
+        <v>0.275024596049772</v>
       </c>
       <c r="Y11">
-        <v>3.350244424001858</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>0.3069725753814032</v>
+        <v>0.682591051338846</v>
       </c>
       <c r="AA11">
-        <v>0.7031148179135396</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.3609743235263839</v>
+        <v>1.007281722747221</v>
       </c>
       <c r="AC11">
-        <v>64.04255765445993</v>
+        <v>64.16680382679213</v>
       </c>
       <c r="AD11" t="s">
         <v>79</v>
@@ -6793,85 +6799,85 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
         <v>91</v>
       </c>
       <c r="C12">
-        <v>13.288</v>
+        <v>1.032</v>
       </c>
       <c r="D12">
-        <v>12.416</v>
+        <v>1.224</v>
       </c>
       <c r="E12">
-        <v>11.45044534583586</v>
+        <v>0.883771840094469</v>
       </c>
       <c r="F12">
-        <v>12.4</v>
+        <v>1.4</v>
       </c>
       <c r="G12">
-        <v>12.87813813537621</v>
+        <v>1.119683427227963</v>
       </c>
       <c r="J12" t="s">
         <v>94</v>
       </c>
       <c r="K12">
-        <v>11.45044534583586</v>
+        <v>0.883771840094469</v>
       </c>
       <c r="L12">
-        <v>2.351026032651849</v>
+        <v>0.9957719791398976</v>
       </c>
       <c r="M12">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N12">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="O12" t="s">
         <v>118</v>
       </c>
       <c r="P12">
-        <v>9.779145216252848</v>
+        <v>0.6952046069791448</v>
       </c>
       <c r="Q12">
-        <v>0.8540406002469759</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R12">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S12" t="s">
         <v>119</v>
       </c>
       <c r="T12">
-        <v>-1.671300129583011</v>
+        <v>-0.1885672331153242</v>
       </c>
       <c r="U12">
-        <v>0.2208547837471517</v>
+        <v>0.3047953930208552</v>
       </c>
       <c r="V12" t="s">
         <v>96</v>
       </c>
       <c r="W12">
-        <v>12.87813813537621</v>
+        <v>1.119683427227963</v>
       </c>
       <c r="X12">
-        <v>1.427692789540352</v>
+        <v>0.2359115871334945</v>
       </c>
       <c r="Y12">
-        <v>1.45044534583586</v>
+        <v>0.116228159905531</v>
       </c>
       <c r="Z12">
-        <v>0.6072637094239147</v>
+        <v>0.2369132613444939</v>
       </c>
       <c r="AA12">
-        <v>0.6169414228900835</v>
+        <v>0.1167216615252858</v>
       </c>
       <c r="AB12">
-        <v>0.6530627868477359</v>
+        <v>1.106413310155442</v>
       </c>
       <c r="AC12">
-        <v>54.29973121083951</v>
+        <v>82.29612186002319</v>
       </c>
       <c r="AD12" t="s">
         <v>120</v>
@@ -6879,343 +6885,343 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13">
-        <v>3.44</v>
+        <v>0.764</v>
       </c>
       <c r="D13">
-        <v>4.696</v>
+        <v>0.532</v>
       </c>
       <c r="E13">
-        <v>5.170440884727479</v>
+        <v>0.4302454583585212</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="G13">
-        <v>4.046198812423416</v>
+        <v>0.6580491920995442</v>
       </c>
       <c r="J13" t="s">
         <v>94</v>
       </c>
       <c r="K13">
-        <v>5.170440884727479</v>
+        <v>0.4302454583585212</v>
       </c>
       <c r="L13">
-        <v>2.262338789582505</v>
+        <v>0.4552884680086201</v>
       </c>
       <c r="M13">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="s">
         <v>118</v>
       </c>
       <c r="P13">
-        <v>5.269620245019544</v>
+        <v>0.5301779565157876</v>
       </c>
       <c r="Q13">
-        <v>1.019181992890591</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S13" t="s">
         <v>119</v>
       </c>
       <c r="T13">
-        <v>0.09917936029206498</v>
+        <v>0.09993249815726635</v>
       </c>
       <c r="U13">
-        <v>-0.269620245019544</v>
+        <v>0.4698220434842124</v>
       </c>
       <c r="V13" t="s">
         <v>96</v>
       </c>
       <c r="W13">
-        <v>4.046198812423416</v>
+        <v>0.6580491920995442</v>
       </c>
       <c r="X13">
-        <v>1.124242072304063</v>
+        <v>0.2278037337410229</v>
       </c>
       <c r="Y13">
-        <v>0.170440884727479</v>
+        <v>0.5697545416414788</v>
       </c>
       <c r="Z13">
-        <v>0.4969379818269978</v>
+        <v>0.5003503267662599</v>
       </c>
       <c r="AA13">
-        <v>0.07533835582553591</v>
+        <v>1.251414392579545</v>
       </c>
       <c r="AB13">
-        <v>0.452467757916501</v>
+        <v>0.7588141133477002</v>
       </c>
       <c r="AC13">
-        <v>70.51264625686264</v>
+        <v>46.61616811374733</v>
       </c>
       <c r="AD13" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C14">
-        <v>1.904</v>
+        <v>0.896</v>
       </c>
       <c r="D14">
-        <v>1.796</v>
+        <v>0.768</v>
       </c>
       <c r="E14">
-        <v>2.604250820161925</v>
+        <v>1.059965154885961</v>
       </c>
       <c r="F14">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="G14">
-        <v>1.851874624409452</v>
+        <v>0.8375443818480244</v>
       </c>
       <c r="J14" t="s">
         <v>94</v>
       </c>
       <c r="K14">
-        <v>2.604250820161925</v>
+        <v>1.059965154885961</v>
       </c>
       <c r="L14">
-        <v>1.198624596172324</v>
+        <v>0.4515884075301241</v>
       </c>
       <c r="M14">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N14">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="O14" t="s">
         <v>118</v>
       </c>
       <c r="P14">
-        <v>2.557215395085126</v>
+        <v>1.30616174762057</v>
       </c>
       <c r="Q14">
-        <v>0.981938980411313</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S14" t="s">
         <v>119</v>
       </c>
       <c r="T14">
-        <v>-0.04703542507679881</v>
+        <v>0.2461965927346088</v>
       </c>
       <c r="U14">
-        <v>0.4427846049148738</v>
+        <v>-0.3061617476205698</v>
       </c>
       <c r="V14" t="s">
         <v>96</v>
       </c>
       <c r="W14">
-        <v>1.851874624409452</v>
+        <v>0.8375443818480244</v>
       </c>
       <c r="X14">
-        <v>0.7523761957524733</v>
+        <v>0.2224207730379366</v>
       </c>
       <c r="Y14">
-        <v>0.395749179838075</v>
+        <v>0.05996515488596099</v>
       </c>
       <c r="Z14">
-        <v>0.6276996135029299</v>
+        <v>0.4925298553486442</v>
       </c>
       <c r="AA14">
-        <v>0.3301694134275707</v>
+        <v>0.1327871882582834</v>
       </c>
       <c r="AB14">
-        <v>0.7491403726077025</v>
+        <v>0.7526473458835402</v>
       </c>
       <c r="AC14">
-        <v>59.24054223283283</v>
+        <v>69.3073016888561</v>
       </c>
       <c r="AD14" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
         <v>91</v>
       </c>
       <c r="C15">
-        <v>0.6879999999999999</v>
+        <v>0.872</v>
       </c>
       <c r="D15">
-        <v>0.608</v>
+        <v>0.64</v>
       </c>
       <c r="E15">
-        <v>-0.01550360442781762</v>
+        <v>0.8641642373275472</v>
       </c>
       <c r="F15">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G15">
-        <v>0.6503979940712121</v>
+        <v>0.766049192099544</v>
       </c>
       <c r="J15" t="s">
         <v>94</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>0.8641642373275472</v>
       </c>
       <c r="L15">
-        <v>1.005444112310955</v>
+        <v>0.6809869320707522</v>
       </c>
       <c r="M15">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N15">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="O15" t="s">
         <v>118</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.064882430574224</v>
       </c>
       <c r="Q15">
-        <v>0.8540406002469759</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="s">
         <v>119</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>0.2007181932466767</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>-0.06488243057422394</v>
       </c>
       <c r="V15" t="s">
         <v>96</v>
       </c>
       <c r="W15">
-        <v>0.6503979940712121</v>
+        <v>0.766049192099544</v>
       </c>
       <c r="X15">
-        <v>0.6503979940712121</v>
+        <v>0.09811504522800318</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>0.1358357626724528</v>
       </c>
       <c r="Z15">
-        <v>0.6468763266973739</v>
+        <v>0.1440777210359293</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>0.1994689710996391</v>
       </c>
       <c r="AB15">
-        <v>1.117160124789949</v>
+        <v>0.8512336650884402</v>
       </c>
       <c r="AC15">
-        <v>65.67383349516004</v>
+        <v>84.91965103002815</v>
       </c>
       <c r="AD15" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
       </c>
       <c r="C16">
-        <v>1.12</v>
+        <v>0.872</v>
       </c>
       <c r="D16">
-        <v>1.168</v>
+        <v>0.64</v>
       </c>
       <c r="E16">
-        <v>1.780416614874208</v>
+        <v>0.8641642373275472</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G16">
-        <v>1.142561203557273</v>
+        <v>0.766049192099544</v>
       </c>
       <c r="J16" t="s">
         <v>94</v>
       </c>
       <c r="K16">
-        <v>1.780416614874208</v>
+        <v>0.8641642373275472</v>
       </c>
       <c r="L16">
-        <v>0.8500971208676269</v>
+        <v>0.6809869320707522</v>
       </c>
       <c r="M16">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N16">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="O16" t="s">
         <v>118</v>
       </c>
       <c r="P16">
-        <v>2.046609860316908</v>
+        <v>1.064882430574224</v>
       </c>
       <c r="Q16">
-        <v>1.149511773378675</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" t="s">
         <v>119</v>
       </c>
       <c r="T16">
-        <v>0.2661932454427003</v>
+        <v>0.2007181932466767</v>
       </c>
       <c r="U16">
-        <v>-0.04660986031690806</v>
+        <v>-0.06488243057422394</v>
       </c>
       <c r="V16" t="s">
         <v>96</v>
       </c>
       <c r="W16">
-        <v>1.142561203557273</v>
+        <v>0.766049192099544</v>
       </c>
       <c r="X16">
-        <v>0.6378554113169352</v>
+        <v>0.09811504522800318</v>
       </c>
       <c r="Y16">
-        <v>0.2195833851257922</v>
+        <v>0.1358357626724528</v>
       </c>
       <c r="Z16">
-        <v>0.7503323980981451</v>
+        <v>0.1440777210359293</v>
       </c>
       <c r="AA16">
-        <v>0.2583038805044779</v>
+        <v>0.1994689710996391</v>
       </c>
       <c r="AB16">
-        <v>1.700194241735254</v>
+        <v>0.8512336650884402</v>
       </c>
       <c r="AC16">
-        <v>56.09506097814787</v>
+        <v>84.91965103002815</v>
       </c>
       <c r="AD16" t="s">
         <v>120</v>

--- a/outputs/Block5_Election_Projection_Report.xlsx
+++ b/outputs/Block5_Election_Projection_Report.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.9566065934066</v>
+        <v>52.80457815565729</v>
       </c>
       <c r="C2" t="inlineStr"/>
     </row>
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.1233934065934</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="C3" t="inlineStr"/>
     </row>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.92</v>
+        <v>2.919999999999995</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -1188,37 +1188,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>44.1233934065934</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="F10" t="n">
-        <v>44.12339340659342</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="G10" t="n">
-        <v>44.16657142857143</v>
+        <v>44.31874863745368</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07847626697110505</v>
+        <v>0.07874665923576957</v>
       </c>
       <c r="J10" t="n">
-        <v>43.99613186813187</v>
+        <v>44.14772182254198</v>
       </c>
       <c r="K10" t="n">
-        <v>44.17793406593407</v>
+        <v>44.33015042511447</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1818021978021989</v>
+        <v>0.1824286025724859</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1272615384615321</v>
+        <v>0.1277000218007345</v>
       </c>
       <c r="N10" t="n">
         <v>1.064148394560983</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1195900300296315</v>
+        <v>0.1200020809629821</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
@@ -1256,37 +1256,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>52.9566065934066</v>
+        <v>52.80457815565729</v>
       </c>
       <c r="F11" t="n">
-        <v>52.9566065934066</v>
+        <v>52.8045781556573</v>
       </c>
       <c r="G11" t="n">
-        <v>53.00842857142858</v>
+        <v>52.85625136254632</v>
       </c>
       <c r="H11" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09418669952721606</v>
+        <v>0.09391630726254439</v>
       </c>
       <c r="J11" t="n">
-        <v>52.80386813186814</v>
+        <v>52.65227817745804</v>
       </c>
       <c r="K11" t="n">
-        <v>53.02206593406594</v>
+        <v>52.86984957488554</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2181978021978068</v>
+        <v>0.2175713974275055</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1527384615384619</v>
+        <v>0.1522999781992525</v>
       </c>
       <c r="N11" t="n">
         <v>1.323492690170848</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1154055951142013</v>
+        <v>0.1150742873990428</v>
       </c>
       <c r="P11" t="b">
         <v>1</v>
@@ -1430,37 +1430,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52.9566065934066</v>
+        <v>52.80457815565729</v>
       </c>
       <c r="F2" t="n">
-        <v>52.9566065934066</v>
+        <v>52.8045781556573</v>
       </c>
       <c r="G2" t="n">
-        <v>53.00842857142858</v>
+        <v>52.85625136254632</v>
       </c>
       <c r="H2" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09418669952721606</v>
+        <v>0.09391630726254439</v>
       </c>
       <c r="J2" t="n">
-        <v>52.80386813186814</v>
+        <v>52.65227817745804</v>
       </c>
       <c r="K2" t="n">
-        <v>53.02206593406594</v>
+        <v>52.86984957488554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2181978021978068</v>
+        <v>0.2175713974275055</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1527384615384619</v>
+        <v>0.1522999781992525</v>
       </c>
       <c r="N2" t="n">
         <v>1.323492690170848</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1154055951142013</v>
+        <v>0.1150742873990428</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -1498,37 +1498,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>44.1233934065934</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="F3" t="n">
-        <v>44.12339340659342</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="G3" t="n">
-        <v>44.16657142857143</v>
+        <v>44.31874863745368</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07847626697110505</v>
+        <v>0.07874665923576957</v>
       </c>
       <c r="J3" t="n">
-        <v>43.99613186813187</v>
+        <v>44.14772182254198</v>
       </c>
       <c r="K3" t="n">
-        <v>44.17793406593407</v>
+        <v>44.33015042511447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1818021978021989</v>
+        <v>0.1824286025724859</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1272615384615321</v>
+        <v>0.1277000218007345</v>
       </c>
       <c r="N3" t="n">
         <v>1.064148394560983</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1195900300296315</v>
+        <v>0.1200020809629821</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
@@ -2099,7 +2099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dd0af9f211044926f193d3ea436dabde2b2960f060ab768c53232e3e59f37c10</t>
+          <t>69084551907b520052181adf33e09563f086f0b6de4f1d95d2e192b06c14159d</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T02:41:23.457320+00:00</t>
+          <t>2026-10-24T07:22:07.989106+00:00</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20T06:09:32.147340+00:00</t>
+          <t>2026-10-24T07:24:45.840036+00:00</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20T06:11:56.240312+00:00</t>
+          <t>2026-10-24T07:26:59.123079+00:00</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>35-race structural motor + polling enrichment on 12 monitored races</t>
+          <t>35-race structural motor + polling enrichment on 15 monitored races</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,53 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Public Senate map highlights 12 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+          <t>Public Senate map highlights 15 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration source</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Recovered Model(5).xlsx / Senate Historic</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration rows</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration reference SHA256</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7b3f807a5128485c7fd4de43f99733784af9627e835db4777c047b68e762feb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senate production policy</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Recovered 5B calibration + 15 current monitored races; automatic structural blending disabled</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2588,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6254f3f54af6754b67deae4c4b8445dd2c4a92fbbcded33cef106f4df9255f2a</t>
+          <t>8a7bfde9efafe267b78417530287877a5e160939951e8ae39d62138f60d4e05a</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2624,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T06:12:00.987520+00:00</t>
+          <t>2026-10-24T07:27:04.098692+00:00</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2685,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
     </row>
     <row r="3">
@@ -2649,7 +2695,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
     </row>
     <row r="4">
@@ -2659,7 +2705,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0292</v>
+        <v>0.02919999999999995</v>
       </c>
     </row>
   </sheetData>
@@ -2725,10 +2771,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C2" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2736,13 +2782,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2992,10 +3038,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.927364392626764</v>
+        <v>4.927364392626762</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6674744605579519</v>
+        <v>-0.6674744605579497</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
@@ -3129,37 +3175,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52.9566065934066</v>
+        <v>52.80457815565729</v>
       </c>
       <c r="F2" t="n">
-        <v>52.9566065934066</v>
+        <v>52.8045781556573</v>
       </c>
       <c r="G2" t="n">
-        <v>53.00842857142858</v>
+        <v>52.85625136254632</v>
       </c>
       <c r="H2" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09418669952721606</v>
+        <v>0.09391630726254439</v>
       </c>
       <c r="J2" t="n">
-        <v>52.80386813186814</v>
+        <v>52.65227817745804</v>
       </c>
       <c r="K2" t="n">
-        <v>53.02206593406594</v>
+        <v>52.86984957488554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2181978021978068</v>
+        <v>0.2175713974275055</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1527384615384619</v>
+        <v>0.1522999781992525</v>
       </c>
       <c r="N2" t="n">
         <v>1.323492690170848</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1154055951142013</v>
+        <v>0.1150742873990428</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -3197,37 +3243,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>44.1233934065934</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="F3" t="n">
-        <v>44.12339340659342</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="G3" t="n">
-        <v>44.16657142857143</v>
+        <v>44.31874863745368</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07847626697110505</v>
+        <v>0.07874665923576957</v>
       </c>
       <c r="J3" t="n">
-        <v>43.99613186813187</v>
+        <v>44.14772182254198</v>
       </c>
       <c r="K3" t="n">
-        <v>44.17793406593407</v>
+        <v>44.33015042511447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1818021978021989</v>
+        <v>0.1824286025724859</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1272615384615321</v>
+        <v>0.1277000218007345</v>
       </c>
       <c r="N3" t="n">
         <v>1.064148394560983</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1195900300296315</v>
+        <v>0.1200020809629821</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
@@ -3930,25 +3976,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5142079999999999</v>
+        <v>0.5143840000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4958199999999996</v>
+        <v>0.4959679999999996</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4976068069845513</v>
+        <v>0.4972024416993439</v>
       </c>
       <c r="F2" t="n">
         <v>0.4868</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5062773903434608</v>
+        <v>0.506441314148639</v>
       </c>
       <c r="H2" t="n">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="I2" t="n">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3956,7 +4002,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="L2" t="n">
         <v>0.01323492690170848</v>
@@ -3975,7 +4021,7 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -4003,25 +4049,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4576439999999986</v>
+        <v>0.4577239999999985</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4753639999999988</v>
+        <v>0.4752239999999988</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4714935259345234</v>
+        <v>0.471947408691133</v>
       </c>
       <c r="F3" t="n">
         <v>0.484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4652865061515034</v>
+        <v>0.4652716217636178</v>
       </c>
       <c r="H3" t="n">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="I3" t="n">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4029,7 +4075,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="L3" t="n">
         <v>0.01064148394560983</v>
@@ -4048,7 +4094,7 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -4600,37 +4646,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52.9566065934066</v>
+        <v>52.80457815565729</v>
       </c>
       <c r="F2" t="n">
-        <v>52.9566065934066</v>
+        <v>52.8045781556573</v>
       </c>
       <c r="G2" t="n">
-        <v>53.00842857142858</v>
+        <v>52.85625136254632</v>
       </c>
       <c r="H2" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09418669952721606</v>
+        <v>0.09391630726254439</v>
       </c>
       <c r="J2" t="n">
-        <v>52.80386813186814</v>
+        <v>52.65227817745804</v>
       </c>
       <c r="K2" t="n">
-        <v>53.02206593406594</v>
+        <v>52.86984957488554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2181978021978068</v>
+        <v>0.2175713974275055</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1527384615384619</v>
+        <v>0.1522999781992525</v>
       </c>
       <c r="N2" t="n">
         <v>1.323492690170848</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1154055951142013</v>
+        <v>0.1150742873990428</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -4668,37 +4714,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>44.1233934065934</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="F3" t="n">
-        <v>44.12339340659342</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="G3" t="n">
-        <v>44.16657142857143</v>
+        <v>44.31874863745368</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07847626697110505</v>
+        <v>0.07874665923576957</v>
       </c>
       <c r="J3" t="n">
-        <v>43.99613186813187</v>
+        <v>44.14772182254198</v>
       </c>
       <c r="K3" t="n">
-        <v>44.17793406593407</v>
+        <v>44.33015042511447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1818021978021989</v>
+        <v>0.1824286025724859</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1272615384615321</v>
+        <v>0.1277000218007345</v>
       </c>
       <c r="N3" t="n">
         <v>1.064148394560983</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1195900300296315</v>
+        <v>0.1200020809629821</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
